--- a/AAII_Financials/Quarterly/ELBM_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/ELBM_QTR_FIN.xlsx
@@ -5,7 +5,7 @@
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Stocks_Automation\AAII_Financials\Quarterly\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Private\Investing\Automation\AAII\AAII_Financials\Quarterly\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -17,12 +17,12 @@
   <definedNames>
     <definedName name="Ticker">#REF!</definedName>
   </definedNames>
-  <calcPr calcId="152511" calcMode="manual" concurrentCalc="0"/>
+  <calcPr calcId="152511" calcMode="manual"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="186" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="180" uniqueCount="92">
   <si>
     <t>ELBM</t>
   </si>
@@ -1548,8 +1548,8 @@
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="D26" s="3" t="s">
-        <v>4</v>
+      <c r="D26" s="3">
+        <v>-9200</v>
       </c>
       <c r="E26" s="3">
         <v>12000</v>
@@ -1598,8 +1598,8 @@
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="D27" s="3" t="s">
-        <v>4</v>
+      <c r="D27" s="3">
+        <v>-9200</v>
       </c>
       <c r="E27" s="3">
         <v>12000</v>
@@ -1898,8 +1898,8 @@
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="D33" s="3" t="s">
-        <v>4</v>
+      <c r="D33" s="3">
+        <v>-9200</v>
       </c>
       <c r="E33" s="3">
         <v>12000</v>
@@ -1998,8 +1998,8 @@
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="D35" s="3" t="s">
-        <v>4</v>
+      <c r="D35" s="3">
+        <v>-9200</v>
       </c>
       <c r="E35" s="3">
         <v>12000</v>
@@ -2884,7 +2884,7 @@
         <v>50</v>
       </c>
       <c r="D57" s="3">
-        <v>5600</v>
+        <v>9600</v>
       </c>
       <c r="E57" s="3">
         <v>17100</v>
@@ -2934,7 +2934,7 @@
         <v>51</v>
       </c>
       <c r="D58" s="3">
-        <v>54500</v>
+        <v>55300</v>
       </c>
       <c r="E58" s="3">
         <v>5200</v>
@@ -3958,8 +3958,8 @@
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="D81" s="3" t="s">
-        <v>4</v>
+      <c r="D81" s="3">
+        <v>-9200</v>
       </c>
       <c r="E81" s="3">
         <v>12000</v>
@@ -4918,8 +4918,8 @@
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
-      <c r="D102" s="3" t="s">
-        <v>4</v>
+      <c r="D102" s="3">
+        <v>8800</v>
       </c>
       <c r="E102" s="3">
         <v>-5000</v>

--- a/AAII_Financials/Quarterly/ELBM_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/ELBM_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="180" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="183" uniqueCount="92">
   <si>
     <t>ELBM</t>
   </si>
@@ -656,88 +656,95 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:R102"/>
+  <dimension ref="A5:T102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.42578125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="16" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:20" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:20" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45382</v>
+      </c>
+      <c r="E7" s="2">
+        <v>45291</v>
+      </c>
+      <c r="F7" s="2">
         <v>45199</v>
       </c>
-      <c r="E7" s="2">
+      <c r="G7" s="2">
         <v>45107</v>
       </c>
-      <c r="F7" s="2">
+      <c r="H7" s="2">
         <v>45016</v>
       </c>
-      <c r="G7" s="2">
+      <c r="I7" s="2">
         <v>44926</v>
       </c>
-      <c r="H7" s="2">
+      <c r="J7" s="2">
         <v>44834</v>
       </c>
-      <c r="I7" s="2">
+      <c r="K7" s="2">
         <v>44742</v>
       </c>
-      <c r="J7" s="2">
+      <c r="L7" s="2">
         <v>44651</v>
       </c>
-      <c r="K7" s="2">
+      <c r="M7" s="2">
         <v>44561</v>
       </c>
-      <c r="L7" s="2">
+      <c r="N7" s="2">
         <v>44469</v>
       </c>
-      <c r="M7" s="2">
+      <c r="O7" s="2">
         <v>44377</v>
       </c>
-      <c r="N7" s="2">
+      <c r="P7" s="2">
         <v>44286</v>
       </c>
-      <c r="O7" s="2">
+      <c r="Q7" s="2">
         <v>44196</v>
       </c>
-      <c r="P7" s="2">
+      <c r="R7" s="2">
         <v>44104</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="S7" s="2">
         <v>44012</v>
       </c>
-      <c r="R7" s="2">
+      <c r="T7" s="2">
         <v>43921</v>
       </c>
     </row>
-    <row r="8" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:20" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
@@ -786,8 +793,14 @@
       <c r="R8" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="9" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S8" s="3">
+        <v>0</v>
+      </c>
+      <c r="T8" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:20" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
@@ -836,8 +849,14 @@
       <c r="R9" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="10" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S9" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="T9" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="10" spans="1:20" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
@@ -886,8 +905,14 @@
       <c r="R10" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="11" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S10" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="T10" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="11" spans="1:20" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -906,58 +931,66 @@
       <c r="P11" s="3"/>
       <c r="Q11" s="3"/>
       <c r="R11" s="3"/>
-    </row>
-    <row r="12" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S11" s="3"/>
+      <c r="T11" s="3"/>
+    </row>
+    <row r="12" spans="1:20" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D12" s="3">
+        <v>100</v>
+      </c>
+      <c r="E12" s="3">
+        <v>100</v>
+      </c>
+      <c r="F12" s="3">
         <v>300</v>
       </c>
-      <c r="E12" s="3">
+      <c r="G12" s="3">
         <v>300</v>
       </c>
-      <c r="F12" s="3">
+      <c r="H12" s="3">
         <v>100</v>
       </c>
-      <c r="G12" s="3">
+      <c r="I12" s="3">
         <v>600</v>
       </c>
-      <c r="H12" s="3">
+      <c r="J12" s="3">
         <v>1300</v>
       </c>
-      <c r="I12" s="3">
+      <c r="K12" s="3">
         <v>1100</v>
       </c>
-      <c r="J12" s="3">
+      <c r="L12" s="3">
         <v>400</v>
       </c>
-      <c r="K12" s="3">
+      <c r="M12" s="3">
         <v>2900</v>
       </c>
-      <c r="L12" s="3">
+      <c r="N12" s="3">
         <v>1200</v>
       </c>
-      <c r="M12" s="3">
+      <c r="O12" s="3">
         <v>400</v>
-      </c>
-      <c r="N12" s="3">
-        <v>100</v>
-      </c>
-      <c r="O12" s="3">
-        <v>300</v>
       </c>
       <c r="P12" s="3">
         <v>100</v>
       </c>
       <c r="Q12" s="3">
-        <v>0</v>
+        <v>300</v>
       </c>
       <c r="R12" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="13" spans="1:18" x14ac:dyDescent="0.2">
+        <v>100</v>
+      </c>
+      <c r="S12" s="3">
+        <v>0</v>
+      </c>
+      <c r="T12" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" spans="1:20" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1006,58 +1039,70 @@
       <c r="R13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S13" s="3">
+        <v>0</v>
+      </c>
+      <c r="T13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:20" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="D14" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="E14" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="F14" s="3" t="s">
-        <v>4</v>
+      <c r="D14" s="3">
+        <v>0</v>
+      </c>
+      <c r="E14" s="3">
+        <v>50500</v>
+      </c>
+      <c r="F14" s="3">
+        <v>0</v>
       </c>
       <c r="G14" s="3">
+        <v>0</v>
+      </c>
+      <c r="H14" s="3">
+        <v>18700</v>
+      </c>
+      <c r="I14" s="3">
         <v>-1300</v>
       </c>
-      <c r="H14" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="I14" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="J14" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="K14" s="3">
-        <v>0</v>
-      </c>
-      <c r="L14" s="3">
-        <v>0</v>
+      <c r="K14" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="L14" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="M14" s="3">
+        <v>0</v>
+      </c>
+      <c r="N14" s="3">
+        <v>0</v>
+      </c>
+      <c r="O14" s="3">
         <v>1600</v>
       </c>
-      <c r="N14" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="O14" s="3">
+      <c r="P14" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Q14" s="3">
         <v>-5700</v>
       </c>
-      <c r="P14" s="3">
-        <v>0</v>
-      </c>
-      <c r="Q14" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="R14" s="3" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="15" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="R14" s="3">
+        <v>0</v>
+      </c>
+      <c r="S14" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="T14" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="15" spans="1:20" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1106,8 +1151,14 @@
       <c r="R15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S15" s="3">
+        <v>0</v>
+      </c>
+      <c r="T15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:20" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1123,58 +1174,66 @@
       <c r="P16" s="3"/>
       <c r="Q16" s="3"/>
       <c r="R16" s="3"/>
-    </row>
-    <row r="17" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S16" s="3"/>
+      <c r="T16" s="3"/>
+    </row>
+    <row r="17" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>3300</v>
+      </c>
+      <c r="E17" s="3">
+        <v>52000</v>
+      </c>
+      <c r="F17" s="3">
         <v>4200</v>
       </c>
-      <c r="E17" s="3">
+      <c r="G17" s="3">
         <v>4500</v>
       </c>
-      <c r="F17" s="3">
-        <v>3800</v>
-      </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
+        <v>22500</v>
+      </c>
+      <c r="I17" s="3">
         <v>4200</v>
       </c>
-      <c r="H17" s="3">
+      <c r="J17" s="3">
         <v>4800</v>
       </c>
-      <c r="I17" s="3">
+      <c r="K17" s="3">
         <v>3900</v>
       </c>
-      <c r="J17" s="3">
+      <c r="L17" s="3">
         <v>2500</v>
       </c>
-      <c r="K17" s="3">
+      <c r="M17" s="3">
         <v>6600</v>
       </c>
-      <c r="L17" s="3">
+      <c r="N17" s="3">
         <v>6500</v>
       </c>
-      <c r="M17" s="3">
+      <c r="O17" s="3">
         <v>5300</v>
       </c>
-      <c r="N17" s="3">
+      <c r="P17" s="3">
         <v>2300</v>
       </c>
-      <c r="O17" s="3">
+      <c r="Q17" s="3">
         <v>-3000</v>
       </c>
-      <c r="P17" s="3">
+      <c r="R17" s="3">
         <v>1400</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="S17" s="3">
         <v>1500</v>
       </c>
-      <c r="R17" s="3">
+      <c r="T17" s="3">
         <v>1800</v>
       </c>
     </row>
-    <row r="18" spans="3:18" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
@@ -1182,49 +1241,55 @@
         <v>4</v>
       </c>
       <c r="E18" s="3">
+        <v>-52000</v>
+      </c>
+      <c r="F18" s="3">
+        <v>-4200</v>
+      </c>
+      <c r="G18" s="3">
         <v>-4500</v>
       </c>
-      <c r="F18" s="3">
-        <v>-3800</v>
-      </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
+        <v>-22500</v>
+      </c>
+      <c r="I18" s="3">
         <v>-4200</v>
       </c>
-      <c r="H18" s="3">
+      <c r="J18" s="3">
         <v>-4800</v>
       </c>
-      <c r="I18" s="3">
+      <c r="K18" s="3">
         <v>-3900</v>
       </c>
-      <c r="J18" s="3">
+      <c r="L18" s="3">
         <v>-2500</v>
       </c>
-      <c r="K18" s="3">
+      <c r="M18" s="3">
         <v>-6600</v>
       </c>
-      <c r="L18" s="3">
+      <c r="N18" s="3">
         <v>-6500</v>
       </c>
-      <c r="M18" s="3">
+      <c r="O18" s="3">
         <v>-5300</v>
       </c>
-      <c r="N18" s="3">
+      <c r="P18" s="3">
         <v>-2300</v>
       </c>
-      <c r="O18" s="3">
+      <c r="Q18" s="3">
         <v>3000</v>
       </c>
-      <c r="P18" s="3">
+      <c r="R18" s="3">
         <v>-1400</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="S18" s="3">
         <v>-1500</v>
       </c>
-      <c r="R18" s="3">
+      <c r="T18" s="3">
         <v>-1800</v>
       </c>
     </row>
-    <row r="19" spans="3:18" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1243,8 +1308,10 @@
       <c r="P19" s="3"/>
       <c r="Q19" s="3"/>
       <c r="R19" s="3"/>
-    </row>
-    <row r="20" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S19" s="3"/>
+      <c r="T19" s="3"/>
+    </row>
+    <row r="20" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
@@ -1252,49 +1319,55 @@
         <v>4</v>
       </c>
       <c r="E20" s="3">
+        <v>6500</v>
+      </c>
+      <c r="F20" s="3">
+        <v>-5100</v>
+      </c>
+      <c r="G20" s="3">
         <v>16500</v>
       </c>
-      <c r="F20" s="3">
-        <v>-18200</v>
-      </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
+        <v>2200</v>
+      </c>
+      <c r="I20" s="3">
         <v>14500</v>
       </c>
-      <c r="H20" s="3">
+      <c r="J20" s="3">
         <v>-2800</v>
       </c>
-      <c r="I20" s="3">
+      <c r="K20" s="3">
         <v>11400</v>
       </c>
-      <c r="J20" s="3">
+      <c r="L20" s="3">
         <v>4800</v>
       </c>
-      <c r="K20" s="3">
+      <c r="M20" s="3">
         <v>-8900</v>
       </c>
-      <c r="L20" s="3">
+      <c r="N20" s="3">
         <v>-4000</v>
       </c>
-      <c r="M20" s="3">
+      <c r="O20" s="3">
         <v>-1100</v>
-      </c>
-      <c r="N20" s="3">
-        <v>-100</v>
-      </c>
-      <c r="O20" s="3">
-        <v>-100</v>
       </c>
       <c r="P20" s="3">
         <v>-100</v>
       </c>
       <c r="Q20" s="3">
+        <v>-100</v>
+      </c>
+      <c r="R20" s="3">
+        <v>-100</v>
+      </c>
+      <c r="S20" s="3">
         <v>-200</v>
       </c>
-      <c r="R20" s="3">
+      <c r="T20" s="3">
         <v>-300</v>
       </c>
     </row>
-    <row r="21" spans="3:18" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
@@ -1302,49 +1375,55 @@
         <v>4</v>
       </c>
       <c r="E21" s="3">
+        <v>-45500</v>
+      </c>
+      <c r="F21" s="3">
+        <v>-9200</v>
+      </c>
+      <c r="G21" s="3">
         <v>12000</v>
       </c>
-      <c r="F21" s="3">
-        <v>-22000</v>
-      </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
+        <v>-20300</v>
+      </c>
+      <c r="I21" s="3">
         <v>10400</v>
       </c>
-      <c r="H21" s="3">
+      <c r="J21" s="3">
         <v>-7600</v>
       </c>
-      <c r="I21" s="3">
+      <c r="K21" s="3">
         <v>7500</v>
       </c>
-      <c r="J21" s="3">
+      <c r="L21" s="3">
         <v>2300</v>
       </c>
-      <c r="K21" s="3">
+      <c r="M21" s="3">
         <v>-15500</v>
       </c>
-      <c r="L21" s="3">
+      <c r="N21" s="3">
         <v>-10500</v>
       </c>
-      <c r="M21" s="3">
+      <c r="O21" s="3">
         <v>-6400</v>
       </c>
-      <c r="N21" s="3">
+      <c r="P21" s="3">
         <v>-2400</v>
       </c>
-      <c r="O21" s="3">
+      <c r="Q21" s="3">
         <v>2900</v>
       </c>
-      <c r="P21" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="Q21" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="R21" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="22" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S21" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="T21" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="22" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1372,79 +1451,91 @@
       <c r="K22" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="L22" s="3">
-        <v>0</v>
-      </c>
-      <c r="M22" s="3">
-        <v>0</v>
+      <c r="L22" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="M22" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="N22" s="3">
+        <v>0</v>
+      </c>
+      <c r="O22" s="3">
+        <v>0</v>
+      </c>
+      <c r="P22" s="3">
         <v>100</v>
       </c>
-      <c r="O22" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="P22" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="Q22" s="3" t="s">
         <v>4</v>
       </c>
       <c r="R22" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="23" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S22" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="T22" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="23" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-12200</v>
+      </c>
+      <c r="E23" s="3">
+        <v>-45500</v>
+      </c>
+      <c r="F23" s="3">
         <v>-9200</v>
       </c>
-      <c r="E23" s="3">
+      <c r="G23" s="3">
         <v>12000</v>
       </c>
-      <c r="F23" s="3">
-        <v>-22000</v>
-      </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
+        <v>-20300</v>
+      </c>
+      <c r="I23" s="3">
         <v>10300</v>
       </c>
-      <c r="H23" s="3">
+      <c r="J23" s="3">
         <v>-7600</v>
       </c>
-      <c r="I23" s="3">
+      <c r="K23" s="3">
         <v>7500</v>
       </c>
-      <c r="J23" s="3">
+      <c r="L23" s="3">
         <v>2300</v>
       </c>
-      <c r="K23" s="3">
+      <c r="M23" s="3">
         <v>-15500</v>
       </c>
-      <c r="L23" s="3">
+      <c r="N23" s="3">
         <v>-10500</v>
       </c>
-      <c r="M23" s="3">
+      <c r="O23" s="3">
         <v>-6400</v>
       </c>
-      <c r="N23" s="3">
+      <c r="P23" s="3">
         <v>-2500</v>
       </c>
-      <c r="O23" s="3">
+      <c r="Q23" s="3">
         <v>2900</v>
       </c>
-      <c r="P23" s="3">
+      <c r="R23" s="3">
         <v>-1500</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="S23" s="3">
         <v>-1700</v>
       </c>
-      <c r="R23" s="3">
+      <c r="T23" s="3">
         <v>-2100</v>
       </c>
     </row>
-    <row r="24" spans="3:18" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
@@ -1493,8 +1584,14 @@
       <c r="R24" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="25" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S24" s="3">
+        <v>0</v>
+      </c>
+      <c r="T24" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1543,108 +1640,126 @@
       <c r="R25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S25" s="3">
+        <v>0</v>
+      </c>
+      <c r="T25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-12200</v>
+      </c>
+      <c r="E26" s="3">
+        <v>-45500</v>
+      </c>
+      <c r="F26" s="3">
         <v>-9200</v>
       </c>
-      <c r="E26" s="3">
+      <c r="G26" s="3">
         <v>12000</v>
       </c>
-      <c r="F26" s="3">
-        <v>-22000</v>
-      </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
+        <v>-20300</v>
+      </c>
+      <c r="I26" s="3">
         <v>10300</v>
       </c>
-      <c r="H26" s="3">
+      <c r="J26" s="3">
         <v>-7600</v>
       </c>
-      <c r="I26" s="3">
+      <c r="K26" s="3">
         <v>7500</v>
       </c>
-      <c r="J26" s="3">
+      <c r="L26" s="3">
         <v>2300</v>
       </c>
-      <c r="K26" s="3">
+      <c r="M26" s="3">
         <v>-15500</v>
       </c>
-      <c r="L26" s="3">
+      <c r="N26" s="3">
         <v>-10500</v>
       </c>
-      <c r="M26" s="3">
+      <c r="O26" s="3">
         <v>-6400</v>
       </c>
-      <c r="N26" s="3">
+      <c r="P26" s="3">
         <v>-2500</v>
       </c>
-      <c r="O26" s="3">
+      <c r="Q26" s="3">
         <v>2900</v>
       </c>
-      <c r="P26" s="3">
+      <c r="R26" s="3">
         <v>-1500</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="S26" s="3">
         <v>-1700</v>
       </c>
-      <c r="R26" s="3">
+      <c r="T26" s="3">
         <v>-2100</v>
       </c>
     </row>
-    <row r="27" spans="3:18" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-12200</v>
+      </c>
+      <c r="E27" s="3">
+        <v>-45500</v>
+      </c>
+      <c r="F27" s="3">
         <v>-9200</v>
       </c>
-      <c r="E27" s="3">
+      <c r="G27" s="3">
         <v>12000</v>
       </c>
-      <c r="F27" s="3">
-        <v>-22000</v>
-      </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
+        <v>-20300</v>
+      </c>
+      <c r="I27" s="3">
         <v>10300</v>
       </c>
-      <c r="H27" s="3">
+      <c r="J27" s="3">
         <v>-7600</v>
       </c>
-      <c r="I27" s="3">
+      <c r="K27" s="3">
         <v>7500</v>
       </c>
-      <c r="J27" s="3">
+      <c r="L27" s="3">
         <v>2300</v>
       </c>
-      <c r="K27" s="3">
+      <c r="M27" s="3">
         <v>-15500</v>
       </c>
-      <c r="L27" s="3">
+      <c r="N27" s="3">
         <v>-10500</v>
       </c>
-      <c r="M27" s="3">
+      <c r="O27" s="3">
         <v>-6400</v>
       </c>
-      <c r="N27" s="3">
+      <c r="P27" s="3">
         <v>-2500</v>
       </c>
-      <c r="O27" s="3">
+      <c r="Q27" s="3">
         <v>2900</v>
       </c>
-      <c r="P27" s="3">
+      <c r="R27" s="3">
         <v>-1500</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="S27" s="3">
         <v>-1700</v>
       </c>
-      <c r="R27" s="3">
+      <c r="T27" s="3">
         <v>-2100</v>
       </c>
     </row>
-    <row r="28" spans="3:18" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1693,8 +1808,14 @@
       <c r="R28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S28" s="3">
+        <v>0</v>
+      </c>
+      <c r="T28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1743,8 +1864,14 @@
       <c r="R29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S29" s="3">
+        <v>0</v>
+      </c>
+      <c r="T29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1793,8 +1920,14 @@
       <c r="R30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S30" s="3">
+        <v>0</v>
+      </c>
+      <c r="T30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1843,8 +1976,14 @@
       <c r="R31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S31" s="3">
+        <v>0</v>
+      </c>
+      <c r="T31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
@@ -1852,99 +1991,111 @@
         <v>4</v>
       </c>
       <c r="E32" s="3">
+        <v>-6500</v>
+      </c>
+      <c r="F32" s="3">
+        <v>5100</v>
+      </c>
+      <c r="G32" s="3">
         <v>-16500</v>
       </c>
-      <c r="F32" s="3">
-        <v>18200</v>
-      </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
+        <v>-2200</v>
+      </c>
+      <c r="I32" s="3">
         <v>-14500</v>
       </c>
-      <c r="H32" s="3">
+      <c r="J32" s="3">
         <v>2800</v>
       </c>
-      <c r="I32" s="3">
+      <c r="K32" s="3">
         <v>-11400</v>
       </c>
-      <c r="J32" s="3">
+      <c r="L32" s="3">
         <v>-4800</v>
       </c>
-      <c r="K32" s="3">
+      <c r="M32" s="3">
         <v>8900</v>
       </c>
-      <c r="L32" s="3">
+      <c r="N32" s="3">
         <v>4000</v>
       </c>
-      <c r="M32" s="3">
+      <c r="O32" s="3">
         <v>1100</v>
-      </c>
-      <c r="N32" s="3">
-        <v>100</v>
-      </c>
-      <c r="O32" s="3">
-        <v>100</v>
       </c>
       <c r="P32" s="3">
         <v>100</v>
       </c>
       <c r="Q32" s="3">
+        <v>100</v>
+      </c>
+      <c r="R32" s="3">
+        <v>100</v>
+      </c>
+      <c r="S32" s="3">
         <v>200</v>
       </c>
-      <c r="R32" s="3">
+      <c r="T32" s="3">
         <v>300</v>
       </c>
     </row>
-    <row r="33" spans="2:18" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-12200</v>
+      </c>
+      <c r="E33" s="3">
+        <v>-45500</v>
+      </c>
+      <c r="F33" s="3">
         <v>-9200</v>
       </c>
-      <c r="E33" s="3">
+      <c r="G33" s="3">
         <v>12000</v>
       </c>
-      <c r="F33" s="3">
-        <v>-22000</v>
-      </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
+        <v>-20300</v>
+      </c>
+      <c r="I33" s="3">
         <v>10300</v>
       </c>
-      <c r="H33" s="3">
+      <c r="J33" s="3">
         <v>-7600</v>
       </c>
-      <c r="I33" s="3">
+      <c r="K33" s="3">
         <v>7500</v>
       </c>
-      <c r="J33" s="3">
+      <c r="L33" s="3">
         <v>2300</v>
       </c>
-      <c r="K33" s="3">
+      <c r="M33" s="3">
         <v>-15500</v>
       </c>
-      <c r="L33" s="3">
+      <c r="N33" s="3">
         <v>-10500</v>
       </c>
-      <c r="M33" s="3">
+      <c r="O33" s="3">
         <v>-6400</v>
       </c>
-      <c r="N33" s="3">
+      <c r="P33" s="3">
         <v>-2500</v>
       </c>
-      <c r="O33" s="3">
+      <c r="Q33" s="3">
         <v>2900</v>
       </c>
-      <c r="P33" s="3">
+      <c r="R33" s="3">
         <v>-1500</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="S33" s="3">
         <v>-1700</v>
       </c>
-      <c r="R33" s="3">
+      <c r="T33" s="3">
         <v>-2100</v>
       </c>
     </row>
-    <row r="34" spans="2:18" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -1993,113 +2144,131 @@
       <c r="R34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S34" s="3">
+        <v>0</v>
+      </c>
+      <c r="T34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-12200</v>
+      </c>
+      <c r="E35" s="3">
+        <v>-45500</v>
+      </c>
+      <c r="F35" s="3">
         <v>-9200</v>
       </c>
-      <c r="E35" s="3">
+      <c r="G35" s="3">
         <v>12000</v>
       </c>
-      <c r="F35" s="3">
-        <v>-22000</v>
-      </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
+        <v>-20300</v>
+      </c>
+      <c r="I35" s="3">
         <v>10300</v>
       </c>
-      <c r="H35" s="3">
+      <c r="J35" s="3">
         <v>-7600</v>
       </c>
-      <c r="I35" s="3">
+      <c r="K35" s="3">
         <v>7500</v>
       </c>
-      <c r="J35" s="3">
+      <c r="L35" s="3">
         <v>2300</v>
       </c>
-      <c r="K35" s="3">
+      <c r="M35" s="3">
         <v>-15500</v>
       </c>
-      <c r="L35" s="3">
+      <c r="N35" s="3">
         <v>-10500</v>
       </c>
-      <c r="M35" s="3">
+      <c r="O35" s="3">
         <v>-6400</v>
       </c>
-      <c r="N35" s="3">
+      <c r="P35" s="3">
         <v>-2500</v>
       </c>
-      <c r="O35" s="3">
+      <c r="Q35" s="3">
         <v>2900</v>
       </c>
-      <c r="P35" s="3">
+      <c r="R35" s="3">
         <v>-1500</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="S35" s="3">
         <v>-1700</v>
       </c>
-      <c r="R35" s="3">
+      <c r="T35" s="3">
         <v>-2100</v>
       </c>
     </row>
-    <row r="37" spans="2:18" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:20" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:18" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45382</v>
+      </c>
+      <c r="E38" s="2">
+        <v>45291</v>
+      </c>
+      <c r="F38" s="2">
         <v>45199</v>
       </c>
-      <c r="E38" s="2">
+      <c r="G38" s="2">
         <v>45107</v>
       </c>
-      <c r="F38" s="2">
+      <c r="H38" s="2">
         <v>45016</v>
       </c>
-      <c r="G38" s="2">
+      <c r="I38" s="2">
         <v>44926</v>
       </c>
-      <c r="H38" s="2">
+      <c r="J38" s="2">
         <v>44834</v>
       </c>
-      <c r="I38" s="2">
+      <c r="K38" s="2">
         <v>44742</v>
       </c>
-      <c r="J38" s="2">
+      <c r="L38" s="2">
         <v>44651</v>
       </c>
-      <c r="K38" s="2">
+      <c r="M38" s="2">
         <v>44561</v>
       </c>
-      <c r="L38" s="2">
+      <c r="N38" s="2">
         <v>44469</v>
       </c>
-      <c r="M38" s="2">
+      <c r="O38" s="2">
         <v>44377</v>
       </c>
-      <c r="N38" s="2">
+      <c r="P38" s="2">
         <v>44286</v>
       </c>
-      <c r="O38" s="2">
+      <c r="Q38" s="2">
         <v>44196</v>
       </c>
-      <c r="P38" s="2">
+      <c r="R38" s="2">
         <v>44104</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="S38" s="2">
         <v>44012</v>
       </c>
-      <c r="R38" s="2">
+      <c r="T38" s="2">
         <v>43921</v>
       </c>
     </row>
-    <row r="39" spans="2:18" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2118,8 +2287,10 @@
       <c r="P39" s="3"/>
       <c r="Q39" s="3"/>
       <c r="R39" s="3"/>
-    </row>
-    <row r="40" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S39" s="3"/>
+      <c r="T39" s="3"/>
+    </row>
+    <row r="40" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2138,158 +2309,178 @@
       <c r="P40" s="3"/>
       <c r="Q40" s="3"/>
       <c r="R40" s="3"/>
-    </row>
-    <row r="41" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S40" s="3"/>
+      <c r="T40" s="3"/>
+    </row>
+    <row r="41" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>5600</v>
+      </c>
+      <c r="E41" s="3">
+        <v>7600</v>
+      </c>
+      <c r="F41" s="3">
         <v>15100</v>
       </c>
-      <c r="E41" s="3">
+      <c r="G41" s="3">
         <v>6200</v>
       </c>
-      <c r="F41" s="3">
+      <c r="H41" s="3">
         <v>11200</v>
       </c>
-      <c r="G41" s="3">
+      <c r="I41" s="3">
         <v>8000</v>
       </c>
-      <c r="H41" s="3">
+      <c r="J41" s="3">
         <v>18900</v>
       </c>
-      <c r="I41" s="3">
+      <c r="K41" s="3">
         <v>40700</v>
       </c>
-      <c r="J41" s="3">
+      <c r="L41" s="3">
         <v>51900</v>
       </c>
-      <c r="K41" s="3">
+      <c r="M41" s="3">
         <v>58600</v>
       </c>
-      <c r="L41" s="3">
+      <c r="N41" s="3">
         <v>61200</v>
       </c>
-      <c r="M41" s="3">
+      <c r="O41" s="3">
         <v>11500</v>
       </c>
-      <c r="N41" s="3">
+      <c r="P41" s="3">
         <v>16000</v>
       </c>
-      <c r="O41" s="3">
+      <c r="Q41" s="3">
         <v>4200</v>
       </c>
-      <c r="P41" s="3">
+      <c r="R41" s="3">
         <v>4700</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="S41" s="3">
         <v>3600</v>
       </c>
-      <c r="R41" s="3">
+      <c r="T41" s="3">
         <v>4600</v>
       </c>
     </row>
-    <row r="42" spans="2:18" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>800</v>
+      </c>
+      <c r="E42" s="3">
         <v>600</v>
       </c>
-      <c r="E42" s="3">
+      <c r="F42" s="3">
+        <v>600</v>
+      </c>
+      <c r="G42" s="3">
         <v>1200</v>
       </c>
-      <c r="F42" s="3">
+      <c r="H42" s="3">
         <v>1700</v>
       </c>
-      <c r="G42" s="3">
+      <c r="I42" s="3">
         <v>400</v>
       </c>
-      <c r="H42" s="3">
+      <c r="J42" s="3">
         <v>700</v>
       </c>
-      <c r="I42" s="3">
+      <c r="K42" s="3">
         <v>1100</v>
       </c>
-      <c r="J42" s="3">
+      <c r="L42" s="3">
         <v>2100</v>
       </c>
-      <c r="K42" s="3">
+      <c r="M42" s="3">
         <v>1800</v>
       </c>
-      <c r="L42" s="3">
+      <c r="N42" s="3">
         <v>2300</v>
       </c>
-      <c r="M42" s="3">
+      <c r="O42" s="3">
         <v>2300</v>
       </c>
-      <c r="N42" s="3">
+      <c r="P42" s="3">
         <v>3500</v>
       </c>
-      <c r="O42" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="P42" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="Q42" s="3" t="s">
         <v>4</v>
       </c>
       <c r="R42" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="43" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S42" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="T42" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="43" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>600</v>
+      </c>
+      <c r="E43" s="3">
+        <v>1100</v>
+      </c>
+      <c r="F43" s="3">
         <v>1000</v>
       </c>
-      <c r="E43" s="3">
+      <c r="G43" s="3">
         <v>800</v>
       </c>
-      <c r="F43" s="3">
+      <c r="H43" s="3">
         <v>1300</v>
       </c>
-      <c r="G43" s="3">
+      <c r="I43" s="3">
         <v>3100</v>
       </c>
-      <c r="H43" s="3">
+      <c r="J43" s="3">
         <v>3500</v>
       </c>
-      <c r="I43" s="3">
+      <c r="K43" s="3">
         <v>1700</v>
       </c>
-      <c r="J43" s="3">
+      <c r="L43" s="3">
         <v>1300</v>
       </c>
-      <c r="K43" s="3">
+      <c r="M43" s="3">
         <v>1000</v>
       </c>
-      <c r="L43" s="3">
+      <c r="N43" s="3">
         <v>1100</v>
       </c>
-      <c r="M43" s="3">
+      <c r="O43" s="3">
         <v>600</v>
       </c>
-      <c r="N43" s="3">
+      <c r="P43" s="3">
         <v>400</v>
       </c>
-      <c r="O43" s="3">
+      <c r="Q43" s="3">
         <v>200</v>
       </c>
-      <c r="P43" s="3">
+      <c r="R43" s="3">
         <v>200</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="S43" s="3">
         <v>100</v>
       </c>
-      <c r="R43" s="3">
+      <c r="T43" s="3">
         <v>400</v>
       </c>
     </row>
-    <row r="44" spans="2:18" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -2338,108 +2529,126 @@
       <c r="R44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S44" s="3">
+        <v>0</v>
+      </c>
+      <c r="T44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>1900</v>
+      </c>
+      <c r="E45" s="3">
+        <v>1400</v>
+      </c>
+      <c r="F45" s="3">
         <v>700</v>
       </c>
-      <c r="E45" s="3">
+      <c r="G45" s="3">
         <v>400</v>
       </c>
-      <c r="F45" s="3">
+      <c r="H45" s="3">
         <v>400</v>
-      </c>
-      <c r="G45" s="3">
-        <v>2100</v>
-      </c>
-      <c r="H45" s="3">
-        <v>2500</v>
       </c>
       <c r="I45" s="3">
         <v>2100</v>
       </c>
       <c r="J45" s="3">
+        <v>2500</v>
+      </c>
+      <c r="K45" s="3">
+        <v>2100</v>
+      </c>
+      <c r="L45" s="3">
         <v>1300</v>
       </c>
-      <c r="K45" s="3">
+      <c r="M45" s="3">
         <v>600</v>
       </c>
-      <c r="L45" s="3">
+      <c r="N45" s="3">
         <v>400</v>
       </c>
-      <c r="M45" s="3">
+      <c r="O45" s="3">
         <v>1000</v>
       </c>
-      <c r="N45" s="3">
+      <c r="P45" s="3">
         <v>900</v>
       </c>
-      <c r="O45" s="3">
+      <c r="Q45" s="3">
         <v>6100</v>
-      </c>
-      <c r="P45" s="3">
-        <v>600</v>
-      </c>
-      <c r="Q45" s="3">
-        <v>400</v>
       </c>
       <c r="R45" s="3">
         <v>600</v>
       </c>
-    </row>
-    <row r="46" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S45" s="3">
+        <v>400</v>
+      </c>
+      <c r="T45" s="3">
+        <v>600</v>
+      </c>
+    </row>
+    <row r="46" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>8900</v>
+      </c>
+      <c r="E46" s="3">
+        <v>10600</v>
+      </c>
+      <c r="F46" s="3">
         <v>17400</v>
       </c>
-      <c r="E46" s="3">
+      <c r="G46" s="3">
         <v>8600</v>
       </c>
-      <c r="F46" s="3">
+      <c r="H46" s="3">
         <v>14500</v>
       </c>
-      <c r="G46" s="3">
+      <c r="I46" s="3">
         <v>13500</v>
       </c>
-      <c r="H46" s="3">
+      <c r="J46" s="3">
         <v>25700</v>
       </c>
-      <c r="I46" s="3">
+      <c r="K46" s="3">
         <v>45600</v>
       </c>
-      <c r="J46" s="3">
+      <c r="L46" s="3">
         <v>56600</v>
       </c>
-      <c r="K46" s="3">
+      <c r="M46" s="3">
         <v>61900</v>
       </c>
-      <c r="L46" s="3">
+      <c r="N46" s="3">
         <v>64900</v>
       </c>
-      <c r="M46" s="3">
+      <c r="O46" s="3">
         <v>15300</v>
       </c>
-      <c r="N46" s="3">
+      <c r="P46" s="3">
         <v>20700</v>
       </c>
-      <c r="O46" s="3">
+      <c r="Q46" s="3">
         <v>10500</v>
       </c>
-      <c r="P46" s="3">
+      <c r="R46" s="3">
         <v>5500</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="S46" s="3">
         <v>4100</v>
       </c>
-      <c r="R46" s="3">
+      <c r="T46" s="3">
         <v>5600</v>
       </c>
     </row>
-    <row r="47" spans="2:18" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -2488,46 +2697,52 @@
       <c r="R47" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S47" s="3">
+        <v>0</v>
+      </c>
+      <c r="T47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>139300</v>
+      </c>
+      <c r="E48" s="3">
+        <v>136900</v>
+      </c>
+      <c r="F48" s="3">
         <v>192900</v>
       </c>
-      <c r="E48" s="3">
+      <c r="G48" s="3">
         <v>190400</v>
       </c>
-      <c r="F48" s="3">
+      <c r="H48" s="3">
         <v>183300</v>
       </c>
-      <c r="G48" s="3">
+      <c r="I48" s="3">
         <v>173100</v>
       </c>
-      <c r="H48" s="3">
+      <c r="J48" s="3">
         <v>144300</v>
       </c>
-      <c r="I48" s="3">
+      <c r="K48" s="3">
         <v>129800</v>
       </c>
-      <c r="J48" s="3">
+      <c r="L48" s="3">
         <v>113700</v>
       </c>
-      <c r="K48" s="3">
+      <c r="M48" s="3">
         <v>104700</v>
       </c>
-      <c r="L48" s="3">
+      <c r="N48" s="3">
         <v>95000</v>
       </c>
-      <c r="M48" s="3">
+      <c r="O48" s="3">
         <v>93900</v>
-      </c>
-      <c r="N48" s="3">
-        <v>92300</v>
-      </c>
-      <c r="O48" s="3">
-        <v>92300</v>
       </c>
       <c r="P48" s="3">
         <v>92300</v>
@@ -2538,8 +2753,14 @@
       <c r="R48" s="3">
         <v>92300</v>
       </c>
-    </row>
-    <row r="49" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S48" s="3">
+        <v>92300</v>
+      </c>
+      <c r="T48" s="3">
+        <v>92300</v>
+      </c>
+    </row>
+    <row r="49" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
@@ -2588,8 +2809,14 @@
       <c r="R49" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="50" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S49" s="3">
+        <v>0</v>
+      </c>
+      <c r="T49" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2638,8 +2865,14 @@
       <c r="R50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S50" s="3">
+        <v>0</v>
+      </c>
+      <c r="T50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -2688,22 +2921,28 @@
       <c r="R51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S51" s="3">
+        <v>0</v>
+      </c>
+      <c r="T51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
-        <v>0</v>
+        <v>1200</v>
       </c>
       <c r="E52" s="3">
-        <v>0</v>
+        <v>1200</v>
       </c>
       <c r="F52" s="3">
-        <v>900</v>
+        <v>0</v>
       </c>
       <c r="G52" s="3">
-        <v>900</v>
+        <v>0</v>
       </c>
       <c r="H52" s="3">
         <v>900</v>
@@ -2738,8 +2977,14 @@
       <c r="R52" s="3">
         <v>900</v>
       </c>
-    </row>
-    <row r="53" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S52" s="3">
+        <v>900</v>
+      </c>
+      <c r="T52" s="3">
+        <v>900</v>
+      </c>
+    </row>
+    <row r="53" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -2788,58 +3033,70 @@
       <c r="R53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S53" s="3">
+        <v>0</v>
+      </c>
+      <c r="T53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>149300</v>
+      </c>
+      <c r="E54" s="3">
+        <v>148700</v>
+      </c>
+      <c r="F54" s="3">
         <v>210300</v>
       </c>
-      <c r="E54" s="3">
+      <c r="G54" s="3">
         <v>199000</v>
       </c>
-      <c r="F54" s="3">
+      <c r="H54" s="3">
         <v>198800</v>
       </c>
-      <c r="G54" s="3">
+      <c r="I54" s="3">
         <v>187500</v>
       </c>
-      <c r="H54" s="3">
+      <c r="J54" s="3">
         <v>170900</v>
       </c>
-      <c r="I54" s="3">
+      <c r="K54" s="3">
         <v>176400</v>
       </c>
-      <c r="J54" s="3">
+      <c r="L54" s="3">
         <v>171300</v>
       </c>
-      <c r="K54" s="3">
+      <c r="M54" s="3">
         <v>167600</v>
       </c>
-      <c r="L54" s="3">
+      <c r="N54" s="3">
         <v>160800</v>
       </c>
-      <c r="M54" s="3">
+      <c r="O54" s="3">
         <v>110100</v>
       </c>
-      <c r="N54" s="3">
+      <c r="P54" s="3">
         <v>114000</v>
       </c>
-      <c r="O54" s="3">
+      <c r="Q54" s="3">
         <v>103700</v>
       </c>
-      <c r="P54" s="3">
+      <c r="R54" s="3">
         <v>98700</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="S54" s="3">
         <v>97300</v>
       </c>
-      <c r="R54" s="3">
+      <c r="T54" s="3">
         <v>98800</v>
       </c>
     </row>
-    <row r="55" spans="3:18" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -2858,8 +3115,10 @@
       <c r="P55" s="3"/>
       <c r="Q55" s="3"/>
       <c r="R55" s="3"/>
-    </row>
-    <row r="56" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S55" s="3"/>
+      <c r="T55" s="3"/>
+    </row>
+    <row r="56" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -2878,79 +3137,87 @@
       <c r="P56" s="3"/>
       <c r="Q56" s="3"/>
       <c r="R56" s="3"/>
-    </row>
-    <row r="57" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S56" s="3"/>
+      <c r="T56" s="3"/>
+    </row>
+    <row r="57" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>7700</v>
+      </c>
+      <c r="E57" s="3">
+        <v>8800</v>
+      </c>
+      <c r="F57" s="3">
         <v>9600</v>
       </c>
-      <c r="E57" s="3">
+      <c r="G57" s="3">
         <v>17100</v>
       </c>
-      <c r="F57" s="3">
+      <c r="H57" s="3">
         <v>15300</v>
       </c>
-      <c r="G57" s="3">
+      <c r="I57" s="3">
         <v>18900</v>
       </c>
-      <c r="H57" s="3">
+      <c r="J57" s="3">
         <v>8200</v>
       </c>
-      <c r="I57" s="3">
+      <c r="K57" s="3">
         <v>9900</v>
       </c>
-      <c r="J57" s="3">
+      <c r="L57" s="3">
         <v>5600</v>
       </c>
-      <c r="K57" s="3">
+      <c r="M57" s="3">
         <v>3500</v>
       </c>
-      <c r="L57" s="3">
+      <c r="N57" s="3">
         <v>2000</v>
       </c>
-      <c r="M57" s="3">
-        <v>0</v>
-      </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
+        <v>0</v>
+      </c>
+      <c r="P57" s="3">
         <v>200</v>
       </c>
-      <c r="O57" s="3">
+      <c r="Q57" s="3">
         <v>400</v>
       </c>
-      <c r="P57" s="3">
-        <v>0</v>
-      </c>
-      <c r="Q57" s="3">
-        <v>0</v>
-      </c>
       <c r="R57" s="3">
+        <v>0</v>
+      </c>
+      <c r="S57" s="3">
+        <v>0</v>
+      </c>
+      <c r="T57" s="3">
         <v>100</v>
       </c>
     </row>
-    <row r="58" spans="3:18" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>47400</v>
+      </c>
+      <c r="E58" s="3">
+        <v>0</v>
+      </c>
+      <c r="F58" s="3">
         <v>55300</v>
       </c>
-      <c r="E58" s="3">
-        <v>5200</v>
-      </c>
-      <c r="F58" s="3">
-        <v>11000</v>
-      </c>
       <c r="G58" s="3">
+        <v>0</v>
+      </c>
+      <c r="H58" s="3">
+        <v>0</v>
+      </c>
+      <c r="I58" s="3">
         <v>25700</v>
       </c>
-      <c r="H58" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="I58" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="J58" s="3" t="s">
         <v>4</v>
       </c>
@@ -2960,226 +3227,256 @@
       <c r="L58" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="M58" s="3">
-        <v>0</v>
-      </c>
-      <c r="N58" s="3">
-        <v>0</v>
-      </c>
-      <c r="O58" s="3" t="s">
-        <v>4</v>
+      <c r="M58" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="N58" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="O58" s="3">
+        <v>0</v>
       </c>
       <c r="P58" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q58" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="R58" s="3">
         <v>7000</v>
       </c>
-      <c r="Q58" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="R58" s="3" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="59" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S58" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="T58" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="59" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>8400</v>
+      </c>
+      <c r="E59" s="3">
+        <v>7200</v>
+      </c>
+      <c r="F59" s="3">
         <v>8000</v>
       </c>
-      <c r="E59" s="3">
-        <v>2700</v>
-      </c>
-      <c r="F59" s="3">
-        <v>2300</v>
-      </c>
       <c r="G59" s="3">
+        <v>7900</v>
+      </c>
+      <c r="H59" s="3">
+        <v>13300</v>
+      </c>
+      <c r="I59" s="3">
         <v>9600</v>
       </c>
-      <c r="H59" s="3">
+      <c r="J59" s="3">
         <v>400</v>
-      </c>
-      <c r="I59" s="3">
-        <v>1200</v>
-      </c>
-      <c r="J59" s="3">
-        <v>500</v>
       </c>
       <c r="K59" s="3">
         <v>1200</v>
       </c>
       <c r="L59" s="3">
+        <v>500</v>
+      </c>
+      <c r="M59" s="3">
+        <v>1200</v>
+      </c>
+      <c r="N59" s="3">
         <v>100</v>
       </c>
-      <c r="M59" s="3">
+      <c r="O59" s="3">
         <v>600</v>
       </c>
-      <c r="N59" s="3">
+      <c r="P59" s="3">
         <v>400</v>
       </c>
-      <c r="O59" s="3">
+      <c r="Q59" s="3">
         <v>2400</v>
       </c>
-      <c r="P59" s="3">
+      <c r="R59" s="3">
         <v>1000</v>
       </c>
-      <c r="Q59" s="3">
-        <v>0</v>
-      </c>
-      <c r="R59" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="60" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S59" s="3">
+        <v>0</v>
+      </c>
+      <c r="T59" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="60" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>63500</v>
+      </c>
+      <c r="E60" s="3">
+        <v>16000</v>
+      </c>
+      <c r="F60" s="3">
         <v>72900</v>
       </c>
-      <c r="E60" s="3">
+      <c r="G60" s="3">
         <v>25000</v>
       </c>
-      <c r="F60" s="3">
+      <c r="H60" s="3">
         <v>28600</v>
       </c>
-      <c r="G60" s="3">
+      <c r="I60" s="3">
         <v>54100</v>
       </c>
-      <c r="H60" s="3">
+      <c r="J60" s="3">
         <v>8700</v>
       </c>
-      <c r="I60" s="3">
+      <c r="K60" s="3">
         <v>11100</v>
       </c>
-      <c r="J60" s="3">
+      <c r="L60" s="3">
         <v>6000</v>
       </c>
-      <c r="K60" s="3">
+      <c r="M60" s="3">
         <v>4700</v>
       </c>
-      <c r="L60" s="3">
+      <c r="N60" s="3">
         <v>2100</v>
       </c>
-      <c r="M60" s="3">
+      <c r="O60" s="3">
         <v>600</v>
       </c>
-      <c r="N60" s="3">
+      <c r="P60" s="3">
         <v>500</v>
       </c>
-      <c r="O60" s="3">
+      <c r="Q60" s="3">
         <v>2800</v>
       </c>
-      <c r="P60" s="3">
+      <c r="R60" s="3">
         <v>8000</v>
       </c>
-      <c r="Q60" s="3">
-        <v>0</v>
-      </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
+        <v>0</v>
+      </c>
+      <c r="T60" s="3">
         <v>100</v>
       </c>
     </row>
-    <row r="61" spans="3:18" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>8600</v>
+      </c>
+      <c r="E61" s="3">
+        <v>46300</v>
+      </c>
+      <c r="F61" s="3">
         <v>4600</v>
       </c>
-      <c r="E61" s="3">
+      <c r="G61" s="3">
         <v>53000</v>
       </c>
-      <c r="F61" s="3">
+      <c r="H61" s="3">
         <v>62000</v>
       </c>
-      <c r="G61" s="3">
+      <c r="I61" s="3">
         <v>5100</v>
       </c>
-      <c r="H61" s="3">
+      <c r="J61" s="3">
         <v>30000</v>
       </c>
-      <c r="I61" s="3">
+      <c r="K61" s="3">
         <v>27600</v>
       </c>
-      <c r="J61" s="3">
+      <c r="L61" s="3">
         <v>26200</v>
       </c>
-      <c r="K61" s="3">
+      <c r="M61" s="3">
         <v>23600</v>
       </c>
-      <c r="L61" s="3">
+      <c r="N61" s="3">
         <v>22400</v>
       </c>
-      <c r="M61" s="3">
-        <v>0</v>
-      </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
+        <v>0</v>
+      </c>
+      <c r="P61" s="3">
         <v>6700</v>
       </c>
-      <c r="O61" s="3">
+      <c r="Q61" s="3">
         <v>6700</v>
       </c>
-      <c r="P61" s="3">
-        <v>0</v>
-      </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
+        <v>0</v>
+      </c>
+      <c r="S61" s="3">
         <v>7000</v>
       </c>
-      <c r="R61" s="3">
+      <c r="T61" s="3">
         <v>7000</v>
       </c>
     </row>
-    <row r="62" spans="3:18" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
-        <v>1700</v>
+        <v>2900</v>
       </c>
       <c r="E62" s="3">
-        <v>1900</v>
+        <v>3100</v>
       </c>
       <c r="F62" s="3">
         <v>1700</v>
       </c>
       <c r="G62" s="3">
+        <v>1900</v>
+      </c>
+      <c r="H62" s="3">
+        <v>1700</v>
+      </c>
+      <c r="I62" s="3">
         <v>1800</v>
       </c>
-      <c r="H62" s="3">
+      <c r="J62" s="3">
         <v>20100</v>
       </c>
-      <c r="I62" s="3">
+      <c r="K62" s="3">
         <v>19500</v>
       </c>
-      <c r="J62" s="3">
+      <c r="L62" s="3">
         <v>34900</v>
       </c>
-      <c r="K62" s="3">
+      <c r="M62" s="3">
         <v>39400</v>
       </c>
-      <c r="L62" s="3">
+      <c r="N62" s="3">
         <v>29300</v>
       </c>
-      <c r="M62" s="3">
+      <c r="O62" s="3">
         <v>1300</v>
       </c>
-      <c r="N62" s="3">
+      <c r="P62" s="3">
         <v>2000</v>
       </c>
-      <c r="O62" s="3">
+      <c r="Q62" s="3">
         <v>2000</v>
       </c>
-      <c r="P62" s="3">
+      <c r="R62" s="3">
         <v>2700</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="S62" s="3">
         <v>3200</v>
       </c>
-      <c r="R62" s="3">
+      <c r="T62" s="3">
         <v>3000</v>
       </c>
     </row>
-    <row r="63" spans="3:18" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -3228,8 +3525,14 @@
       <c r="R63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S63" s="3">
+        <v>0</v>
+      </c>
+      <c r="T63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -3278,8 +3581,14 @@
       <c r="R64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S64" s="3">
+        <v>0</v>
+      </c>
+      <c r="T64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -3328,58 +3637,70 @@
       <c r="R65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S65" s="3">
+        <v>0</v>
+      </c>
+      <c r="T65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>74900</v>
+      </c>
+      <c r="E66" s="3">
+        <v>65400</v>
+      </c>
+      <c r="F66" s="3">
         <v>79200</v>
       </c>
-      <c r="E66" s="3">
+      <c r="G66" s="3">
         <v>79800</v>
       </c>
-      <c r="F66" s="3">
+      <c r="H66" s="3">
         <v>92300</v>
       </c>
-      <c r="G66" s="3">
+      <c r="I66" s="3">
         <v>61000</v>
       </c>
-      <c r="H66" s="3">
+      <c r="J66" s="3">
         <v>58800</v>
       </c>
-      <c r="I66" s="3">
+      <c r="K66" s="3">
         <v>58200</v>
       </c>
-      <c r="J66" s="3">
+      <c r="L66" s="3">
         <v>67100</v>
       </c>
-      <c r="K66" s="3">
+      <c r="M66" s="3">
         <v>67600</v>
       </c>
-      <c r="L66" s="3">
+      <c r="N66" s="3">
         <v>53900</v>
       </c>
-      <c r="M66" s="3">
+      <c r="O66" s="3">
         <v>1900</v>
       </c>
-      <c r="N66" s="3">
+      <c r="P66" s="3">
         <v>9300</v>
       </c>
-      <c r="O66" s="3">
+      <c r="Q66" s="3">
         <v>11500</v>
       </c>
-      <c r="P66" s="3">
+      <c r="R66" s="3">
         <v>10700</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="S66" s="3">
         <v>10200</v>
       </c>
-      <c r="R66" s="3">
+      <c r="T66" s="3">
         <v>10100</v>
       </c>
     </row>
-    <row r="67" spans="2:18" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -3398,8 +3719,10 @@
       <c r="P67" s="3"/>
       <c r="Q67" s="3"/>
       <c r="R67" s="3"/>
-    </row>
-    <row r="68" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S67" s="3"/>
+      <c r="T67" s="3"/>
+    </row>
+    <row r="68" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -3448,8 +3771,14 @@
       <c r="R68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S68" s="3">
+        <v>0</v>
+      </c>
+      <c r="T68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -3498,8 +3827,14 @@
       <c r="R69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S69" s="3">
+        <v>0</v>
+      </c>
+      <c r="T69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -3548,8 +3883,14 @@
       <c r="R70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S70" s="3">
+        <v>0</v>
+      </c>
+      <c r="T70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -3598,58 +3939,70 @@
       <c r="R71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S71" s="3">
+        <v>0</v>
+      </c>
+      <c r="T71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-232400</v>
+      </c>
+      <c r="E72" s="3">
+        <v>-219900</v>
+      </c>
+      <c r="F72" s="3">
         <v>-173000</v>
       </c>
-      <c r="E72" s="3">
+      <c r="G72" s="3">
         <v>-171400</v>
       </c>
-      <c r="F72" s="3">
+      <c r="H72" s="3">
         <v>-183600</v>
       </c>
-      <c r="G72" s="3">
+      <c r="I72" s="3">
         <v>-162900</v>
       </c>
-      <c r="H72" s="3">
+      <c r="J72" s="3">
         <v>-173900</v>
       </c>
-      <c r="I72" s="3">
+      <c r="K72" s="3">
         <v>-166600</v>
       </c>
-      <c r="J72" s="3">
+      <c r="L72" s="3">
         <v>-174000</v>
       </c>
-      <c r="K72" s="3">
+      <c r="M72" s="3">
         <v>-176800</v>
       </c>
-      <c r="L72" s="3">
+      <c r="N72" s="3">
         <v>-161500</v>
       </c>
-      <c r="M72" s="3">
+      <c r="O72" s="3">
         <v>-151200</v>
       </c>
-      <c r="N72" s="3">
+      <c r="P72" s="3">
         <v>-145000</v>
       </c>
-      <c r="O72" s="3">
+      <c r="Q72" s="3">
         <v>-143000</v>
       </c>
-      <c r="P72" s="3">
+      <c r="R72" s="3">
         <v>-145900</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="S72" s="3">
         <v>-145200</v>
       </c>
-      <c r="R72" s="3">
+      <c r="T72" s="3">
         <v>-143600</v>
       </c>
     </row>
-    <row r="73" spans="2:18" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -3698,8 +4051,14 @@
       <c r="R73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S73" s="3">
+        <v>0</v>
+      </c>
+      <c r="T73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -3748,8 +4107,14 @@
       <c r="R74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S74" s="3">
+        <v>0</v>
+      </c>
+      <c r="T74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -3798,58 +4163,70 @@
       <c r="R75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S75" s="3">
+        <v>0</v>
+      </c>
+      <c r="T75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>74500</v>
+      </c>
+      <c r="E76" s="3">
+        <v>83300</v>
+      </c>
+      <c r="F76" s="3">
         <v>131100</v>
       </c>
-      <c r="E76" s="3">
+      <c r="G76" s="3">
         <v>119100</v>
       </c>
-      <c r="F76" s="3">
+      <c r="H76" s="3">
         <v>106500</v>
       </c>
-      <c r="G76" s="3">
+      <c r="I76" s="3">
         <v>126500</v>
       </c>
-      <c r="H76" s="3">
+      <c r="J76" s="3">
         <v>112100</v>
       </c>
-      <c r="I76" s="3">
+      <c r="K76" s="3">
         <v>118200</v>
       </c>
-      <c r="J76" s="3">
+      <c r="L76" s="3">
         <v>104200</v>
       </c>
-      <c r="K76" s="3">
+      <c r="M76" s="3">
         <v>100000</v>
       </c>
-      <c r="L76" s="3">
+      <c r="N76" s="3">
         <v>107000</v>
       </c>
-      <c r="M76" s="3">
+      <c r="O76" s="3">
         <v>108200</v>
       </c>
-      <c r="N76" s="3">
+      <c r="P76" s="3">
         <v>104700</v>
       </c>
-      <c r="O76" s="3">
+      <c r="Q76" s="3">
         <v>92200</v>
       </c>
-      <c r="P76" s="3">
+      <c r="R76" s="3">
         <v>88000</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="S76" s="3">
         <v>87200</v>
       </c>
-      <c r="R76" s="3">
+      <c r="T76" s="3">
         <v>88700</v>
       </c>
     </row>
-    <row r="77" spans="2:18" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -3898,113 +4275,131 @@
       <c r="R77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S77" s="3">
+        <v>0</v>
+      </c>
+      <c r="T77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:20" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:18" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45382</v>
+      </c>
+      <c r="E80" s="2">
+        <v>45291</v>
+      </c>
+      <c r="F80" s="2">
         <v>45199</v>
       </c>
-      <c r="E80" s="2">
+      <c r="G80" s="2">
         <v>45107</v>
       </c>
-      <c r="F80" s="2">
+      <c r="H80" s="2">
         <v>45016</v>
       </c>
-      <c r="G80" s="2">
+      <c r="I80" s="2">
         <v>44926</v>
       </c>
-      <c r="H80" s="2">
+      <c r="J80" s="2">
         <v>44834</v>
       </c>
-      <c r="I80" s="2">
+      <c r="K80" s="2">
         <v>44742</v>
       </c>
-      <c r="J80" s="2">
+      <c r="L80" s="2">
         <v>44651</v>
       </c>
-      <c r="K80" s="2">
+      <c r="M80" s="2">
         <v>44561</v>
       </c>
-      <c r="L80" s="2">
+      <c r="N80" s="2">
         <v>44469</v>
       </c>
-      <c r="M80" s="2">
+      <c r="O80" s="2">
         <v>44377</v>
       </c>
-      <c r="N80" s="2">
+      <c r="P80" s="2">
         <v>44286</v>
       </c>
-      <c r="O80" s="2">
+      <c r="Q80" s="2">
         <v>44196</v>
       </c>
-      <c r="P80" s="2">
+      <c r="R80" s="2">
         <v>44104</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="S80" s="2">
         <v>44012</v>
       </c>
-      <c r="R80" s="2">
+      <c r="T80" s="2">
         <v>43921</v>
       </c>
     </row>
-    <row r="81" spans="3:18" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-12200</v>
+      </c>
+      <c r="E81" s="3">
+        <v>-45500</v>
+      </c>
+      <c r="F81" s="3">
         <v>-9200</v>
       </c>
-      <c r="E81" s="3">
+      <c r="G81" s="3">
         <v>12000</v>
       </c>
-      <c r="F81" s="3">
-        <v>-22000</v>
-      </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
+        <v>-20300</v>
+      </c>
+      <c r="I81" s="3">
         <v>10300</v>
       </c>
-      <c r="H81" s="3">
+      <c r="J81" s="3">
         <v>-7600</v>
       </c>
-      <c r="I81" s="3">
+      <c r="K81" s="3">
         <v>7500</v>
       </c>
-      <c r="J81" s="3">
+      <c r="L81" s="3">
         <v>2300</v>
       </c>
-      <c r="K81" s="3">
+      <c r="M81" s="3">
         <v>-15500</v>
       </c>
-      <c r="L81" s="3">
+      <c r="N81" s="3">
         <v>-10500</v>
       </c>
-      <c r="M81" s="3">
+      <c r="O81" s="3">
         <v>-6400</v>
       </c>
-      <c r="N81" s="3">
+      <c r="P81" s="3">
         <v>-2500</v>
       </c>
-      <c r="O81" s="3">
+      <c r="Q81" s="3">
         <v>2900</v>
       </c>
-      <c r="P81" s="3">
+      <c r="R81" s="3">
         <v>-1500</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="S81" s="3">
         <v>-1700</v>
       </c>
-      <c r="R81" s="3">
+      <c r="T81" s="3">
         <v>-2100</v>
       </c>
     </row>
-    <row r="82" spans="3:18" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -4023,8 +4418,10 @@
       <c r="P82" s="3"/>
       <c r="Q82" s="3"/>
       <c r="R82" s="3"/>
-    </row>
-    <row r="83" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S82" s="3"/>
+      <c r="T82" s="3"/>
+    </row>
+    <row r="83" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
@@ -4037,26 +4434,26 @@
       <c r="F83" s="3">
         <v>0</v>
       </c>
-      <c r="G83" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="H83" s="3" t="s">
-        <v>4</v>
+      <c r="G83" s="3">
+        <v>0</v>
+      </c>
+      <c r="H83" s="3">
+        <v>0</v>
       </c>
       <c r="I83" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="J83" s="3">
-        <v>0</v>
-      </c>
-      <c r="K83" s="3">
-        <v>0</v>
-      </c>
-      <c r="L83" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="M83" s="3" t="s">
-        <v>4</v>
+      <c r="J83" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="K83" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="L83" s="3">
+        <v>0</v>
+      </c>
+      <c r="M83" s="3">
+        <v>0</v>
       </c>
       <c r="N83" s="3" t="s">
         <v>4</v>
@@ -4073,8 +4470,14 @@
       <c r="R83" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="84" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S83" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="T83" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="84" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -4123,8 +4526,14 @@
       <c r="R84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S84" s="3">
+        <v>0</v>
+      </c>
+      <c r="T84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -4173,8 +4582,14 @@
       <c r="R85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S85" s="3">
+        <v>0</v>
+      </c>
+      <c r="T85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -4223,8 +4638,14 @@
       <c r="R86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S86" s="3">
+        <v>0</v>
+      </c>
+      <c r="T86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -4273,8 +4694,14 @@
       <c r="R87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S87" s="3">
+        <v>0</v>
+      </c>
+      <c r="T87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -4323,58 +4750,70 @@
       <c r="R88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S88" s="3">
+        <v>0</v>
+      </c>
+      <c r="T88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>-4100</v>
+      </c>
+      <c r="E89" s="3">
+        <v>-6000</v>
+      </c>
+      <c r="F89" s="3">
         <v>-12000</v>
       </c>
-      <c r="E89" s="3">
+      <c r="G89" s="3">
         <v>-4000</v>
       </c>
-      <c r="F89" s="3">
+      <c r="H89" s="3">
         <v>-1000</v>
       </c>
-      <c r="G89" s="3">
+      <c r="I89" s="3">
         <v>-6600</v>
       </c>
-      <c r="H89" s="3">
+      <c r="J89" s="3">
         <v>-500</v>
       </c>
-      <c r="I89" s="3">
+      <c r="K89" s="3">
         <v>-5300</v>
       </c>
-      <c r="J89" s="3">
+      <c r="L89" s="3">
         <v>-3500</v>
       </c>
-      <c r="K89" s="3">
+      <c r="M89" s="3">
         <v>-4900</v>
       </c>
-      <c r="L89" s="3">
+      <c r="N89" s="3">
         <v>-5300</v>
       </c>
-      <c r="M89" s="3">
+      <c r="O89" s="3">
         <v>-3600</v>
       </c>
-      <c r="N89" s="3">
+      <c r="P89" s="3">
         <v>-3100</v>
       </c>
-      <c r="O89" s="3">
+      <c r="Q89" s="3">
         <v>-1500</v>
       </c>
-      <c r="P89" s="3">
+      <c r="R89" s="3">
         <v>-1200</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="S89" s="3">
         <v>-1100</v>
       </c>
-      <c r="R89" s="3">
+      <c r="T89" s="3">
         <v>-1800</v>
       </c>
     </row>
-    <row r="90" spans="3:18" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -4393,58 +4832,66 @@
       <c r="P90" s="3"/>
       <c r="Q90" s="3"/>
       <c r="R90" s="3"/>
-    </row>
-    <row r="91" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S90" s="3"/>
+      <c r="T90" s="3"/>
+    </row>
+    <row r="91" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-600</v>
+      </c>
+      <c r="E91" s="3">
         <v>-500</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
+        <v>-500</v>
+      </c>
+      <c r="G91" s="3">
         <v>-2500</v>
       </c>
-      <c r="F91" s="3">
+      <c r="H91" s="3">
         <v>-12300</v>
       </c>
-      <c r="G91" s="3">
+      <c r="I91" s="3">
         <v>-15600</v>
       </c>
-      <c r="H91" s="3">
+      <c r="J91" s="3">
         <v>-18800</v>
       </c>
-      <c r="I91" s="3">
+      <c r="K91" s="3">
         <v>-8700</v>
       </c>
-      <c r="J91" s="3">
+      <c r="L91" s="3">
         <v>-4500</v>
       </c>
-      <c r="K91" s="3">
+      <c r="M91" s="3">
         <v>-6100</v>
       </c>
-      <c r="L91" s="3">
+      <c r="N91" s="3">
         <v>-600</v>
       </c>
-      <c r="M91" s="3">
+      <c r="O91" s="3">
         <v>500</v>
       </c>
-      <c r="N91" s="3">
+      <c r="P91" s="3">
         <v>-500</v>
       </c>
-      <c r="O91" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="P91" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="Q91" s="3" t="s">
         <v>4</v>
       </c>
       <c r="R91" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="92" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S91" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="T91" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="92" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -4493,8 +4940,14 @@
       <c r="R92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S92" s="3">
+        <v>0</v>
+      </c>
+      <c r="T92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -4543,47 +4996,53 @@
       <c r="R93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S93" s="3">
+        <v>0</v>
+      </c>
+      <c r="T93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-100</v>
+      </c>
+      <c r="E94" s="3">
+        <v>-1500</v>
+      </c>
+      <c r="F94" s="3">
         <v>800</v>
       </c>
-      <c r="E94" s="3">
+      <c r="G94" s="3">
         <v>-1000</v>
       </c>
-      <c r="F94" s="3">
+      <c r="H94" s="3">
         <v>-12200</v>
       </c>
-      <c r="G94" s="3">
+      <c r="I94" s="3">
         <v>-10900</v>
       </c>
-      <c r="H94" s="3">
+      <c r="J94" s="3">
         <v>-18800</v>
       </c>
-      <c r="I94" s="3">
+      <c r="K94" s="3">
         <v>-8700</v>
       </c>
-      <c r="J94" s="3">
+      <c r="L94" s="3">
         <v>-5100</v>
       </c>
-      <c r="K94" s="3">
+      <c r="M94" s="3">
         <v>-6100</v>
       </c>
-      <c r="L94" s="3">
+      <c r="N94" s="3">
         <v>-500</v>
       </c>
-      <c r="M94" s="3">
+      <c r="O94" s="3">
         <v>-1500</v>
       </c>
-      <c r="N94" s="3">
-        <v>0</v>
-      </c>
-      <c r="O94" s="3">
-        <v>0</v>
-      </c>
       <c r="P94" s="3">
         <v>0</v>
       </c>
@@ -4593,8 +5052,14 @@
       <c r="R94" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="95" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S94" s="3">
+        <v>0</v>
+      </c>
+      <c r="T94" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="95" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -4613,8 +5078,10 @@
       <c r="P95" s="3"/>
       <c r="Q95" s="3"/>
       <c r="R95" s="3"/>
-    </row>
-    <row r="96" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S95" s="3"/>
+      <c r="T95" s="3"/>
+    </row>
+    <row r="96" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -4663,8 +5130,14 @@
       <c r="R96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S96" s="3">
+        <v>0</v>
+      </c>
+      <c r="T96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -4713,8 +5186,14 @@
       <c r="R97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S97" s="3">
+        <v>0</v>
+      </c>
+      <c r="T97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -4763,8 +5242,14 @@
       <c r="R98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S98" s="3">
+        <v>0</v>
+      </c>
+      <c r="T98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -4813,58 +5298,70 @@
       <c r="R99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S99" s="3">
+        <v>0</v>
+      </c>
+      <c r="T99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>2300</v>
+      </c>
+      <c r="E100" s="3">
+        <v>-100</v>
+      </c>
+      <c r="F100" s="3">
         <v>20100</v>
       </c>
-      <c r="E100" s="3">
-        <v>0</v>
-      </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
+        <v>0</v>
+      </c>
+      <c r="H100" s="3">
         <v>16500</v>
       </c>
-      <c r="G100" s="3">
+      <c r="I100" s="3">
         <v>6500</v>
       </c>
-      <c r="H100" s="3">
+      <c r="J100" s="3">
         <v>-2500</v>
       </c>
-      <c r="I100" s="3">
+      <c r="K100" s="3">
         <v>2900</v>
       </c>
-      <c r="J100" s="3">
+      <c r="L100" s="3">
         <v>1600</v>
       </c>
-      <c r="K100" s="3">
+      <c r="M100" s="3">
         <v>8500</v>
       </c>
-      <c r="L100" s="3">
+      <c r="N100" s="3">
         <v>54900</v>
       </c>
-      <c r="M100" s="3">
+      <c r="O100" s="3">
         <v>600</v>
       </c>
-      <c r="N100" s="3">
+      <c r="P100" s="3">
         <v>14900</v>
       </c>
-      <c r="O100" s="3">
+      <c r="Q100" s="3">
         <v>1100</v>
       </c>
-      <c r="P100" s="3">
+      <c r="R100" s="3">
         <v>2400</v>
       </c>
-      <c r="Q100" s="3">
-        <v>0</v>
-      </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
+        <v>0</v>
+      </c>
+      <c r="T100" s="3">
         <v>2100</v>
       </c>
     </row>
-    <row r="101" spans="3:18" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -4878,7 +5375,7 @@
         <v>0</v>
       </c>
       <c r="G101" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="H101" s="3">
         <v>0</v>
@@ -4887,80 +5384,92 @@
         <v>0</v>
       </c>
       <c r="J101" s="3">
+        <v>0</v>
+      </c>
+      <c r="K101" s="3">
+        <v>0</v>
+      </c>
+      <c r="L101" s="3">
         <v>200</v>
       </c>
-      <c r="K101" s="3">
+      <c r="M101" s="3">
         <v>-100</v>
       </c>
-      <c r="L101" s="3">
+      <c r="N101" s="3">
         <v>600</v>
       </c>
-      <c r="M101" s="3">
-        <v>0</v>
-      </c>
-      <c r="N101" s="3">
-        <v>0</v>
-      </c>
       <c r="O101" s="3">
+        <v>0</v>
+      </c>
+      <c r="P101" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q101" s="3">
         <v>-100</v>
       </c>
-      <c r="P101" s="3">
-        <v>0</v>
-      </c>
-      <c r="Q101" s="3">
-        <v>0</v>
-      </c>
       <c r="R101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S101" s="3">
+        <v>0</v>
+      </c>
+      <c r="T101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-1900</v>
+      </c>
+      <c r="E102" s="3">
+        <v>-7500</v>
+      </c>
+      <c r="F102" s="3">
         <v>8800</v>
       </c>
-      <c r="E102" s="3">
+      <c r="G102" s="3">
         <v>-5000</v>
       </c>
-      <c r="F102" s="3">
+      <c r="H102" s="3">
         <v>3300</v>
       </c>
-      <c r="G102" s="3">
+      <c r="I102" s="3">
         <v>-11000</v>
       </c>
-      <c r="H102" s="3">
+      <c r="J102" s="3">
         <v>-21800</v>
       </c>
-      <c r="I102" s="3">
+      <c r="K102" s="3">
         <v>-11200</v>
       </c>
-      <c r="J102" s="3">
+      <c r="L102" s="3">
         <v>-6700</v>
       </c>
-      <c r="K102" s="3">
+      <c r="M102" s="3">
         <v>-2600</v>
       </c>
-      <c r="L102" s="3">
+      <c r="N102" s="3">
         <v>49700</v>
       </c>
-      <c r="M102" s="3">
+      <c r="O102" s="3">
         <v>-4500</v>
       </c>
-      <c r="N102" s="3">
+      <c r="P102" s="3">
         <v>11800</v>
       </c>
-      <c r="O102" s="3">
+      <c r="Q102" s="3">
         <v>-500</v>
       </c>
-      <c r="P102" s="3">
+      <c r="R102" s="3">
         <v>1100</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="S102" s="3">
         <v>-1100</v>
       </c>
-      <c r="R102" s="3">
+      <c r="T102" s="3">
         <v>200</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/ELBM_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/ELBM_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="183" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="179" uniqueCount="92">
   <si>
     <t>ELBM</t>
   </si>
@@ -656,95 +656,99 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:T102"/>
+  <dimension ref="A5:U102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.42578125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="19" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:21" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:21" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45473</v>
+      </c>
+      <c r="E7" s="2">
         <v>45382</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45291</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45199</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45107</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45016</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>44926</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44834</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44742</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44651</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44561</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44469</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44377</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44286</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44196</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44104</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44012</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>43921</v>
       </c>
     </row>
-    <row r="8" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:21" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
@@ -799,8 +803,11 @@
       <c r="T8" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="9" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="U8" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:21" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
@@ -855,8 +862,11 @@
       <c r="T9" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="10" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="U9" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="10" spans="1:21" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
@@ -911,8 +921,11 @@
       <c r="T10" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="11" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="U10" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="11" spans="1:21" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -933,8 +946,9 @@
       <c r="R11" s="3"/>
       <c r="S11" s="3"/>
       <c r="T11" s="3"/>
-    </row>
-    <row r="12" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="U11" s="3"/>
+    </row>
+    <row r="12" spans="1:21" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -945,52 +959,55 @@
         <v>100</v>
       </c>
       <c r="F12" s="3">
-        <v>300</v>
+        <v>100</v>
       </c>
       <c r="G12" s="3">
         <v>300</v>
       </c>
       <c r="H12" s="3">
+        <v>300</v>
+      </c>
+      <c r="I12" s="3">
         <v>100</v>
       </c>
-      <c r="I12" s="3">
+      <c r="J12" s="3">
         <v>600</v>
       </c>
-      <c r="J12" s="3">
+      <c r="K12" s="3">
         <v>1300</v>
       </c>
-      <c r="K12" s="3">
+      <c r="L12" s="3">
         <v>1100</v>
       </c>
-      <c r="L12" s="3">
+      <c r="M12" s="3">
         <v>400</v>
       </c>
-      <c r="M12" s="3">
+      <c r="N12" s="3">
         <v>2900</v>
       </c>
-      <c r="N12" s="3">
+      <c r="O12" s="3">
         <v>1200</v>
       </c>
-      <c r="O12" s="3">
+      <c r="P12" s="3">
         <v>400</v>
       </c>
-      <c r="P12" s="3">
+      <c r="Q12" s="3">
         <v>100</v>
       </c>
-      <c r="Q12" s="3">
+      <c r="R12" s="3">
         <v>300</v>
       </c>
-      <c r="R12" s="3">
+      <c r="S12" s="3">
         <v>100</v>
       </c>
-      <c r="S12" s="3">
-        <v>0</v>
-      </c>
       <c r="T12" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="13" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="U12" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" spans="1:21" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1045,8 +1062,11 @@
       <c r="T13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="U13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:21" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -1054,55 +1074,58 @@
         <v>0</v>
       </c>
       <c r="E14" s="3">
+        <v>0</v>
+      </c>
+      <c r="F14" s="3">
         <v>50500</v>
       </c>
-      <c r="F14" s="3">
-        <v>0</v>
-      </c>
       <c r="G14" s="3">
         <v>0</v>
       </c>
       <c r="H14" s="3">
+        <v>0</v>
+      </c>
+      <c r="I14" s="3">
         <v>18700</v>
       </c>
-      <c r="I14" s="3">
+      <c r="J14" s="3">
         <v>-1300</v>
       </c>
-      <c r="J14" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="K14" s="3" t="s">
         <v>4</v>
       </c>
       <c r="L14" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="M14" s="3">
-        <v>0</v>
+      <c r="M14" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="N14" s="3">
         <v>0</v>
       </c>
       <c r="O14" s="3">
+        <v>0</v>
+      </c>
+      <c r="P14" s="3">
         <v>1600</v>
       </c>
-      <c r="P14" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="Q14" s="3">
+      <c r="Q14" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="R14" s="3">
         <v>-5700</v>
       </c>
-      <c r="R14" s="3">
-        <v>0</v>
-      </c>
-      <c r="S14" s="3" t="s">
-        <v>4</v>
+      <c r="S14" s="3">
+        <v>0</v>
       </c>
       <c r="T14" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="15" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="U14" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="15" spans="1:21" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1157,8 +1180,11 @@
       <c r="T15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="U15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:21" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1176,64 +1202,68 @@
       <c r="R16" s="3"/>
       <c r="S16" s="3"/>
       <c r="T16" s="3"/>
-    </row>
-    <row r="17" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U16" s="3"/>
+    </row>
+    <row r="17" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>3400</v>
+      </c>
+      <c r="E17" s="3">
         <v>3300</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>52000</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>4200</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>4500</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>22500</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>4200</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>4800</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>3900</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>2500</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>6600</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>6500</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>5300</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>2300</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>-3000</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>1400</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>1500</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>1800</v>
       </c>
     </row>
-    <row r="18" spans="3:20" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
@@ -1241,55 +1271,58 @@
         <v>4</v>
       </c>
       <c r="E18" s="3">
+        <v>-3300</v>
+      </c>
+      <c r="F18" s="3">
         <v>-52000</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>-4200</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>-4500</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>-22500</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>-4200</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>-4800</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>-3900</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>-2500</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>-6600</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>-6500</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>-5300</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>-2300</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>3000</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>-1400</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>-1500</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>-1800</v>
       </c>
     </row>
-    <row r="19" spans="3:20" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1310,8 +1343,9 @@
       <c r="R19" s="3"/>
       <c r="S19" s="3"/>
       <c r="T19" s="3"/>
-    </row>
-    <row r="20" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U19" s="3"/>
+    </row>
+    <row r="20" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
@@ -1319,40 +1353,40 @@
         <v>4</v>
       </c>
       <c r="E20" s="3">
+        <v>-8800</v>
+      </c>
+      <c r="F20" s="3">
         <v>6500</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>-5100</v>
       </c>
-      <c r="G20" s="3">
-        <v>16500</v>
-      </c>
       <c r="H20" s="3">
+        <v>16300</v>
+      </c>
+      <c r="I20" s="3">
         <v>2200</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>14500</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>-2800</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>11400</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>4800</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>-8900</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>-4000</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>-1100</v>
-      </c>
-      <c r="P20" s="3">
-        <v>-100</v>
       </c>
       <c r="Q20" s="3">
         <v>-100</v>
@@ -1361,13 +1395,16 @@
         <v>-100</v>
       </c>
       <c r="S20" s="3">
+        <v>-100</v>
+      </c>
+      <c r="T20" s="3">
         <v>-200</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>-300</v>
       </c>
     </row>
-    <row r="21" spans="3:20" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
@@ -1375,78 +1412,81 @@
         <v>4</v>
       </c>
       <c r="E21" s="3">
+        <v>-12200</v>
+      </c>
+      <c r="F21" s="3">
         <v>-45500</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>-9200</v>
       </c>
-      <c r="G21" s="3">
-        <v>12000</v>
-      </c>
       <c r="H21" s="3">
+        <v>11800</v>
+      </c>
+      <c r="I21" s="3">
         <v>-20300</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>10400</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>-7600</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>7500</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>2300</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>-15500</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>-10500</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>-6400</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>-2400</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>2900</v>
       </c>
-      <c r="R21" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="S21" s="3" t="s">
         <v>4</v>
       </c>
       <c r="T21" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="22" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U21" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="22" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="D22" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="E22" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="F22" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="G22" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="H22" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="I22" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="J22" s="3" t="s">
-        <v>4</v>
+      <c r="D22" s="3">
+        <v>0</v>
+      </c>
+      <c r="E22" s="3">
+        <v>0</v>
+      </c>
+      <c r="F22" s="3">
+        <v>0</v>
+      </c>
+      <c r="G22" s="3">
+        <v>0</v>
+      </c>
+      <c r="H22" s="3">
+        <v>0</v>
+      </c>
+      <c r="I22" s="3">
+        <v>0</v>
+      </c>
+      <c r="J22" s="3">
+        <v>0</v>
       </c>
       <c r="K22" s="3" t="s">
         <v>4</v>
@@ -1457,18 +1497,18 @@
       <c r="M22" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="N22" s="3">
-        <v>0</v>
+      <c r="N22" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="O22" s="3">
         <v>0</v>
       </c>
       <c r="P22" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q22" s="3">
         <v>100</v>
       </c>
-      <c r="Q22" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="R22" s="3" t="s">
         <v>4</v>
       </c>
@@ -1478,64 +1518,70 @@
       <c r="T22" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="23" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U22" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="23" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-5800</v>
+      </c>
+      <c r="E23" s="3">
         <v>-12200</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>-45500</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>-9200</v>
       </c>
-      <c r="G23" s="3">
-        <v>12000</v>
-      </c>
       <c r="H23" s="3">
+        <v>11800</v>
+      </c>
+      <c r="I23" s="3">
         <v>-20300</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>10300</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>-7600</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>7500</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>2300</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>-15500</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>-10500</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>-6400</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>-2500</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>2900</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>-1500</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>-1700</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>-2100</v>
       </c>
     </row>
-    <row r="24" spans="3:20" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
@@ -1590,8 +1636,11 @@
       <c r="T24" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="25" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U24" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1646,120 +1695,129 @@
       <c r="T25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-5800</v>
+      </c>
+      <c r="E26" s="3">
         <v>-12200</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>-45500</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>-9200</v>
       </c>
-      <c r="G26" s="3">
-        <v>12000</v>
-      </c>
       <c r="H26" s="3">
+        <v>11800</v>
+      </c>
+      <c r="I26" s="3">
         <v>-20300</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>10300</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>-7600</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>7500</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>2300</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>-15500</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>-10500</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>-6400</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>-2500</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>2900</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>-1500</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>-1700</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>-2100</v>
       </c>
     </row>
-    <row r="27" spans="3:20" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-5800</v>
+      </c>
+      <c r="E27" s="3">
         <v>-12200</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>-45500</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>-9200</v>
       </c>
-      <c r="G27" s="3">
-        <v>12000</v>
-      </c>
       <c r="H27" s="3">
+        <v>11800</v>
+      </c>
+      <c r="I27" s="3">
         <v>-20300</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>10300</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>-7600</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>7500</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>2300</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>-15500</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>-10500</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>-6400</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>-2500</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>2900</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>-1500</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>-1700</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>-2100</v>
       </c>
     </row>
-    <row r="28" spans="3:20" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1814,8 +1872,11 @@
       <c r="T28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1870,8 +1931,11 @@
       <c r="T29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1926,8 +1990,11 @@
       <c r="T30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1982,8 +2049,11 @@
       <c r="T31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
@@ -1991,40 +2061,40 @@
         <v>4</v>
       </c>
       <c r="E32" s="3">
+        <v>8800</v>
+      </c>
+      <c r="F32" s="3">
         <v>-6500</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>5100</v>
       </c>
-      <c r="G32" s="3">
-        <v>-16500</v>
-      </c>
       <c r="H32" s="3">
+        <v>-16300</v>
+      </c>
+      <c r="I32" s="3">
         <v>-2200</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>-14500</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>2800</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>-11400</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>-4800</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>8900</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>4000</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>1100</v>
-      </c>
-      <c r="P32" s="3">
-        <v>100</v>
       </c>
       <c r="Q32" s="3">
         <v>100</v>
@@ -2033,69 +2103,75 @@
         <v>100</v>
       </c>
       <c r="S32" s="3">
+        <v>100</v>
+      </c>
+      <c r="T32" s="3">
         <v>200</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>300</v>
       </c>
     </row>
-    <row r="33" spans="2:20" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-5800</v>
+      </c>
+      <c r="E33" s="3">
         <v>-12200</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>-45500</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>-9200</v>
       </c>
-      <c r="G33" s="3">
-        <v>12000</v>
-      </c>
       <c r="H33" s="3">
+        <v>11800</v>
+      </c>
+      <c r="I33" s="3">
         <v>-20300</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>10300</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>-7600</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>7500</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>2300</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>-15500</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>-10500</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>-6400</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>-2500</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>2900</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>-1500</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>-1700</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>-2100</v>
       </c>
     </row>
-    <row r="34" spans="2:20" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2150,125 +2226,134 @@
       <c r="T34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-5800</v>
+      </c>
+      <c r="E35" s="3">
         <v>-12200</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>-45500</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>-9200</v>
       </c>
-      <c r="G35" s="3">
-        <v>12000</v>
-      </c>
       <c r="H35" s="3">
+        <v>11800</v>
+      </c>
+      <c r="I35" s="3">
         <v>-20300</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>10300</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>-7600</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>7500</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>2300</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>-15500</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>-10500</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>-6400</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>-2500</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>2900</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>-1500</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>-1700</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>-2100</v>
       </c>
     </row>
-    <row r="37" spans="2:20" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:21" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:20" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45473</v>
+      </c>
+      <c r="E38" s="2">
         <v>45382</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45291</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45199</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45107</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45016</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>44926</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44834</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44742</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44651</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44561</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44469</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44377</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44286</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44196</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44104</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44012</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>43921</v>
       </c>
     </row>
-    <row r="39" spans="2:20" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2289,8 +2374,9 @@
       <c r="R39" s="3"/>
       <c r="S39" s="3"/>
       <c r="T39" s="3"/>
-    </row>
-    <row r="40" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U39" s="3"/>
+    </row>
+    <row r="40" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2311,109 +2397,113 @@
       <c r="R40" s="3"/>
       <c r="S40" s="3"/>
       <c r="T40" s="3"/>
-    </row>
-    <row r="41" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U40" s="3"/>
+    </row>
+    <row r="41" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>4800</v>
+      </c>
+      <c r="E41" s="3">
         <v>5600</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>7600</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>15100</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>6200</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>11200</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>8000</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>18900</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>40700</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>51900</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>58600</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>61200</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>11500</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>16000</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>4200</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>4700</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>3600</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>4600</v>
       </c>
     </row>
-    <row r="42" spans="2:20" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>300</v>
+      </c>
+      <c r="E42" s="3">
         <v>800</v>
-      </c>
-      <c r="E42" s="3">
-        <v>600</v>
       </c>
       <c r="F42" s="3">
         <v>600</v>
       </c>
       <c r="G42" s="3">
+        <v>600</v>
+      </c>
+      <c r="H42" s="3">
         <v>1200</v>
       </c>
-      <c r="H42" s="3">
+      <c r="I42" s="3">
         <v>1700</v>
       </c>
-      <c r="I42" s="3">
+      <c r="J42" s="3">
         <v>400</v>
       </c>
-      <c r="J42" s="3">
+      <c r="K42" s="3">
         <v>700</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>1100</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>2100</v>
       </c>
-      <c r="M42" s="3">
+      <c r="N42" s="3">
         <v>1800</v>
-      </c>
-      <c r="N42" s="3">
-        <v>2300</v>
       </c>
       <c r="O42" s="3">
         <v>2300</v>
       </c>
       <c r="P42" s="3">
+        <v>2300</v>
+      </c>
+      <c r="Q42" s="3">
         <v>3500</v>
       </c>
-      <c r="Q42" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="R42" s="3" t="s">
         <v>4</v>
       </c>
@@ -2423,64 +2513,70 @@
       <c r="T42" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="43" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U42" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="43" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>400</v>
+      </c>
+      <c r="E43" s="3">
         <v>600</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>1100</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>1000</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>800</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>1300</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>3100</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>3500</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>1700</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>1300</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>1000</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>1100</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>600</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>400</v>
-      </c>
-      <c r="Q43" s="3">
-        <v>200</v>
       </c>
       <c r="R43" s="3">
         <v>200</v>
       </c>
       <c r="S43" s="3">
+        <v>200</v>
+      </c>
+      <c r="T43" s="3">
         <v>100</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>400</v>
       </c>
     </row>
-    <row r="44" spans="2:20" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -2535,120 +2631,129 @@
       <c r="T44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>1500</v>
+      </c>
+      <c r="E45" s="3">
         <v>1900</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>1400</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>700</v>
-      </c>
-      <c r="G45" s="3">
-        <v>400</v>
       </c>
       <c r="H45" s="3">
         <v>400</v>
       </c>
       <c r="I45" s="3">
+        <v>400</v>
+      </c>
+      <c r="J45" s="3">
         <v>2100</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>2500</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>2100</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>1300</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>600</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>400</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>1000</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>900</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>6100</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>600</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>400</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>600</v>
       </c>
     </row>
-    <row r="46" spans="2:20" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>7000</v>
+      </c>
+      <c r="E46" s="3">
         <v>8900</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>10600</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>17400</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>8600</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>14500</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>13500</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>25700</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>45600</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>56600</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>61900</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>64900</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>15300</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>20700</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>10500</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>5500</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>4100</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>5600</v>
       </c>
     </row>
-    <row r="47" spans="2:20" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -2703,49 +2808,52 @@
       <c r="T47" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>140000</v>
+      </c>
+      <c r="E48" s="3">
         <v>139300</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>136900</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>192900</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>190400</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>183300</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>173100</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>144300</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>129800</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>113700</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>104700</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>95000</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>93900</v>
-      </c>
-      <c r="P48" s="3">
-        <v>92300</v>
       </c>
       <c r="Q48" s="3">
         <v>92300</v>
@@ -2759,8 +2867,11 @@
       <c r="T48" s="3">
         <v>92300</v>
       </c>
-    </row>
-    <row r="49" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U48" s="3">
+        <v>92300</v>
+      </c>
+    </row>
+    <row r="49" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
@@ -2815,8 +2926,11 @@
       <c r="T49" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="50" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U49" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2871,8 +2985,11 @@
       <c r="T50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -2927,8 +3044,11 @@
       <c r="T51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
@@ -2939,13 +3059,13 @@
         <v>1200</v>
       </c>
       <c r="F52" s="3">
-        <v>0</v>
+        <v>1200</v>
       </c>
       <c r="G52" s="3">
         <v>0</v>
       </c>
       <c r="H52" s="3">
-        <v>900</v>
+        <v>0</v>
       </c>
       <c r="I52" s="3">
         <v>900</v>
@@ -2983,8 +3103,11 @@
       <c r="T52" s="3">
         <v>900</v>
       </c>
-    </row>
-    <row r="53" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U52" s="3">
+        <v>900</v>
+      </c>
+    </row>
+    <row r="53" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -3039,64 +3162,70 @@
       <c r="T53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>148200</v>
+      </c>
+      <c r="E54" s="3">
         <v>149300</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>148700</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>210300</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>199000</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>198800</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>187500</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>170900</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>176400</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>171300</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>167600</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>160800</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>110100</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>114000</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>103700</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>98700</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>97300</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>98800</v>
       </c>
     </row>
-    <row r="55" spans="3:20" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -3117,8 +3246,9 @@
       <c r="R55" s="3"/>
       <c r="S55" s="3"/>
       <c r="T55" s="3"/>
-    </row>
-    <row r="56" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U55" s="3"/>
+    </row>
+    <row r="56" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -3139,88 +3269,92 @@
       <c r="R56" s="3"/>
       <c r="S56" s="3"/>
       <c r="T56" s="3"/>
-    </row>
-    <row r="57" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U56" s="3"/>
+    </row>
+    <row r="57" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>6400</v>
+      </c>
+      <c r="E57" s="3">
         <v>7700</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>8800</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>9600</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>17100</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>15300</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>18900</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>8200</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>9900</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>5600</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>3500</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>2000</v>
       </c>
-      <c r="O57" s="3">
-        <v>0</v>
-      </c>
       <c r="P57" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q57" s="3">
         <v>200</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>400</v>
       </c>
-      <c r="R57" s="3">
-        <v>0</v>
-      </c>
       <c r="S57" s="3">
         <v>0</v>
       </c>
       <c r="T57" s="3">
+        <v>0</v>
+      </c>
+      <c r="U57" s="3">
         <v>100</v>
       </c>
     </row>
-    <row r="58" spans="3:20" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>48400</v>
+      </c>
+      <c r="E58" s="3">
         <v>47400</v>
       </c>
-      <c r="E58" s="3">
-        <v>0</v>
-      </c>
       <c r="F58" s="3">
+        <v>0</v>
+      </c>
+      <c r="G58" s="3">
         <v>55300</v>
       </c>
-      <c r="G58" s="3">
-        <v>0</v>
-      </c>
       <c r="H58" s="3">
         <v>0</v>
       </c>
       <c r="I58" s="3">
+        <v>0</v>
+      </c>
+      <c r="J58" s="3">
         <v>25700</v>
       </c>
-      <c r="J58" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="K58" s="3" t="s">
         <v>4</v>
       </c>
@@ -3233,250 +3367,265 @@
       <c r="N58" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="O58" s="3">
-        <v>0</v>
+      <c r="O58" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="P58" s="3">
         <v>0</v>
       </c>
-      <c r="Q58" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="R58" s="3">
+      <c r="Q58" s="3">
+        <v>0</v>
+      </c>
+      <c r="R58" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="S58" s="3">
         <v>7000</v>
       </c>
-      <c r="S58" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="T58" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="59" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U58" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="59" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>9900</v>
+      </c>
+      <c r="E59" s="3">
         <v>8400</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>7200</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>8000</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>7900</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>13300</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>9600</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>400</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>1200</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>500</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>1200</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>100</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>600</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>400</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>2400</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>1000</v>
       </c>
-      <c r="S59" s="3">
-        <v>0</v>
-      </c>
       <c r="T59" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="60" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U59" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="60" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>64600</v>
+      </c>
+      <c r="E60" s="3">
         <v>63500</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>16000</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>72900</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>25000</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>28600</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>54100</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>8700</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>11100</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>6000</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>4700</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>2100</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>600</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>500</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>2800</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>8000</v>
       </c>
-      <c r="S60" s="3">
-        <v>0</v>
-      </c>
       <c r="T60" s="3">
+        <v>0</v>
+      </c>
+      <c r="U60" s="3">
         <v>100</v>
       </c>
     </row>
-    <row r="61" spans="3:20" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>10500</v>
+      </c>
+      <c r="E61" s="3">
         <v>8600</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>46300</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>4600</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>53000</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>62000</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>5100</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>30000</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>27600</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>26200</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>23600</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>22400</v>
       </c>
-      <c r="O61" s="3">
-        <v>0</v>
-      </c>
       <c r="P61" s="3">
-        <v>6700</v>
+        <v>0</v>
       </c>
       <c r="Q61" s="3">
         <v>6700</v>
       </c>
       <c r="R61" s="3">
-        <v>0</v>
+        <v>6700</v>
       </c>
       <c r="S61" s="3">
-        <v>7000</v>
+        <v>0</v>
       </c>
       <c r="T61" s="3">
         <v>7000</v>
       </c>
-    </row>
-    <row r="62" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U61" s="3">
+        <v>7000</v>
+      </c>
+    </row>
+    <row r="62" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>3000</v>
+      </c>
+      <c r="E62" s="3">
         <v>2900</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>3100</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>1700</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>1900</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>1700</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>1800</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>20100</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>19500</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>34900</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>39400</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>29300</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>1300</v>
-      </c>
-      <c r="P62" s="3">
-        <v>2000</v>
       </c>
       <c r="Q62" s="3">
         <v>2000</v>
       </c>
       <c r="R62" s="3">
+        <v>2000</v>
+      </c>
+      <c r="S62" s="3">
         <v>2700</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>3200</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>3000</v>
       </c>
     </row>
-    <row r="63" spans="3:20" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -3531,8 +3680,11 @@
       <c r="T63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -3587,8 +3739,11 @@
       <c r="T64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -3643,64 +3798,70 @@
       <c r="T65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>78100</v>
+      </c>
+      <c r="E66" s="3">
         <v>74900</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>65400</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>79200</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>79800</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>92300</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>61000</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>58800</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>58200</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>67100</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>67600</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>53900</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>1900</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>9300</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>11500</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>10700</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>10200</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>10100</v>
       </c>
     </row>
-    <row r="67" spans="2:20" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -3721,8 +3882,9 @@
       <c r="R67" s="3"/>
       <c r="S67" s="3"/>
       <c r="T67" s="3"/>
-    </row>
-    <row r="68" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U67" s="3"/>
+    </row>
+    <row r="68" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -3777,8 +3939,11 @@
       <c r="T68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -3833,8 +3998,11 @@
       <c r="T69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -3889,8 +4057,11 @@
       <c r="T70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -3945,64 +4116,70 @@
       <c r="T71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-237800</v>
+      </c>
+      <c r="E72" s="3">
         <v>-232400</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-219900</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-173000</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-171400</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-183600</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-162900</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>-173900</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-166600</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>-174000</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>-176800</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>-161500</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>-151200</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>-145000</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>-143000</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>-145900</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>-145200</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>-143600</v>
       </c>
     </row>
-    <row r="73" spans="2:20" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -4057,8 +4234,11 @@
       <c r="T73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -4113,8 +4293,11 @@
       <c r="T74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -4169,64 +4352,70 @@
       <c r="T75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>70000</v>
+      </c>
+      <c r="E76" s="3">
         <v>74500</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>83300</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>131100</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>119100</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>106500</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>126500</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>112100</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>118200</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>104200</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>100000</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>107000</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>108200</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>104700</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>92200</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>88000</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>87200</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>88700</v>
       </c>
     </row>
-    <row r="77" spans="2:20" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -4281,125 +4470,134 @@
       <c r="T77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:21" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:20" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45473</v>
+      </c>
+      <c r="E80" s="2">
         <v>45382</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45291</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45199</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45107</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45016</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>44926</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44834</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44742</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44651</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44561</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44469</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44377</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44286</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44196</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44104</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44012</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>43921</v>
       </c>
     </row>
-    <row r="81" spans="3:20" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-5800</v>
+      </c>
+      <c r="E81" s="3">
         <v>-12200</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>-45500</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>-9200</v>
       </c>
-      <c r="G81" s="3">
-        <v>12000</v>
-      </c>
       <c r="H81" s="3">
+        <v>11800</v>
+      </c>
+      <c r="I81" s="3">
         <v>-20300</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>10300</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>-7600</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>7500</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>2300</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>-15500</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>-10500</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>-6400</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>-2500</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>2900</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>-1500</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>-1700</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>-2100</v>
       </c>
     </row>
-    <row r="82" spans="3:20" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -4420,8 +4618,9 @@
       <c r="R82" s="3"/>
       <c r="S82" s="3"/>
       <c r="T82" s="3"/>
-    </row>
-    <row r="83" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U82" s="3"/>
+    </row>
+    <row r="83" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
@@ -4440,8 +4639,8 @@
       <c r="H83" s="3">
         <v>0</v>
       </c>
-      <c r="I83" s="3" t="s">
-        <v>4</v>
+      <c r="I83" s="3">
+        <v>0</v>
       </c>
       <c r="J83" s="3" t="s">
         <v>4</v>
@@ -4449,14 +4648,14 @@
       <c r="K83" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="L83" s="3">
-        <v>0</v>
+      <c r="L83" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="M83" s="3">
         <v>0</v>
       </c>
-      <c r="N83" s="3" t="s">
-        <v>4</v>
+      <c r="N83" s="3">
+        <v>0</v>
       </c>
       <c r="O83" s="3" t="s">
         <v>4</v>
@@ -4476,8 +4675,11 @@
       <c r="T83" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="84" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U83" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="84" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -4532,8 +4734,11 @@
       <c r="T84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -4588,8 +4793,11 @@
       <c r="T85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -4644,8 +4852,11 @@
       <c r="T86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -4700,8 +4911,11 @@
       <c r="T87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -4756,64 +4970,70 @@
       <c r="T88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>-3900</v>
+      </c>
+      <c r="E89" s="3">
         <v>-4100</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>-6000</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>-12000</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>-4000</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>-1000</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>-6600</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>-500</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>-5300</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>-3500</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>-4900</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>-5300</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>-3600</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>-3100</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>-1500</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>-1200</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>-1100</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>-1800</v>
       </c>
     </row>
-    <row r="90" spans="3:20" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -4834,53 +5054,54 @@
       <c r="R90" s="3"/>
       <c r="S90" s="3"/>
       <c r="T90" s="3"/>
-    </row>
-    <row r="91" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U90" s="3"/>
+    </row>
+    <row r="91" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-300</v>
+      </c>
+      <c r="E91" s="3">
         <v>-600</v>
-      </c>
-      <c r="E91" s="3">
-        <v>-500</v>
       </c>
       <c r="F91" s="3">
         <v>-500</v>
       </c>
       <c r="G91" s="3">
+        <v>-500</v>
+      </c>
+      <c r="H91" s="3">
         <v>-2500</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-12300</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-15600</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-18800</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-8700</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-4500</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-6100</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-600</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>500</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-500</v>
       </c>
-      <c r="Q91" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="R91" s="3" t="s">
         <v>4</v>
       </c>
@@ -4890,8 +5111,11 @@
       <c r="T91" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="92" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U91" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="92" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -4946,8 +5170,11 @@
       <c r="T92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -5002,50 +5229,53 @@
       <c r="T93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>1000</v>
+      </c>
+      <c r="E94" s="3">
         <v>-100</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-1500</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>800</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-1000</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-12200</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-10900</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-18800</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-8700</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-5100</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-6100</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-500</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-1500</v>
       </c>
-      <c r="P94" s="3">
-        <v>0</v>
-      </c>
       <c r="Q94" s="3">
         <v>0</v>
       </c>
@@ -5058,8 +5288,11 @@
       <c r="T94" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="95" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U94" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="95" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -5080,8 +5313,9 @@
       <c r="R95" s="3"/>
       <c r="S95" s="3"/>
       <c r="T95" s="3"/>
-    </row>
-    <row r="96" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U95" s="3"/>
+    </row>
+    <row r="96" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -5136,8 +5370,11 @@
       <c r="T96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -5192,8 +5429,11 @@
       <c r="T97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -5248,8 +5488,11 @@
       <c r="T98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -5304,64 +5547,70 @@
       <c r="T99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>2000</v>
+      </c>
+      <c r="E100" s="3">
         <v>2300</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-100</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>20100</v>
       </c>
-      <c r="G100" s="3">
-        <v>0</v>
-      </c>
       <c r="H100" s="3">
+        <v>0</v>
+      </c>
+      <c r="I100" s="3">
         <v>16500</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>6500</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-2500</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>2900</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>1600</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>8500</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>54900</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>600</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>14900</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>1100</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>2400</v>
       </c>
-      <c r="S100" s="3">
-        <v>0</v>
-      </c>
       <c r="T100" s="3">
+        <v>0</v>
+      </c>
+      <c r="U100" s="3">
         <v>2100</v>
       </c>
     </row>
-    <row r="101" spans="3:20" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -5369,17 +5618,17 @@
         <v>0</v>
       </c>
       <c r="E101" s="3">
+        <v>0</v>
+      </c>
+      <c r="F101" s="3">
         <v>100</v>
       </c>
-      <c r="F101" s="3">
-        <v>0</v>
-      </c>
       <c r="G101" s="3">
+        <v>0</v>
+      </c>
+      <c r="H101" s="3">
         <v>100</v>
       </c>
-      <c r="H101" s="3">
-        <v>0</v>
-      </c>
       <c r="I101" s="3">
         <v>0</v>
       </c>
@@ -5390,86 +5639,92 @@
         <v>0</v>
       </c>
       <c r="L101" s="3">
+        <v>0</v>
+      </c>
+      <c r="M101" s="3">
         <v>200</v>
       </c>
-      <c r="M101" s="3">
+      <c r="N101" s="3">
         <v>-100</v>
       </c>
-      <c r="N101" s="3">
+      <c r="O101" s="3">
         <v>600</v>
       </c>
-      <c r="O101" s="3">
-        <v>0</v>
-      </c>
       <c r="P101" s="3">
         <v>0</v>
       </c>
       <c r="Q101" s="3">
+        <v>0</v>
+      </c>
+      <c r="R101" s="3">
         <v>-100</v>
       </c>
-      <c r="R101" s="3">
-        <v>0</v>
-      </c>
       <c r="S101" s="3">
         <v>0</v>
       </c>
       <c r="T101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-800</v>
+      </c>
+      <c r="E102" s="3">
         <v>-1900</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-7500</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>8800</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-5000</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>3300</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-11000</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-21800</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-11200</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-6700</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-2600</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>49700</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-4500</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>11800</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>-500</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>1100</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>-1100</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>200</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/ELBM_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/ELBM_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="179" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="230" uniqueCount="92">
   <si>
     <t>ELBM</t>
   </si>
@@ -656,122 +656,126 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:U102"/>
+  <dimension ref="A5:V102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.42578125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="19" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="16" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="20" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:22" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:22" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45565</v>
+      </c>
+      <c r="E7" s="2">
         <v>45473</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45382</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45291</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45199</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45107</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45016</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44926</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44834</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44742</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44651</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44561</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44469</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44377</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44286</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44196</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44104</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44012</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>43921</v>
       </c>
     </row>
-    <row r="8" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:22" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="E8" s="3">
-        <v>0</v>
-      </c>
-      <c r="F8" s="3">
-        <v>0</v>
-      </c>
-      <c r="G8" s="3">
-        <v>0</v>
-      </c>
-      <c r="H8" s="3">
-        <v>0</v>
-      </c>
-      <c r="I8" s="3">
-        <v>0</v>
-      </c>
-      <c r="J8" s="3">
-        <v>0</v>
+      <c r="E8" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="F8" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="G8" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="H8" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="I8" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="J8" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="K8" s="3">
         <v>0</v>
@@ -806,8 +810,11 @@
       <c r="U8" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="9" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="V8" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:22" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
@@ -865,8 +872,11 @@
       <c r="U9" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="10" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="V9" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="10" spans="1:22" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
@@ -924,8 +934,11 @@
       <c r="U10" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="11" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="V10" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="11" spans="1:22" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -947,67 +960,71 @@
       <c r="S11" s="3"/>
       <c r="T11" s="3"/>
       <c r="U11" s="3"/>
-    </row>
-    <row r="12" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="V11" s="3"/>
+    </row>
+    <row r="12" spans="1:22" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="D12" s="3">
+      <c r="D12" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="E12" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="F12" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="G12" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="H12" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="I12" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="J12" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="K12" s="3">
+        <v>600</v>
+      </c>
+      <c r="L12" s="3">
+        <v>1300</v>
+      </c>
+      <c r="M12" s="3">
+        <v>1100</v>
+      </c>
+      <c r="N12" s="3">
+        <v>400</v>
+      </c>
+      <c r="O12" s="3">
+        <v>2900</v>
+      </c>
+      <c r="P12" s="3">
+        <v>1200</v>
+      </c>
+      <c r="Q12" s="3">
+        <v>400</v>
+      </c>
+      <c r="R12" s="3">
         <v>100</v>
       </c>
-      <c r="E12" s="3">
+      <c r="S12" s="3">
+        <v>300</v>
+      </c>
+      <c r="T12" s="3">
         <v>100</v>
       </c>
-      <c r="F12" s="3">
-        <v>100</v>
-      </c>
-      <c r="G12" s="3">
-        <v>300</v>
-      </c>
-      <c r="H12" s="3">
-        <v>300</v>
-      </c>
-      <c r="I12" s="3">
-        <v>100</v>
-      </c>
-      <c r="J12" s="3">
-        <v>600</v>
-      </c>
-      <c r="K12" s="3">
-        <v>1300</v>
-      </c>
-      <c r="L12" s="3">
-        <v>1100</v>
-      </c>
-      <c r="M12" s="3">
-        <v>400</v>
-      </c>
-      <c r="N12" s="3">
-        <v>2900</v>
-      </c>
-      <c r="O12" s="3">
-        <v>1200</v>
-      </c>
-      <c r="P12" s="3">
-        <v>400</v>
-      </c>
-      <c r="Q12" s="3">
-        <v>100</v>
-      </c>
-      <c r="R12" s="3">
-        <v>300</v>
-      </c>
-      <c r="S12" s="3">
-        <v>100</v>
-      </c>
-      <c r="T12" s="3">
-        <v>0</v>
-      </c>
       <c r="U12" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="13" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="V12" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" spans="1:22" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1065,8 +1082,11 @@
       <c r="U13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="V13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:22" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -1074,58 +1094,61 @@
         <v>0</v>
       </c>
       <c r="E14" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="F14" s="3">
-        <v>50500</v>
+        <v>-100</v>
       </c>
       <c r="G14" s="3">
-        <v>0</v>
+        <v>38200</v>
       </c>
       <c r="H14" s="3">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="I14" s="3">
-        <v>18700</v>
+        <v>0</v>
       </c>
       <c r="J14" s="3">
+        <v>13800</v>
+      </c>
+      <c r="K14" s="3">
         <v>-1300</v>
       </c>
-      <c r="K14" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="L14" s="3" t="s">
         <v>4</v>
       </c>
       <c r="M14" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="N14" s="3">
-        <v>0</v>
+      <c r="N14" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="O14" s="3">
         <v>0</v>
       </c>
       <c r="P14" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q14" s="3">
         <v>1600</v>
       </c>
-      <c r="Q14" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="R14" s="3">
+      <c r="R14" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="S14" s="3">
         <v>-5700</v>
       </c>
-      <c r="S14" s="3">
-        <v>0</v>
-      </c>
-      <c r="T14" s="3" t="s">
-        <v>4</v>
+      <c r="T14" s="3">
+        <v>0</v>
       </c>
       <c r="U14" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="15" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="V14" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="15" spans="1:22" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1183,8 +1206,11 @@
       <c r="U15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="V15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:22" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1203,126 +1229,133 @@
       <c r="S16" s="3"/>
       <c r="T16" s="3"/>
       <c r="U16" s="3"/>
-    </row>
-    <row r="17" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V16" s="3"/>
+    </row>
+    <row r="17" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
-        <v>3400</v>
+        <v>2400</v>
       </c>
       <c r="E17" s="3">
+        <v>2400</v>
+      </c>
+      <c r="F17" s="3">
+        <v>2300</v>
+      </c>
+      <c r="G17" s="3">
+        <v>900</v>
+      </c>
+      <c r="H17" s="3">
+        <v>2900</v>
+      </c>
+      <c r="I17" s="3">
         <v>3300</v>
       </c>
-      <c r="F17" s="3">
-        <v>52000</v>
-      </c>
-      <c r="G17" s="3">
+      <c r="J17" s="3">
+        <v>2800</v>
+      </c>
+      <c r="K17" s="3">
         <v>4200</v>
       </c>
-      <c r="H17" s="3">
-        <v>4500</v>
-      </c>
-      <c r="I17" s="3">
-        <v>22500</v>
-      </c>
-      <c r="J17" s="3">
-        <v>4200</v>
-      </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>4800</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>3900</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>2500</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>6600</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>6500</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>5300</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>2300</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>-3000</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>1400</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>1500</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>1800</v>
       </c>
     </row>
-    <row r="18" spans="3:21" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="D18" s="3" t="s">
-        <v>4</v>
+      <c r="D18" s="3">
+        <v>-2400</v>
       </c>
       <c r="E18" s="3">
+        <v>-2400</v>
+      </c>
+      <c r="F18" s="3">
+        <v>-2300</v>
+      </c>
+      <c r="G18" s="3">
+        <v>-900</v>
+      </c>
+      <c r="H18" s="3">
+        <v>-2900</v>
+      </c>
+      <c r="I18" s="3">
         <v>-3300</v>
       </c>
-      <c r="F18" s="3">
-        <v>-52000</v>
-      </c>
-      <c r="G18" s="3">
+      <c r="J18" s="3">
+        <v>-2800</v>
+      </c>
+      <c r="K18" s="3">
         <v>-4200</v>
       </c>
-      <c r="H18" s="3">
-        <v>-4500</v>
-      </c>
-      <c r="I18" s="3">
-        <v>-22500</v>
-      </c>
-      <c r="J18" s="3">
-        <v>-4200</v>
-      </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>-4800</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>-3900</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>-2500</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>-6600</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>-6500</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>-5300</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>-2300</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>3000</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>-1400</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>-1500</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>-1800</v>
       </c>
     </row>
-    <row r="19" spans="3:21" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1344,52 +1377,53 @@
       <c r="S19" s="3"/>
       <c r="T19" s="3"/>
       <c r="U19" s="3"/>
-    </row>
-    <row r="20" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V19" s="3"/>
+    </row>
+    <row r="20" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="D20" s="3" t="s">
-        <v>4</v>
+      <c r="D20" s="3">
+        <v>-2200</v>
       </c>
       <c r="E20" s="3">
-        <v>-8800</v>
+        <v>900</v>
       </c>
       <c r="F20" s="3">
-        <v>6500</v>
+        <v>6000</v>
       </c>
       <c r="G20" s="3">
-        <v>-5100</v>
+        <v>-11100</v>
       </c>
       <c r="H20" s="3">
-        <v>16300</v>
+        <v>3700</v>
       </c>
       <c r="I20" s="3">
-        <v>2200</v>
+        <v>-12100</v>
       </c>
       <c r="J20" s="3">
+        <v>-1500</v>
+      </c>
+      <c r="K20" s="3">
         <v>14500</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>-2800</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>11400</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>4800</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>-8900</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>-4000</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>-1100</v>
-      </c>
-      <c r="Q20" s="3">
-        <v>-100</v>
       </c>
       <c r="R20" s="3">
         <v>-100</v>
@@ -1398,98 +1432,104 @@
         <v>-100</v>
       </c>
       <c r="T20" s="3">
+        <v>-100</v>
+      </c>
+      <c r="U20" s="3">
         <v>-200</v>
       </c>
-      <c r="U20" s="3">
+      <c r="V20" s="3">
         <v>-300</v>
       </c>
     </row>
-    <row r="21" spans="3:21" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="D21" s="3" t="s">
-        <v>4</v>
+      <c r="D21" s="3">
+        <v>-200</v>
       </c>
       <c r="E21" s="3">
-        <v>-12200</v>
+        <v>-3300</v>
       </c>
       <c r="F21" s="3">
-        <v>-45500</v>
+        <v>-8300</v>
       </c>
       <c r="G21" s="3">
-        <v>-9200</v>
+        <v>10100</v>
       </c>
       <c r="H21" s="3">
-        <v>11800</v>
+        <v>-6700</v>
       </c>
       <c r="I21" s="3">
-        <v>-20300</v>
+        <v>8800</v>
       </c>
       <c r="J21" s="3">
+        <v>-1300</v>
+      </c>
+      <c r="K21" s="3">
         <v>10400</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>-7600</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>7500</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>2300</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>-15500</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>-10500</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>-6400</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>-2400</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>2900</v>
       </c>
-      <c r="S21" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="T21" s="3" t="s">
         <v>4</v>
       </c>
       <c r="U21" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="22" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V21" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="22" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
-        <v>0</v>
+        <v>2000</v>
       </c>
       <c r="E22" s="3">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="F22" s="3">
-        <v>0</v>
+        <v>700</v>
       </c>
       <c r="G22" s="3">
-        <v>0</v>
-      </c>
-      <c r="H22" s="3">
-        <v>0</v>
-      </c>
-      <c r="I22" s="3">
-        <v>0</v>
-      </c>
-      <c r="J22" s="3">
-        <v>0</v>
-      </c>
-      <c r="K22" s="3" t="s">
-        <v>4</v>
+        <v>6200</v>
+      </c>
+      <c r="H22" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="I22" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="J22" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="K22" s="3">
+        <v>0</v>
       </c>
       <c r="L22" s="3" t="s">
         <v>4</v>
@@ -1500,18 +1540,18 @@
       <c r="N22" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="O22" s="3">
-        <v>0</v>
+      <c r="O22" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="P22" s="3">
         <v>0</v>
       </c>
       <c r="Q22" s="3">
+        <v>0</v>
+      </c>
+      <c r="R22" s="3">
         <v>100</v>
       </c>
-      <c r="R22" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="S22" s="3" t="s">
         <v>4</v>
       </c>
@@ -1521,90 +1561,96 @@
       <c r="U22" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="23" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V22" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="23" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
-        <v>-5800</v>
+        <v>-2200</v>
       </c>
       <c r="E23" s="3">
-        <v>-12200</v>
+        <v>-4200</v>
       </c>
       <c r="F23" s="3">
-        <v>-45500</v>
+        <v>-9000</v>
       </c>
       <c r="G23" s="3">
-        <v>-9200</v>
+        <v>-34400</v>
       </c>
       <c r="H23" s="3">
-        <v>11800</v>
+        <v>-6800</v>
       </c>
       <c r="I23" s="3">
-        <v>-20300</v>
+        <v>8900</v>
       </c>
       <c r="J23" s="3">
+        <v>-15000</v>
+      </c>
+      <c r="K23" s="3">
         <v>10300</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>-7600</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>7500</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>2300</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>-15500</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>-10500</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>-6400</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>-2500</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>2900</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>-1500</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>-1700</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>-2100</v>
       </c>
     </row>
-    <row r="24" spans="3:21" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="D24" s="3">
-        <v>0</v>
-      </c>
-      <c r="E24" s="3">
-        <v>0</v>
-      </c>
-      <c r="F24" s="3">
-        <v>0</v>
-      </c>
-      <c r="G24" s="3">
-        <v>0</v>
-      </c>
-      <c r="H24" s="3">
-        <v>0</v>
-      </c>
-      <c r="I24" s="3">
-        <v>0</v>
-      </c>
-      <c r="J24" s="3">
-        <v>0</v>
+      <c r="D24" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="E24" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="F24" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="G24" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="H24" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="I24" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="J24" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="K24" s="3">
         <v>0</v>
@@ -1639,8 +1685,11 @@
       <c r="U24" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="25" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V24" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1698,126 +1747,135 @@
       <c r="U25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
-        <v>-5800</v>
+        <v>-2200</v>
       </c>
       <c r="E26" s="3">
-        <v>-12200</v>
+        <v>-4200</v>
       </c>
       <c r="F26" s="3">
-        <v>-45500</v>
+        <v>-9000</v>
       </c>
       <c r="G26" s="3">
-        <v>-9200</v>
+        <v>-34400</v>
       </c>
       <c r="H26" s="3">
-        <v>11800</v>
+        <v>-6800</v>
       </c>
       <c r="I26" s="3">
-        <v>-20300</v>
+        <v>8900</v>
       </c>
       <c r="J26" s="3">
+        <v>-15000</v>
+      </c>
+      <c r="K26" s="3">
         <v>10300</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>-7600</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>7500</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>2300</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>-15500</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>-10500</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>-6400</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>-2500</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>2900</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>-1500</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>-1700</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>-2100</v>
       </c>
     </row>
-    <row r="27" spans="3:21" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
-        <v>-5800</v>
+        <v>-2200</v>
       </c>
       <c r="E27" s="3">
-        <v>-12200</v>
+        <v>-4200</v>
       </c>
       <c r="F27" s="3">
-        <v>-45500</v>
+        <v>-9000</v>
       </c>
       <c r="G27" s="3">
-        <v>-9200</v>
+        <v>-34400</v>
       </c>
       <c r="H27" s="3">
-        <v>11800</v>
+        <v>-6800</v>
       </c>
       <c r="I27" s="3">
-        <v>-20300</v>
+        <v>8900</v>
       </c>
       <c r="J27" s="3">
+        <v>-15000</v>
+      </c>
+      <c r="K27" s="3">
         <v>10300</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>-7600</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>7500</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>2300</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>-15500</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>-10500</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>-6400</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>-2500</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>2900</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>-1500</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>-1700</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>-2100</v>
       </c>
     </row>
-    <row r="28" spans="3:21" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1875,8 +1933,11 @@
       <c r="U28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1934,8 +1995,11 @@
       <c r="U29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1993,8 +2057,11 @@
       <c r="U30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2052,52 +2119,55 @@
       <c r="U31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="D32" s="3" t="s">
-        <v>4</v>
+      <c r="D32" s="3">
+        <v>2200</v>
       </c>
       <c r="E32" s="3">
-        <v>8800</v>
+        <v>-900</v>
       </c>
       <c r="F32" s="3">
-        <v>-6500</v>
+        <v>-6000</v>
       </c>
       <c r="G32" s="3">
-        <v>5100</v>
+        <v>11100</v>
       </c>
       <c r="H32" s="3">
-        <v>-16300</v>
+        <v>-3700</v>
       </c>
       <c r="I32" s="3">
-        <v>-2200</v>
+        <v>12100</v>
       </c>
       <c r="J32" s="3">
+        <v>1500</v>
+      </c>
+      <c r="K32" s="3">
         <v>-14500</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>2800</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>-11400</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>-4800</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>8900</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>4000</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>1100</v>
-      </c>
-      <c r="Q32" s="3">
-        <v>100</v>
       </c>
       <c r="R32" s="3">
         <v>100</v>
@@ -2106,72 +2176,78 @@
         <v>100</v>
       </c>
       <c r="T32" s="3">
+        <v>100</v>
+      </c>
+      <c r="U32" s="3">
         <v>200</v>
       </c>
-      <c r="U32" s="3">
+      <c r="V32" s="3">
         <v>300</v>
       </c>
     </row>
-    <row r="33" spans="2:21" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
-        <v>-5800</v>
+        <v>-2200</v>
       </c>
       <c r="E33" s="3">
-        <v>-12200</v>
+        <v>-4200</v>
       </c>
       <c r="F33" s="3">
-        <v>-45500</v>
+        <v>-9000</v>
       </c>
       <c r="G33" s="3">
-        <v>-9200</v>
+        <v>-34400</v>
       </c>
       <c r="H33" s="3">
-        <v>11800</v>
+        <v>-6800</v>
       </c>
       <c r="I33" s="3">
-        <v>-20300</v>
+        <v>8900</v>
       </c>
       <c r="J33" s="3">
+        <v>-15000</v>
+      </c>
+      <c r="K33" s="3">
         <v>10300</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>-7600</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>7500</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>2300</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>-15500</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>-10500</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>-6400</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>-2500</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>2900</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>-1500</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>-1700</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>-2100</v>
       </c>
     </row>
-    <row r="34" spans="2:21" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2229,131 +2305,140 @@
       <c r="U34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
-        <v>-5800</v>
+        <v>-2200</v>
       </c>
       <c r="E35" s="3">
-        <v>-12200</v>
+        <v>-4200</v>
       </c>
       <c r="F35" s="3">
-        <v>-45500</v>
+        <v>-9000</v>
       </c>
       <c r="G35" s="3">
-        <v>-9200</v>
+        <v>-34400</v>
       </c>
       <c r="H35" s="3">
-        <v>11800</v>
+        <v>-6800</v>
       </c>
       <c r="I35" s="3">
-        <v>-20300</v>
+        <v>8900</v>
       </c>
       <c r="J35" s="3">
+        <v>-15000</v>
+      </c>
+      <c r="K35" s="3">
         <v>10300</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>-7600</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>7500</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>2300</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>-15500</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>-10500</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>-6400</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>-2500</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>2900</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>-1500</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>-1700</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>-2100</v>
       </c>
     </row>
-    <row r="37" spans="2:21" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:22" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:21" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45565</v>
+      </c>
+      <c r="E38" s="2">
         <v>45473</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45382</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45291</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45199</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45107</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45016</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44926</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44834</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44742</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44651</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44561</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44469</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44377</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44286</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44196</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44104</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44012</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>43921</v>
       </c>
     </row>
-    <row r="39" spans="2:21" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2375,8 +2460,9 @@
       <c r="S39" s="3"/>
       <c r="T39" s="3"/>
       <c r="U39" s="3"/>
-    </row>
-    <row r="40" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V39" s="3"/>
+    </row>
+    <row r="40" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2398,115 +2484,119 @@
       <c r="S40" s="3"/>
       <c r="T40" s="3"/>
       <c r="U40" s="3"/>
-    </row>
-    <row r="41" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V40" s="3"/>
+    </row>
+    <row r="41" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
-        <v>4800</v>
+        <v>2400</v>
       </c>
       <c r="E41" s="3">
-        <v>5600</v>
+        <v>3500</v>
       </c>
       <c r="F41" s="3">
-        <v>7600</v>
+        <v>4200</v>
       </c>
       <c r="G41" s="3">
-        <v>15100</v>
+        <v>5700</v>
       </c>
       <c r="H41" s="3">
-        <v>6200</v>
+        <v>11100</v>
       </c>
       <c r="I41" s="3">
-        <v>11200</v>
+        <v>4700</v>
       </c>
       <c r="J41" s="3">
+        <v>8300</v>
+      </c>
+      <c r="K41" s="3">
         <v>8000</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>18900</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>40700</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>51900</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>58600</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>61200</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>11500</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>16000</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>4200</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>4700</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>3600</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>4600</v>
       </c>
     </row>
-    <row r="42" spans="2:21" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
-        <v>300</v>
+        <v>100</v>
       </c>
       <c r="E42" s="3">
-        <v>800</v>
+        <v>200</v>
       </c>
       <c r="F42" s="3">
         <v>600</v>
       </c>
       <c r="G42" s="3">
-        <v>600</v>
+        <v>500</v>
       </c>
       <c r="H42" s="3">
+        <v>500</v>
+      </c>
+      <c r="I42" s="3">
+        <v>900</v>
+      </c>
+      <c r="J42" s="3">
         <v>1200</v>
       </c>
-      <c r="I42" s="3">
-        <v>1700</v>
-      </c>
-      <c r="J42" s="3">
+      <c r="K42" s="3">
         <v>400</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>700</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>1100</v>
       </c>
-      <c r="M42" s="3">
+      <c r="N42" s="3">
         <v>2100</v>
       </c>
-      <c r="N42" s="3">
+      <c r="O42" s="3">
         <v>1800</v>
-      </c>
-      <c r="O42" s="3">
-        <v>2300</v>
       </c>
       <c r="P42" s="3">
         <v>2300</v>
       </c>
       <c r="Q42" s="3">
+        <v>2300</v>
+      </c>
+      <c r="R42" s="3">
         <v>3500</v>
       </c>
-      <c r="R42" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="S42" s="3" t="s">
         <v>4</v>
       </c>
@@ -2516,90 +2606,96 @@
       <c r="U42" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="43" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V42" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="43" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>200</v>
+      </c>
+      <c r="E43" s="3">
+        <v>300</v>
+      </c>
+      <c r="F43" s="3">
         <v>400</v>
       </c>
-      <c r="E43" s="3">
+      <c r="G43" s="3">
+        <v>800</v>
+      </c>
+      <c r="H43" s="3">
+        <v>700</v>
+      </c>
+      <c r="I43" s="3">
         <v>600</v>
       </c>
-      <c r="F43" s="3">
+      <c r="J43" s="3">
+        <v>900</v>
+      </c>
+      <c r="K43" s="3">
+        <v>3100</v>
+      </c>
+      <c r="L43" s="3">
+        <v>3500</v>
+      </c>
+      <c r="M43" s="3">
+        <v>1700</v>
+      </c>
+      <c r="N43" s="3">
+        <v>1300</v>
+      </c>
+      <c r="O43" s="3">
+        <v>1000</v>
+      </c>
+      <c r="P43" s="3">
         <v>1100</v>
       </c>
-      <c r="G43" s="3">
-        <v>1000</v>
-      </c>
-      <c r="H43" s="3">
-        <v>800</v>
-      </c>
-      <c r="I43" s="3">
-        <v>1300</v>
-      </c>
-      <c r="J43" s="3">
-        <v>3100</v>
-      </c>
-      <c r="K43" s="3">
-        <v>3500</v>
-      </c>
-      <c r="L43" s="3">
-        <v>1700</v>
-      </c>
-      <c r="M43" s="3">
-        <v>1300</v>
-      </c>
-      <c r="N43" s="3">
-        <v>1000</v>
-      </c>
-      <c r="O43" s="3">
-        <v>1100</v>
-      </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>600</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>400</v>
-      </c>
-      <c r="R43" s="3">
-        <v>200</v>
       </c>
       <c r="S43" s="3">
         <v>200</v>
       </c>
       <c r="T43" s="3">
+        <v>200</v>
+      </c>
+      <c r="U43" s="3">
         <v>100</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>400</v>
       </c>
     </row>
-    <row r="44" spans="2:21" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="D44" s="3">
-        <v>0</v>
-      </c>
-      <c r="E44" s="3">
-        <v>0</v>
-      </c>
-      <c r="F44" s="3">
-        <v>0</v>
-      </c>
-      <c r="G44" s="3">
-        <v>0</v>
-      </c>
-      <c r="H44" s="3">
-        <v>0</v>
-      </c>
-      <c r="I44" s="3">
-        <v>0</v>
-      </c>
-      <c r="J44" s="3">
-        <v>0</v>
+      <c r="D44" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="E44" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="F44" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="G44" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="H44" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="I44" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="J44" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="K44" s="3">
         <v>0</v>
@@ -2634,149 +2730,158 @@
       <c r="U44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="D45" s="3">
-        <v>1500</v>
-      </c>
-      <c r="E45" s="3">
-        <v>1900</v>
-      </c>
-      <c r="F45" s="3">
-        <v>1400</v>
-      </c>
-      <c r="G45" s="3">
-        <v>700</v>
-      </c>
-      <c r="H45" s="3">
+      <c r="D45" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="E45" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="F45" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="G45" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="H45" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="I45" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="J45" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="K45" s="3">
+        <v>2100</v>
+      </c>
+      <c r="L45" s="3">
+        <v>2500</v>
+      </c>
+      <c r="M45" s="3">
+        <v>2100</v>
+      </c>
+      <c r="N45" s="3">
+        <v>1300</v>
+      </c>
+      <c r="O45" s="3">
+        <v>600</v>
+      </c>
+      <c r="P45" s="3">
         <v>400</v>
       </c>
-      <c r="I45" s="3">
+      <c r="Q45" s="3">
+        <v>1000</v>
+      </c>
+      <c r="R45" s="3">
+        <v>900</v>
+      </c>
+      <c r="S45" s="3">
+        <v>6100</v>
+      </c>
+      <c r="T45" s="3">
+        <v>600</v>
+      </c>
+      <c r="U45" s="3">
         <v>400</v>
       </c>
-      <c r="J45" s="3">
-        <v>2100</v>
-      </c>
-      <c r="K45" s="3">
-        <v>2500</v>
-      </c>
-      <c r="L45" s="3">
-        <v>2100</v>
-      </c>
-      <c r="M45" s="3">
-        <v>1300</v>
-      </c>
-      <c r="N45" s="3">
+      <c r="V45" s="3">
         <v>600</v>
       </c>
-      <c r="O45" s="3">
-        <v>400</v>
-      </c>
-      <c r="P45" s="3">
-        <v>1000</v>
-      </c>
-      <c r="Q45" s="3">
-        <v>900</v>
-      </c>
-      <c r="R45" s="3">
-        <v>6100</v>
-      </c>
-      <c r="S45" s="3">
-        <v>600</v>
-      </c>
-      <c r="T45" s="3">
-        <v>400</v>
-      </c>
-      <c r="U45" s="3">
-        <v>600</v>
-      </c>
-    </row>
-    <row r="46" spans="2:21" x14ac:dyDescent="0.2">
+    </row>
+    <row r="46" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
-        <v>7000</v>
+        <v>3400</v>
       </c>
       <c r="E46" s="3">
-        <v>8900</v>
+        <v>5100</v>
       </c>
       <c r="F46" s="3">
-        <v>10600</v>
+        <v>6500</v>
       </c>
       <c r="G46" s="3">
-        <v>17400</v>
+        <v>8000</v>
       </c>
       <c r="H46" s="3">
-        <v>8600</v>
+        <v>12900</v>
       </c>
       <c r="I46" s="3">
-        <v>14500</v>
+        <v>6500</v>
       </c>
       <c r="J46" s="3">
+        <v>10700</v>
+      </c>
+      <c r="K46" s="3">
         <v>13500</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>25700</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>45600</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>56600</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>61900</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>64900</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>15300</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>20700</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>10500</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>5500</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>4100</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>5600</v>
       </c>
     </row>
-    <row r="47" spans="2:21" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="D47" s="3">
-        <v>0</v>
-      </c>
-      <c r="E47" s="3">
-        <v>0</v>
-      </c>
-      <c r="F47" s="3">
-        <v>0</v>
-      </c>
-      <c r="G47" s="3">
-        <v>0</v>
-      </c>
-      <c r="H47" s="3">
-        <v>0</v>
-      </c>
-      <c r="I47" s="3">
-        <v>0</v>
-      </c>
-      <c r="J47" s="3">
-        <v>0</v>
+      <c r="D47" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="E47" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="F47" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="G47" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="H47" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="I47" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="J47" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="K47" s="3">
         <v>0</v>
@@ -2811,52 +2916,55 @@
       <c r="U47" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
-        <v>140000</v>
+        <v>102800</v>
       </c>
       <c r="E48" s="3">
-        <v>139300</v>
+        <v>102300</v>
       </c>
       <c r="F48" s="3">
-        <v>136900</v>
+        <v>102900</v>
       </c>
       <c r="G48" s="3">
-        <v>192900</v>
+        <v>103700</v>
       </c>
       <c r="H48" s="3">
-        <v>190400</v>
+        <v>142600</v>
       </c>
       <c r="I48" s="3">
-        <v>183300</v>
+        <v>142100</v>
       </c>
       <c r="J48" s="3">
+        <v>133700</v>
+      </c>
+      <c r="K48" s="3">
         <v>173100</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>144300</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>129800</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>113700</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>104700</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>95000</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>93900</v>
-      </c>
-      <c r="Q48" s="3">
-        <v>92300</v>
       </c>
       <c r="R48" s="3">
         <v>92300</v>
@@ -2870,8 +2978,11 @@
       <c r="U48" s="3">
         <v>92300</v>
       </c>
-    </row>
-    <row r="49" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V48" s="3">
+        <v>92300</v>
+      </c>
+    </row>
+    <row r="49" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
@@ -2929,8 +3040,11 @@
       <c r="U49" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="50" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V49" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2988,8 +3102,11 @@
       <c r="U50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -3047,31 +3164,34 @@
       <c r="U51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
-        <v>1200</v>
+        <v>900</v>
       </c>
       <c r="E52" s="3">
-        <v>1200</v>
+        <v>900</v>
       </c>
       <c r="F52" s="3">
-        <v>1200</v>
+        <v>900</v>
       </c>
       <c r="G52" s="3">
-        <v>0</v>
-      </c>
-      <c r="H52" s="3">
-        <v>0</v>
+        <v>900</v>
+      </c>
+      <c r="H52" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="I52" s="3">
-        <v>900</v>
+        <v>1700</v>
       </c>
       <c r="J52" s="3">
-        <v>900</v>
+        <v>2500</v>
       </c>
       <c r="K52" s="3">
         <v>900</v>
@@ -3106,8 +3226,11 @@
       <c r="U52" s="3">
         <v>900</v>
       </c>
-    </row>
-    <row r="53" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V52" s="3">
+        <v>900</v>
+      </c>
+    </row>
+    <row r="53" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -3165,67 +3288,73 @@
       <c r="U53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
-        <v>148200</v>
+        <v>107100</v>
       </c>
       <c r="E54" s="3">
-        <v>149300</v>
+        <v>108300</v>
       </c>
       <c r="F54" s="3">
-        <v>148700</v>
+        <v>110300</v>
       </c>
       <c r="G54" s="3">
-        <v>210300</v>
+        <v>112600</v>
       </c>
       <c r="H54" s="3">
-        <v>199000</v>
+        <v>155500</v>
       </c>
       <c r="I54" s="3">
-        <v>198800</v>
+        <v>150300</v>
       </c>
       <c r="J54" s="3">
+        <v>146900</v>
+      </c>
+      <c r="K54" s="3">
         <v>187500</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>170900</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>176400</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>171300</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>167600</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>160800</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>110100</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>114000</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>103700</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>98700</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>97300</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>98800</v>
       </c>
     </row>
-    <row r="55" spans="3:21" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -3247,8 +3376,9 @@
       <c r="S55" s="3"/>
       <c r="T55" s="3"/>
       <c r="U55" s="3"/>
-    </row>
-    <row r="56" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V55" s="3"/>
+    </row>
+    <row r="56" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -3270,94 +3400,98 @@
       <c r="S56" s="3"/>
       <c r="T56" s="3"/>
       <c r="U56" s="3"/>
-    </row>
-    <row r="57" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V56" s="3"/>
+    </row>
+    <row r="57" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
-        <v>6400</v>
+        <v>3200</v>
       </c>
       <c r="E57" s="3">
-        <v>7700</v>
+        <v>3500</v>
       </c>
       <c r="F57" s="3">
-        <v>8800</v>
+        <v>5700</v>
       </c>
       <c r="G57" s="3">
-        <v>9600</v>
+        <v>6700</v>
       </c>
       <c r="H57" s="3">
-        <v>17100</v>
+        <v>7100</v>
       </c>
       <c r="I57" s="3">
-        <v>15300</v>
+        <v>12900</v>
       </c>
       <c r="J57" s="3">
+        <v>11300</v>
+      </c>
+      <c r="K57" s="3">
         <v>18900</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>8200</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>9900</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>5600</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>3500</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>2000</v>
       </c>
-      <c r="P57" s="3">
-        <v>0</v>
-      </c>
       <c r="Q57" s="3">
+        <v>0</v>
+      </c>
+      <c r="R57" s="3">
         <v>200</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>400</v>
       </c>
-      <c r="S57" s="3">
-        <v>0</v>
-      </c>
       <c r="T57" s="3">
         <v>0</v>
       </c>
       <c r="U57" s="3">
+        <v>0</v>
+      </c>
+      <c r="V57" s="3">
         <v>100</v>
       </c>
     </row>
-    <row r="58" spans="3:21" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
-        <v>48400</v>
+        <v>34300</v>
       </c>
       <c r="E58" s="3">
-        <v>47400</v>
+        <v>35300</v>
       </c>
       <c r="F58" s="3">
-        <v>0</v>
+        <v>35000</v>
       </c>
       <c r="G58" s="3">
-        <v>55300</v>
+        <v>0</v>
       </c>
       <c r="H58" s="3">
-        <v>0</v>
+        <v>40900</v>
       </c>
       <c r="I58" s="3">
         <v>0</v>
       </c>
       <c r="J58" s="3">
+        <v>0</v>
+      </c>
+      <c r="K58" s="3">
         <v>25700</v>
       </c>
-      <c r="K58" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="L58" s="3" t="s">
         <v>4</v>
       </c>
@@ -3370,262 +3504,277 @@
       <c r="O58" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="P58" s="3">
-        <v>0</v>
+      <c r="P58" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="Q58" s="3">
         <v>0</v>
       </c>
-      <c r="R58" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="S58" s="3">
+      <c r="R58" s="3">
+        <v>0</v>
+      </c>
+      <c r="S58" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="T58" s="3">
         <v>7000</v>
       </c>
-      <c r="T58" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="U58" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="59" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V58" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="59" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>9900</v>
+        <v>2700</v>
       </c>
       <c r="E59" s="3">
-        <v>8400</v>
+        <v>2600</v>
       </c>
       <c r="F59" s="3">
-        <v>7200</v>
+        <v>1500</v>
       </c>
       <c r="G59" s="3">
-        <v>8000</v>
+        <v>1100</v>
       </c>
       <c r="H59" s="3">
-        <v>7900</v>
+        <v>3000</v>
       </c>
       <c r="I59" s="3">
-        <v>13300</v>
+        <v>4000</v>
       </c>
       <c r="J59" s="3">
+        <v>9100</v>
+      </c>
+      <c r="K59" s="3">
         <v>9600</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>400</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>1200</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>500</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>1200</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>100</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>600</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>400</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>2400</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>1000</v>
       </c>
-      <c r="T59" s="3">
-        <v>0</v>
-      </c>
       <c r="U59" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="60" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V59" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="60" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
-        <v>64600</v>
+        <v>47400</v>
       </c>
       <c r="E60" s="3">
-        <v>63500</v>
+        <v>47200</v>
       </c>
       <c r="F60" s="3">
-        <v>16000</v>
+        <v>46900</v>
       </c>
       <c r="G60" s="3">
-        <v>72900</v>
+        <v>12100</v>
       </c>
       <c r="H60" s="3">
-        <v>25000</v>
+        <v>53900</v>
       </c>
       <c r="I60" s="3">
-        <v>28600</v>
+        <v>18800</v>
       </c>
       <c r="J60" s="3">
+        <v>21100</v>
+      </c>
+      <c r="K60" s="3">
         <v>54100</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>8700</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>11100</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>6000</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>4700</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>2100</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>600</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>500</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>2800</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>8000</v>
       </c>
-      <c r="T60" s="3">
-        <v>0</v>
-      </c>
       <c r="U60" s="3">
+        <v>0</v>
+      </c>
+      <c r="V60" s="3">
         <v>100</v>
       </c>
     </row>
-    <row r="61" spans="3:21" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
-        <v>10500</v>
+        <v>5800</v>
       </c>
       <c r="E61" s="3">
-        <v>8600</v>
+        <v>5300</v>
       </c>
       <c r="F61" s="3">
-        <v>46300</v>
+        <v>4100</v>
       </c>
       <c r="G61" s="3">
-        <v>4600</v>
+        <v>33800</v>
       </c>
       <c r="H61" s="3">
-        <v>53000</v>
+        <v>2700</v>
       </c>
       <c r="I61" s="3">
-        <v>62000</v>
+        <v>39300</v>
       </c>
       <c r="J61" s="3">
+        <v>45100</v>
+      </c>
+      <c r="K61" s="3">
         <v>5100</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>30000</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>27600</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>26200</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>23600</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>22400</v>
       </c>
-      <c r="P61" s="3">
-        <v>0</v>
-      </c>
       <c r="Q61" s="3">
-        <v>6700</v>
+        <v>0</v>
       </c>
       <c r="R61" s="3">
         <v>6700</v>
       </c>
       <c r="S61" s="3">
-        <v>0</v>
+        <v>6700</v>
       </c>
       <c r="T61" s="3">
-        <v>7000</v>
+        <v>0</v>
       </c>
       <c r="U61" s="3">
         <v>7000</v>
       </c>
-    </row>
-    <row r="62" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V61" s="3">
+        <v>7000</v>
+      </c>
+    </row>
+    <row r="62" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
-        <v>3000</v>
+        <v>3200</v>
       </c>
       <c r="E62" s="3">
         <v>2900</v>
       </c>
       <c r="F62" s="3">
-        <v>3100</v>
+        <v>2800</v>
       </c>
       <c r="G62" s="3">
-        <v>1700</v>
+        <v>3000</v>
       </c>
       <c r="H62" s="3">
-        <v>1900</v>
+        <v>1200</v>
       </c>
       <c r="I62" s="3">
-        <v>1700</v>
+        <v>1400</v>
       </c>
       <c r="J62" s="3">
+        <v>1300</v>
+      </c>
+      <c r="K62" s="3">
         <v>1800</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>20100</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>19500</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>34900</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>39400</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>29300</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>1300</v>
-      </c>
-      <c r="Q62" s="3">
-        <v>2000</v>
       </c>
       <c r="R62" s="3">
         <v>2000</v>
       </c>
       <c r="S62" s="3">
+        <v>2000</v>
+      </c>
+      <c r="T62" s="3">
         <v>2700</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>3200</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>3000</v>
       </c>
     </row>
-    <row r="63" spans="3:21" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -3683,8 +3832,11 @@
       <c r="U63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -3742,8 +3894,11 @@
       <c r="U64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -3801,67 +3956,73 @@
       <c r="U65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
-        <v>78100</v>
+        <v>58600</v>
       </c>
       <c r="E66" s="3">
-        <v>74900</v>
+        <v>57100</v>
       </c>
       <c r="F66" s="3">
-        <v>65400</v>
+        <v>55300</v>
       </c>
       <c r="G66" s="3">
-        <v>79200</v>
+        <v>49500</v>
       </c>
       <c r="H66" s="3">
-        <v>79800</v>
+        <v>58500</v>
       </c>
       <c r="I66" s="3">
-        <v>92300</v>
+        <v>60300</v>
       </c>
       <c r="J66" s="3">
+        <v>68200</v>
+      </c>
+      <c r="K66" s="3">
         <v>61000</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>58800</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>58200</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>67100</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>67600</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>53900</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>1900</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>9300</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>11500</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>10700</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>10200</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>10100</v>
       </c>
     </row>
-    <row r="67" spans="2:21" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -3883,8 +4044,9 @@
       <c r="S67" s="3"/>
       <c r="T67" s="3"/>
       <c r="U67" s="3"/>
-    </row>
-    <row r="68" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V67" s="3"/>
+    </row>
+    <row r="68" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -3942,8 +4104,11 @@
       <c r="U68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -4001,8 +4166,11 @@
       <c r="U69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -4060,8 +4228,11 @@
       <c r="U70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -4119,67 +4290,73 @@
       <c r="U71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
-        <v>-237800</v>
+        <v>-197100</v>
       </c>
       <c r="E72" s="3">
-        <v>-232400</v>
+        <v>-192400</v>
       </c>
       <c r="F72" s="3">
-        <v>-219900</v>
+        <v>-190200</v>
       </c>
       <c r="G72" s="3">
-        <v>-173000</v>
+        <v>-185900</v>
       </c>
       <c r="H72" s="3">
-        <v>-171400</v>
+        <v>-147800</v>
       </c>
       <c r="I72" s="3">
-        <v>-183600</v>
+        <v>-144100</v>
       </c>
       <c r="J72" s="3">
+        <v>-149700</v>
+      </c>
+      <c r="K72" s="3">
         <v>-162900</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-173900</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>-166600</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>-174000</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>-176800</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>-161500</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>-151200</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>-145000</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>-143000</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>-145900</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>-145200</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>-143600</v>
       </c>
     </row>
-    <row r="73" spans="2:21" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -4237,8 +4414,11 @@
       <c r="U73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -4296,8 +4476,11 @@
       <c r="U74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -4355,67 +4538,73 @@
       <c r="U75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
-        <v>70000</v>
+        <v>48500</v>
       </c>
       <c r="E76" s="3">
-        <v>74500</v>
+        <v>51200</v>
       </c>
       <c r="F76" s="3">
-        <v>83300</v>
+        <v>55000</v>
       </c>
       <c r="G76" s="3">
-        <v>131100</v>
+        <v>63100</v>
       </c>
       <c r="H76" s="3">
-        <v>119100</v>
+        <v>96900</v>
       </c>
       <c r="I76" s="3">
-        <v>106500</v>
+        <v>90000</v>
       </c>
       <c r="J76" s="3">
+        <v>78700</v>
+      </c>
+      <c r="K76" s="3">
         <v>126500</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>112100</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>118200</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>104200</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>100000</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>107000</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>108200</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>104700</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>92200</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>88000</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>87200</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>88700</v>
       </c>
     </row>
-    <row r="77" spans="2:21" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -4473,131 +4662,140 @@
       <c r="U77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:22" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:21" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45565</v>
+      </c>
+      <c r="E80" s="2">
         <v>45473</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45382</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45291</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45199</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45107</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45016</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44926</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44834</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44742</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44651</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44561</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44469</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44377</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44286</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44196</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44104</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44012</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>43921</v>
       </c>
     </row>
-    <row r="81" spans="3:21" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
-        <v>-5800</v>
+        <v>-2200</v>
       </c>
       <c r="E81" s="3">
-        <v>-12200</v>
+        <v>-4200</v>
       </c>
       <c r="F81" s="3">
-        <v>-45500</v>
+        <v>-9000</v>
       </c>
       <c r="G81" s="3">
-        <v>-9200</v>
+        <v>-34400</v>
       </c>
       <c r="H81" s="3">
-        <v>11800</v>
+        <v>-6800</v>
       </c>
       <c r="I81" s="3">
-        <v>-20300</v>
+        <v>8900</v>
       </c>
       <c r="J81" s="3">
+        <v>-15000</v>
+      </c>
+      <c r="K81" s="3">
         <v>10300</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>-7600</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>7500</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>2300</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>-15500</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>-10500</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>-6400</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>-2500</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>2900</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>-1500</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>-1700</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>-2100</v>
       </c>
     </row>
-    <row r="82" spans="3:21" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -4619,8 +4817,9 @@
       <c r="S82" s="3"/>
       <c r="T82" s="3"/>
       <c r="U82" s="3"/>
-    </row>
-    <row r="83" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V82" s="3"/>
+    </row>
+    <row r="83" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
@@ -4636,14 +4835,14 @@
       <c r="G83" s="3">
         <v>0</v>
       </c>
-      <c r="H83" s="3">
-        <v>0</v>
+      <c r="H83" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="I83" s="3">
         <v>0</v>
       </c>
-      <c r="J83" s="3" t="s">
-        <v>4</v>
+      <c r="J83" s="3">
+        <v>0</v>
       </c>
       <c r="K83" s="3" t="s">
         <v>4</v>
@@ -4651,14 +4850,14 @@
       <c r="L83" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="M83" s="3">
-        <v>0</v>
+      <c r="M83" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="N83" s="3">
         <v>0</v>
       </c>
-      <c r="O83" s="3" t="s">
-        <v>4</v>
+      <c r="O83" s="3">
+        <v>0</v>
       </c>
       <c r="P83" s="3" t="s">
         <v>4</v>
@@ -4678,8 +4877,11 @@
       <c r="U83" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="84" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V83" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="84" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -4737,8 +4939,11 @@
       <c r="U84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -4796,8 +5001,11 @@
       <c r="U85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -4855,8 +5063,11 @@
       <c r="U86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -4914,8 +5125,11 @@
       <c r="U87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -4973,67 +5187,73 @@
       <c r="U88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
-        <v>-3900</v>
+        <v>-2200</v>
       </c>
       <c r="E89" s="3">
-        <v>-4100</v>
+        <v>-2800</v>
       </c>
       <c r="F89" s="3">
-        <v>-6000</v>
+        <v>-3000</v>
       </c>
       <c r="G89" s="3">
-        <v>-12000</v>
+        <v>-4500</v>
       </c>
       <c r="H89" s="3">
-        <v>-4000</v>
+        <v>-8900</v>
       </c>
       <c r="I89" s="3">
-        <v>-1000</v>
+        <v>-3000</v>
       </c>
       <c r="J89" s="3">
+        <v>-700</v>
+      </c>
+      <c r="K89" s="3">
         <v>-6600</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>-500</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>-5300</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>-3500</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>-4900</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>-5300</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>-3600</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>-3100</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>-1500</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>-1200</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>-1100</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>-1800</v>
       </c>
     </row>
-    <row r="90" spans="3:21" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -5055,56 +5275,57 @@
       <c r="S90" s="3"/>
       <c r="T90" s="3"/>
       <c r="U90" s="3"/>
-    </row>
-    <row r="91" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V90" s="3"/>
+    </row>
+    <row r="91" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
-        <v>-300</v>
+        <v>-100</v>
       </c>
       <c r="E91" s="3">
+        <v>200</v>
+      </c>
+      <c r="F91" s="3">
+        <v>-400</v>
+      </c>
+      <c r="G91" s="3">
+        <v>400</v>
+      </c>
+      <c r="H91" s="3">
+        <v>400</v>
+      </c>
+      <c r="I91" s="3">
+        <v>-1900</v>
+      </c>
+      <c r="J91" s="3">
+        <v>-9100</v>
+      </c>
+      <c r="K91" s="3">
+        <v>-15600</v>
+      </c>
+      <c r="L91" s="3">
+        <v>-18800</v>
+      </c>
+      <c r="M91" s="3">
+        <v>-8700</v>
+      </c>
+      <c r="N91" s="3">
+        <v>-4500</v>
+      </c>
+      <c r="O91" s="3">
+        <v>-6100</v>
+      </c>
+      <c r="P91" s="3">
         <v>-600</v>
       </c>
-      <c r="F91" s="3">
+      <c r="Q91" s="3">
+        <v>500</v>
+      </c>
+      <c r="R91" s="3">
         <v>-500</v>
       </c>
-      <c r="G91" s="3">
-        <v>-500</v>
-      </c>
-      <c r="H91" s="3">
-        <v>-2500</v>
-      </c>
-      <c r="I91" s="3">
-        <v>-12300</v>
-      </c>
-      <c r="J91" s="3">
-        <v>-15600</v>
-      </c>
-      <c r="K91" s="3">
-        <v>-18800</v>
-      </c>
-      <c r="L91" s="3">
-        <v>-8700</v>
-      </c>
-      <c r="M91" s="3">
-        <v>-4500</v>
-      </c>
-      <c r="N91" s="3">
-        <v>-6100</v>
-      </c>
-      <c r="O91" s="3">
-        <v>-600</v>
-      </c>
-      <c r="P91" s="3">
-        <v>500</v>
-      </c>
-      <c r="Q91" s="3">
-        <v>-500</v>
-      </c>
-      <c r="R91" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="S91" s="3" t="s">
         <v>4</v>
       </c>
@@ -5114,8 +5335,11 @@
       <c r="U91" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="92" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V91" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="92" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -5173,8 +5397,11 @@
       <c r="U92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -5232,53 +5459,56 @@
       <c r="U93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
-        <v>1000</v>
+        <v>300</v>
       </c>
       <c r="E94" s="3">
-        <v>-100</v>
+        <v>700</v>
       </c>
       <c r="F94" s="3">
+        <v>0</v>
+      </c>
+      <c r="G94" s="3">
+        <v>-1200</v>
+      </c>
+      <c r="H94" s="3">
+        <v>600</v>
+      </c>
+      <c r="I94" s="3">
+        <v>-800</v>
+      </c>
+      <c r="J94" s="3">
+        <v>-9100</v>
+      </c>
+      <c r="K94" s="3">
+        <v>-10900</v>
+      </c>
+      <c r="L94" s="3">
+        <v>-18800</v>
+      </c>
+      <c r="M94" s="3">
+        <v>-8700</v>
+      </c>
+      <c r="N94" s="3">
+        <v>-5100</v>
+      </c>
+      <c r="O94" s="3">
+        <v>-6100</v>
+      </c>
+      <c r="P94" s="3">
+        <v>-500</v>
+      </c>
+      <c r="Q94" s="3">
         <v>-1500</v>
       </c>
-      <c r="G94" s="3">
-        <v>800</v>
-      </c>
-      <c r="H94" s="3">
-        <v>-1000</v>
-      </c>
-      <c r="I94" s="3">
-        <v>-12200</v>
-      </c>
-      <c r="J94" s="3">
-        <v>-10900</v>
-      </c>
-      <c r="K94" s="3">
-        <v>-18800</v>
-      </c>
-      <c r="L94" s="3">
-        <v>-8700</v>
-      </c>
-      <c r="M94" s="3">
-        <v>-5100</v>
-      </c>
-      <c r="N94" s="3">
-        <v>-6100</v>
-      </c>
-      <c r="O94" s="3">
-        <v>-500</v>
-      </c>
-      <c r="P94" s="3">
-        <v>-1500</v>
-      </c>
-      <c r="Q94" s="3">
-        <v>0</v>
-      </c>
       <c r="R94" s="3">
         <v>0</v>
       </c>
@@ -5291,8 +5521,11 @@
       <c r="U94" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="95" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V94" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="95" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -5314,31 +5547,32 @@
       <c r="S95" s="3"/>
       <c r="T95" s="3"/>
       <c r="U95" s="3"/>
-    </row>
-    <row r="96" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V95" s="3"/>
+    </row>
+    <row r="96" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
-      <c r="D96" s="3">
-        <v>0</v>
-      </c>
-      <c r="E96" s="3">
-        <v>0</v>
-      </c>
-      <c r="F96" s="3">
-        <v>0</v>
-      </c>
-      <c r="G96" s="3">
-        <v>0</v>
-      </c>
-      <c r="H96" s="3">
-        <v>0</v>
-      </c>
-      <c r="I96" s="3">
-        <v>0</v>
-      </c>
-      <c r="J96" s="3">
-        <v>0</v>
+      <c r="D96" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="E96" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="F96" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="G96" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="H96" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="I96" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="J96" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="K96" s="3">
         <v>0</v>
@@ -5373,8 +5607,11 @@
       <c r="U96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -5432,8 +5669,11 @@
       <c r="U97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -5491,8 +5731,11 @@
       <c r="U98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -5550,67 +5793,73 @@
       <c r="U99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
-        <v>2000</v>
+        <v>700</v>
       </c>
       <c r="E100" s="3">
-        <v>2300</v>
+        <v>1400</v>
       </c>
       <c r="F100" s="3">
-        <v>-100</v>
+        <v>1700</v>
       </c>
       <c r="G100" s="3">
-        <v>20100</v>
+        <v>0</v>
       </c>
       <c r="H100" s="3">
-        <v>0</v>
+        <v>14900</v>
       </c>
       <c r="I100" s="3">
-        <v>16500</v>
+        <v>0</v>
       </c>
       <c r="J100" s="3">
+        <v>12200</v>
+      </c>
+      <c r="K100" s="3">
         <v>6500</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-2500</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>2900</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>1600</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>8500</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>54900</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>600</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>14900</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>1100</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>2400</v>
       </c>
-      <c r="T100" s="3">
-        <v>0</v>
-      </c>
       <c r="U100" s="3">
+        <v>0</v>
+      </c>
+      <c r="V100" s="3">
         <v>2100</v>
       </c>
     </row>
-    <row r="101" spans="3:21" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -5621,19 +5870,19 @@
         <v>0</v>
       </c>
       <c r="F101" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="G101" s="3">
         <v>0</v>
       </c>
       <c r="H101" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="I101" s="3">
         <v>0</v>
       </c>
       <c r="J101" s="3">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="K101" s="3">
         <v>0</v>
@@ -5642,89 +5891,95 @@
         <v>0</v>
       </c>
       <c r="M101" s="3">
+        <v>0</v>
+      </c>
+      <c r="N101" s="3">
         <v>200</v>
       </c>
-      <c r="N101" s="3">
+      <c r="O101" s="3">
         <v>-100</v>
       </c>
-      <c r="O101" s="3">
+      <c r="P101" s="3">
         <v>600</v>
       </c>
-      <c r="P101" s="3">
-        <v>0</v>
-      </c>
       <c r="Q101" s="3">
         <v>0</v>
       </c>
       <c r="R101" s="3">
+        <v>0</v>
+      </c>
+      <c r="S101" s="3">
         <v>-100</v>
       </c>
-      <c r="S101" s="3">
-        <v>0</v>
-      </c>
       <c r="T101" s="3">
         <v>0</v>
       </c>
       <c r="U101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
-        <v>-800</v>
+        <v>-1100</v>
       </c>
       <c r="E102" s="3">
-        <v>-1900</v>
+        <v>-600</v>
       </c>
       <c r="F102" s="3">
-        <v>-7500</v>
+        <v>-1400</v>
       </c>
       <c r="G102" s="3">
-        <v>8800</v>
+        <v>-5700</v>
       </c>
       <c r="H102" s="3">
-        <v>-5000</v>
+        <v>6500</v>
       </c>
       <c r="I102" s="3">
-        <v>3300</v>
+        <v>-3800</v>
       </c>
       <c r="J102" s="3">
+        <v>2400</v>
+      </c>
+      <c r="K102" s="3">
         <v>-11000</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-21800</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-11200</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-6700</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-2600</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>49700</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>-4500</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>11800</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>-500</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>1100</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>-1100</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>200</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/ELBM_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/ELBM_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="230" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="249" uniqueCount="92">
   <si>
     <t>ELBM</t>
   </si>
@@ -656,103 +656,110 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:V102"/>
+  <dimension ref="A5:X102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.42578125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="16" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="20" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="22" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:24" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:24" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45747</v>
+      </c>
+      <c r="E7" s="2">
+        <v>45657</v>
+      </c>
+      <c r="F7" s="2">
         <v>45565</v>
       </c>
-      <c r="E7" s="2">
+      <c r="G7" s="2">
         <v>45473</v>
       </c>
-      <c r="F7" s="2">
+      <c r="H7" s="2">
         <v>45382</v>
       </c>
-      <c r="G7" s="2">
+      <c r="I7" s="2">
         <v>45291</v>
       </c>
-      <c r="H7" s="2">
+      <c r="J7" s="2">
         <v>45199</v>
       </c>
-      <c r="I7" s="2">
+      <c r="K7" s="2">
         <v>45107</v>
       </c>
-      <c r="J7" s="2">
+      <c r="L7" s="2">
         <v>45016</v>
       </c>
-      <c r="K7" s="2">
+      <c r="M7" s="2">
         <v>44926</v>
       </c>
-      <c r="L7" s="2">
+      <c r="N7" s="2">
         <v>44834</v>
       </c>
-      <c r="M7" s="2">
+      <c r="O7" s="2">
         <v>44742</v>
       </c>
-      <c r="N7" s="2">
+      <c r="P7" s="2">
         <v>44651</v>
       </c>
-      <c r="O7" s="2">
+      <c r="Q7" s="2">
         <v>44561</v>
       </c>
-      <c r="P7" s="2">
+      <c r="R7" s="2">
         <v>44469</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="S7" s="2">
         <v>44377</v>
       </c>
-      <c r="R7" s="2">
+      <c r="T7" s="2">
         <v>44286</v>
       </c>
-      <c r="S7" s="2">
+      <c r="U7" s="2">
         <v>44196</v>
       </c>
-      <c r="T7" s="2">
+      <c r="V7" s="2">
         <v>44104</v>
       </c>
-      <c r="U7" s="2">
+      <c r="W7" s="2">
         <v>44012</v>
       </c>
-      <c r="V7" s="2">
+      <c r="X7" s="2">
         <v>43921</v>
       </c>
     </row>
-    <row r="8" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:24" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
@@ -777,11 +784,11 @@
       <c r="J8" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="K8" s="3">
-        <v>0</v>
-      </c>
-      <c r="L8" s="3">
-        <v>0</v>
+      <c r="K8" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="L8" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="M8" s="3">
         <v>0</v>
@@ -813,8 +820,14 @@
       <c r="V8" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="9" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W8" s="3">
+        <v>0</v>
+      </c>
+      <c r="X8" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:24" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
@@ -875,8 +888,14 @@
       <c r="V9" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="10" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W9" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="X9" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="10" spans="1:24" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
@@ -937,8 +956,14 @@
       <c r="V10" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="11" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W10" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="X10" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="11" spans="1:24" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -961,8 +986,10 @@
       <c r="T11" s="3"/>
       <c r="U11" s="3"/>
       <c r="V11" s="3"/>
-    </row>
-    <row r="12" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W11" s="3"/>
+      <c r="X11" s="3"/>
+    </row>
+    <row r="12" spans="1:24" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -987,44 +1014,50 @@
       <c r="J12" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="K12" s="3">
+      <c r="K12" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="L12" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="M12" s="3">
         <v>600</v>
       </c>
-      <c r="L12" s="3">
+      <c r="N12" s="3">
         <v>1300</v>
       </c>
-      <c r="M12" s="3">
+      <c r="O12" s="3">
         <v>1100</v>
       </c>
-      <c r="N12" s="3">
+      <c r="P12" s="3">
         <v>400</v>
       </c>
-      <c r="O12" s="3">
+      <c r="Q12" s="3">
         <v>2900</v>
       </c>
-      <c r="P12" s="3">
+      <c r="R12" s="3">
         <v>1200</v>
       </c>
-      <c r="Q12" s="3">
+      <c r="S12" s="3">
         <v>400</v>
-      </c>
-      <c r="R12" s="3">
-        <v>100</v>
-      </c>
-      <c r="S12" s="3">
-        <v>300</v>
       </c>
       <c r="T12" s="3">
         <v>100</v>
       </c>
       <c r="U12" s="3">
-        <v>0</v>
+        <v>300</v>
       </c>
       <c r="V12" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="13" spans="1:22" x14ac:dyDescent="0.2">
+        <v>100</v>
+      </c>
+      <c r="W12" s="3">
+        <v>0</v>
+      </c>
+      <c r="X12" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" spans="1:24" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1085,8 +1118,14 @@
       <c r="V13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W13" s="3">
+        <v>0</v>
+      </c>
+      <c r="X13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:24" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -1094,61 +1133,67 @@
         <v>0</v>
       </c>
       <c r="E14" s="3">
+        <v>0</v>
+      </c>
+      <c r="F14" s="3">
+        <v>0</v>
+      </c>
+      <c r="G14" s="3">
         <v>-100</v>
       </c>
-      <c r="F14" s="3">
+      <c r="H14" s="3">
         <v>-100</v>
       </c>
-      <c r="G14" s="3">
-        <v>38200</v>
-      </c>
-      <c r="H14" s="3">
+      <c r="I14" s="3">
+        <v>39300</v>
+      </c>
+      <c r="J14" s="3">
         <v>200</v>
       </c>
-      <c r="I14" s="3">
-        <v>0</v>
-      </c>
-      <c r="J14" s="3">
+      <c r="K14" s="3">
+        <v>0</v>
+      </c>
+      <c r="L14" s="3">
         <v>13800</v>
       </c>
-      <c r="K14" s="3">
+      <c r="M14" s="3">
         <v>-1300</v>
       </c>
-      <c r="L14" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="M14" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="N14" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="O14" s="3">
-        <v>0</v>
-      </c>
-      <c r="P14" s="3">
-        <v>0</v>
+      <c r="O14" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="P14" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="Q14" s="3">
+        <v>0</v>
+      </c>
+      <c r="R14" s="3">
+        <v>0</v>
+      </c>
+      <c r="S14" s="3">
         <v>1600</v>
       </c>
-      <c r="R14" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="S14" s="3">
+      <c r="T14" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="U14" s="3">
         <v>-5700</v>
       </c>
-      <c r="T14" s="3">
-        <v>0</v>
-      </c>
-      <c r="U14" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="V14" s="3" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="15" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="V14" s="3">
+        <v>0</v>
+      </c>
+      <c r="W14" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="X14" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="15" spans="1:24" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1209,8 +1254,14 @@
       <c r="V15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W15" s="3">
+        <v>0</v>
+      </c>
+      <c r="X15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:24" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1230,132 +1281,146 @@
       <c r="T16" s="3"/>
       <c r="U16" s="3"/>
       <c r="V16" s="3"/>
-    </row>
-    <row r="17" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W16" s="3"/>
+      <c r="X16" s="3"/>
+    </row>
+    <row r="17" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
-        <v>2400</v>
+        <v>2500</v>
       </c>
       <c r="E17" s="3">
         <v>2400</v>
       </c>
       <c r="F17" s="3">
+        <v>2400</v>
+      </c>
+      <c r="G17" s="3">
+        <v>2400</v>
+      </c>
+      <c r="H17" s="3">
         <v>2300</v>
       </c>
-      <c r="G17" s="3">
+      <c r="I17" s="3">
         <v>900</v>
       </c>
-      <c r="H17" s="3">
+      <c r="J17" s="3">
         <v>2900</v>
       </c>
-      <c r="I17" s="3">
+      <c r="K17" s="3">
         <v>3300</v>
       </c>
-      <c r="J17" s="3">
+      <c r="L17" s="3">
         <v>2800</v>
       </c>
-      <c r="K17" s="3">
+      <c r="M17" s="3">
         <v>4200</v>
       </c>
-      <c r="L17" s="3">
+      <c r="N17" s="3">
         <v>4800</v>
       </c>
-      <c r="M17" s="3">
+      <c r="O17" s="3">
         <v>3900</v>
       </c>
-      <c r="N17" s="3">
+      <c r="P17" s="3">
         <v>2500</v>
       </c>
-      <c r="O17" s="3">
+      <c r="Q17" s="3">
         <v>6600</v>
       </c>
-      <c r="P17" s="3">
+      <c r="R17" s="3">
         <v>6500</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="S17" s="3">
         <v>5300</v>
       </c>
-      <c r="R17" s="3">
+      <c r="T17" s="3">
         <v>2300</v>
       </c>
-      <c r="S17" s="3">
+      <c r="U17" s="3">
         <v>-3000</v>
       </c>
-      <c r="T17" s="3">
+      <c r="V17" s="3">
         <v>1400</v>
       </c>
-      <c r="U17" s="3">
+      <c r="W17" s="3">
         <v>1500</v>
       </c>
-      <c r="V17" s="3">
+      <c r="X17" s="3">
         <v>1800</v>
       </c>
     </row>
-    <row r="18" spans="3:22" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
-        <v>-2400</v>
+        <v>-2500</v>
       </c>
       <c r="E18" s="3">
         <v>-2400</v>
       </c>
       <c r="F18" s="3">
+        <v>-2400</v>
+      </c>
+      <c r="G18" s="3">
+        <v>-2400</v>
+      </c>
+      <c r="H18" s="3">
         <v>-2300</v>
       </c>
-      <c r="G18" s="3">
+      <c r="I18" s="3">
         <v>-900</v>
       </c>
-      <c r="H18" s="3">
+      <c r="J18" s="3">
         <v>-2900</v>
       </c>
-      <c r="I18" s="3">
+      <c r="K18" s="3">
         <v>-3300</v>
       </c>
-      <c r="J18" s="3">
+      <c r="L18" s="3">
         <v>-2800</v>
       </c>
-      <c r="K18" s="3">
+      <c r="M18" s="3">
         <v>-4200</v>
       </c>
-      <c r="L18" s="3">
+      <c r="N18" s="3">
         <v>-4800</v>
       </c>
-      <c r="M18" s="3">
+      <c r="O18" s="3">
         <v>-3900</v>
       </c>
-      <c r="N18" s="3">
+      <c r="P18" s="3">
         <v>-2500</v>
       </c>
-      <c r="O18" s="3">
+      <c r="Q18" s="3">
         <v>-6600</v>
       </c>
-      <c r="P18" s="3">
+      <c r="R18" s="3">
         <v>-6500</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="S18" s="3">
         <v>-5300</v>
       </c>
-      <c r="R18" s="3">
+      <c r="T18" s="3">
         <v>-2300</v>
       </c>
-      <c r="S18" s="3">
+      <c r="U18" s="3">
         <v>3000</v>
       </c>
-      <c r="T18" s="3">
+      <c r="V18" s="3">
         <v>-1400</v>
       </c>
-      <c r="U18" s="3">
+      <c r="W18" s="3">
         <v>-1500</v>
       </c>
-      <c r="V18" s="3">
+      <c r="X18" s="3">
         <v>-1800</v>
       </c>
     </row>
-    <row r="19" spans="3:22" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1378,164 +1443,178 @@
       <c r="T19" s="3"/>
       <c r="U19" s="3"/>
       <c r="V19" s="3"/>
-    </row>
-    <row r="20" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W19" s="3"/>
+      <c r="X19" s="3"/>
+    </row>
+    <row r="20" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>6300</v>
+      </c>
+      <c r="E20" s="3">
+        <v>2100</v>
+      </c>
+      <c r="F20" s="3">
         <v>-2200</v>
       </c>
-      <c r="E20" s="3">
+      <c r="G20" s="3">
         <v>900</v>
       </c>
-      <c r="F20" s="3">
+      <c r="H20" s="3">
         <v>6000</v>
       </c>
-      <c r="G20" s="3">
+      <c r="I20" s="3">
         <v>-11100</v>
       </c>
-      <c r="H20" s="3">
+      <c r="J20" s="3">
         <v>3700</v>
       </c>
-      <c r="I20" s="3">
+      <c r="K20" s="3">
         <v>-12100</v>
       </c>
-      <c r="J20" s="3">
+      <c r="L20" s="3">
         <v>-1500</v>
       </c>
-      <c r="K20" s="3">
+      <c r="M20" s="3">
         <v>14500</v>
       </c>
-      <c r="L20" s="3">
+      <c r="N20" s="3">
         <v>-2800</v>
       </c>
-      <c r="M20" s="3">
+      <c r="O20" s="3">
         <v>11400</v>
       </c>
-      <c r="N20" s="3">
+      <c r="P20" s="3">
         <v>4800</v>
       </c>
-      <c r="O20" s="3">
+      <c r="Q20" s="3">
         <v>-8900</v>
       </c>
-      <c r="P20" s="3">
+      <c r="R20" s="3">
         <v>-4000</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="S20" s="3">
         <v>-1100</v>
-      </c>
-      <c r="R20" s="3">
-        <v>-100</v>
-      </c>
-      <c r="S20" s="3">
-        <v>-100</v>
       </c>
       <c r="T20" s="3">
         <v>-100</v>
       </c>
       <c r="U20" s="3">
+        <v>-100</v>
+      </c>
+      <c r="V20" s="3">
+        <v>-100</v>
+      </c>
+      <c r="W20" s="3">
         <v>-200</v>
       </c>
-      <c r="V20" s="3">
+      <c r="X20" s="3">
         <v>-300</v>
       </c>
     </row>
-    <row r="21" spans="3:22" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>-8800</v>
+      </c>
+      <c r="E21" s="3">
+        <v>-4500</v>
+      </c>
+      <c r="F21" s="3">
         <v>-200</v>
       </c>
-      <c r="E21" s="3">
+      <c r="G21" s="3">
         <v>-3300</v>
       </c>
-      <c r="F21" s="3">
+      <c r="H21" s="3">
         <v>-8300</v>
       </c>
-      <c r="G21" s="3">
+      <c r="I21" s="3">
         <v>10100</v>
       </c>
-      <c r="H21" s="3">
+      <c r="J21" s="3">
         <v>-6700</v>
       </c>
-      <c r="I21" s="3">
+      <c r="K21" s="3">
         <v>8800</v>
       </c>
-      <c r="J21" s="3">
+      <c r="L21" s="3">
         <v>-1300</v>
       </c>
-      <c r="K21" s="3">
+      <c r="M21" s="3">
         <v>10400</v>
       </c>
-      <c r="L21" s="3">
+      <c r="N21" s="3">
         <v>-7600</v>
       </c>
-      <c r="M21" s="3">
+      <c r="O21" s="3">
         <v>7500</v>
       </c>
-      <c r="N21" s="3">
+      <c r="P21" s="3">
         <v>2300</v>
       </c>
-      <c r="O21" s="3">
+      <c r="Q21" s="3">
         <v>-15500</v>
       </c>
-      <c r="P21" s="3">
+      <c r="R21" s="3">
         <v>-10500</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="S21" s="3">
         <v>-6400</v>
       </c>
-      <c r="R21" s="3">
+      <c r="T21" s="3">
         <v>-2400</v>
       </c>
-      <c r="S21" s="3">
+      <c r="U21" s="3">
         <v>2900</v>
       </c>
-      <c r="T21" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="U21" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="V21" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="22" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W21" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="X21" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="22" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="D22" s="3">
+      <c r="D22" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="E22" s="3">
+        <v>1500</v>
+      </c>
+      <c r="F22" s="3">
         <v>2000</v>
       </c>
-      <c r="E22" s="3">
+      <c r="G22" s="3">
         <v>1000</v>
       </c>
-      <c r="F22" s="3">
+      <c r="H22" s="3">
         <v>700</v>
       </c>
-      <c r="G22" s="3">
+      <c r="I22" s="3">
         <v>6200</v>
       </c>
-      <c r="H22" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="I22" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="J22" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="K22" s="3">
-        <v>0</v>
+      <c r="K22" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="L22" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="M22" s="3" t="s">
-        <v>4</v>
+      <c r="M22" s="3">
+        <v>0</v>
       </c>
       <c r="N22" s="3" t="s">
         <v>4</v>
@@ -1543,91 +1622,103 @@
       <c r="O22" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="P22" s="3">
-        <v>0</v>
-      </c>
-      <c r="Q22" s="3">
-        <v>0</v>
+      <c r="P22" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Q22" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="R22" s="3">
+        <v>0</v>
+      </c>
+      <c r="S22" s="3">
+        <v>0</v>
+      </c>
+      <c r="T22" s="3">
         <v>100</v>
       </c>
-      <c r="S22" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="T22" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="U22" s="3" t="s">
         <v>4</v>
       </c>
       <c r="V22" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="23" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W22" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="X22" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="23" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-8800</v>
+      </c>
+      <c r="E23" s="3">
+        <v>-6000</v>
+      </c>
+      <c r="F23" s="3">
         <v>-2200</v>
       </c>
-      <c r="E23" s="3">
+      <c r="G23" s="3">
         <v>-4200</v>
       </c>
-      <c r="F23" s="3">
+      <c r="H23" s="3">
         <v>-9000</v>
       </c>
-      <c r="G23" s="3">
-        <v>-34400</v>
-      </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
+        <v>-35500</v>
+      </c>
+      <c r="J23" s="3">
         <v>-6800</v>
       </c>
-      <c r="I23" s="3">
+      <c r="K23" s="3">
         <v>8900</v>
       </c>
-      <c r="J23" s="3">
+      <c r="L23" s="3">
         <v>-15000</v>
       </c>
-      <c r="K23" s="3">
+      <c r="M23" s="3">
         <v>10300</v>
       </c>
-      <c r="L23" s="3">
+      <c r="N23" s="3">
         <v>-7600</v>
       </c>
-      <c r="M23" s="3">
+      <c r="O23" s="3">
         <v>7500</v>
       </c>
-      <c r="N23" s="3">
+      <c r="P23" s="3">
         <v>2300</v>
       </c>
-      <c r="O23" s="3">
+      <c r="Q23" s="3">
         <v>-15500</v>
       </c>
-      <c r="P23" s="3">
+      <c r="R23" s="3">
         <v>-10500</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="S23" s="3">
         <v>-6400</v>
       </c>
-      <c r="R23" s="3">
+      <c r="T23" s="3">
         <v>-2500</v>
       </c>
-      <c r="S23" s="3">
+      <c r="U23" s="3">
         <v>2900</v>
       </c>
-      <c r="T23" s="3">
+      <c r="V23" s="3">
         <v>-1500</v>
       </c>
-      <c r="U23" s="3">
+      <c r="W23" s="3">
         <v>-1700</v>
       </c>
-      <c r="V23" s="3">
+      <c r="X23" s="3">
         <v>-2100</v>
       </c>
     </row>
-    <row r="24" spans="3:22" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
@@ -1652,11 +1743,11 @@
       <c r="J24" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="K24" s="3">
-        <v>0</v>
-      </c>
-      <c r="L24" s="3">
-        <v>0</v>
+      <c r="K24" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="L24" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="M24" s="3">
         <v>0</v>
@@ -1688,8 +1779,14 @@
       <c r="V24" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="25" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W24" s="3">
+        <v>0</v>
+      </c>
+      <c r="X24" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1750,132 +1847,150 @@
       <c r="V25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W25" s="3">
+        <v>0</v>
+      </c>
+      <c r="X25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-8800</v>
+      </c>
+      <c r="E26" s="3">
+        <v>-6000</v>
+      </c>
+      <c r="F26" s="3">
         <v>-2200</v>
       </c>
-      <c r="E26" s="3">
+      <c r="G26" s="3">
         <v>-4200</v>
       </c>
-      <c r="F26" s="3">
+      <c r="H26" s="3">
         <v>-9000</v>
       </c>
-      <c r="G26" s="3">
-        <v>-34400</v>
-      </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
+        <v>-35500</v>
+      </c>
+      <c r="J26" s="3">
         <v>-6800</v>
       </c>
-      <c r="I26" s="3">
+      <c r="K26" s="3">
         <v>8900</v>
       </c>
-      <c r="J26" s="3">
+      <c r="L26" s="3">
         <v>-15000</v>
       </c>
-      <c r="K26" s="3">
+      <c r="M26" s="3">
         <v>10300</v>
       </c>
-      <c r="L26" s="3">
+      <c r="N26" s="3">
         <v>-7600</v>
       </c>
-      <c r="M26" s="3">
+      <c r="O26" s="3">
         <v>7500</v>
       </c>
-      <c r="N26" s="3">
+      <c r="P26" s="3">
         <v>2300</v>
       </c>
-      <c r="O26" s="3">
+      <c r="Q26" s="3">
         <v>-15500</v>
       </c>
-      <c r="P26" s="3">
+      <c r="R26" s="3">
         <v>-10500</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="S26" s="3">
         <v>-6400</v>
       </c>
-      <c r="R26" s="3">
+      <c r="T26" s="3">
         <v>-2500</v>
       </c>
-      <c r="S26" s="3">
+      <c r="U26" s="3">
         <v>2900</v>
       </c>
-      <c r="T26" s="3">
+      <c r="V26" s="3">
         <v>-1500</v>
       </c>
-      <c r="U26" s="3">
+      <c r="W26" s="3">
         <v>-1700</v>
       </c>
-      <c r="V26" s="3">
+      <c r="X26" s="3">
         <v>-2100</v>
       </c>
     </row>
-    <row r="27" spans="3:22" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-8800</v>
+      </c>
+      <c r="E27" s="3">
+        <v>-6000</v>
+      </c>
+      <c r="F27" s="3">
         <v>-2200</v>
       </c>
-      <c r="E27" s="3">
+      <c r="G27" s="3">
         <v>-4200</v>
       </c>
-      <c r="F27" s="3">
+      <c r="H27" s="3">
         <v>-9000</v>
       </c>
-      <c r="G27" s="3">
-        <v>-34400</v>
-      </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
+        <v>-35500</v>
+      </c>
+      <c r="J27" s="3">
         <v>-6800</v>
       </c>
-      <c r="I27" s="3">
+      <c r="K27" s="3">
         <v>8900</v>
       </c>
-      <c r="J27" s="3">
+      <c r="L27" s="3">
         <v>-15000</v>
       </c>
-      <c r="K27" s="3">
+      <c r="M27" s="3">
         <v>10300</v>
       </c>
-      <c r="L27" s="3">
+      <c r="N27" s="3">
         <v>-7600</v>
       </c>
-      <c r="M27" s="3">
+      <c r="O27" s="3">
         <v>7500</v>
       </c>
-      <c r="N27" s="3">
+      <c r="P27" s="3">
         <v>2300</v>
       </c>
-      <c r="O27" s="3">
+      <c r="Q27" s="3">
         <v>-15500</v>
       </c>
-      <c r="P27" s="3">
+      <c r="R27" s="3">
         <v>-10500</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="S27" s="3">
         <v>-6400</v>
       </c>
-      <c r="R27" s="3">
+      <c r="T27" s="3">
         <v>-2500</v>
       </c>
-      <c r="S27" s="3">
+      <c r="U27" s="3">
         <v>2900</v>
       </c>
-      <c r="T27" s="3">
+      <c r="V27" s="3">
         <v>-1500</v>
       </c>
-      <c r="U27" s="3">
+      <c r="W27" s="3">
         <v>-1700</v>
       </c>
-      <c r="V27" s="3">
+      <c r="X27" s="3">
         <v>-2100</v>
       </c>
     </row>
-    <row r="28" spans="3:22" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1936,8 +2051,14 @@
       <c r="V28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W28" s="3">
+        <v>0</v>
+      </c>
+      <c r="X28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1998,8 +2119,14 @@
       <c r="V29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W29" s="3">
+        <v>0</v>
+      </c>
+      <c r="X29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2060,8 +2187,14 @@
       <c r="V30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W30" s="3">
+        <v>0</v>
+      </c>
+      <c r="X30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2122,132 +2255,150 @@
       <c r="V31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W31" s="3">
+        <v>0</v>
+      </c>
+      <c r="X31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>-6300</v>
+      </c>
+      <c r="E32" s="3">
+        <v>-2100</v>
+      </c>
+      <c r="F32" s="3">
         <v>2200</v>
       </c>
-      <c r="E32" s="3">
+      <c r="G32" s="3">
         <v>-900</v>
       </c>
-      <c r="F32" s="3">
+      <c r="H32" s="3">
         <v>-6000</v>
       </c>
-      <c r="G32" s="3">
+      <c r="I32" s="3">
         <v>11100</v>
       </c>
-      <c r="H32" s="3">
+      <c r="J32" s="3">
         <v>-3700</v>
       </c>
-      <c r="I32" s="3">
+      <c r="K32" s="3">
         <v>12100</v>
       </c>
-      <c r="J32" s="3">
+      <c r="L32" s="3">
         <v>1500</v>
       </c>
-      <c r="K32" s="3">
+      <c r="M32" s="3">
         <v>-14500</v>
       </c>
-      <c r="L32" s="3">
+      <c r="N32" s="3">
         <v>2800</v>
       </c>
-      <c r="M32" s="3">
+      <c r="O32" s="3">
         <v>-11400</v>
       </c>
-      <c r="N32" s="3">
+      <c r="P32" s="3">
         <v>-4800</v>
       </c>
-      <c r="O32" s="3">
+      <c r="Q32" s="3">
         <v>8900</v>
       </c>
-      <c r="P32" s="3">
+      <c r="R32" s="3">
         <v>4000</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="S32" s="3">
         <v>1100</v>
-      </c>
-      <c r="R32" s="3">
-        <v>100</v>
-      </c>
-      <c r="S32" s="3">
-        <v>100</v>
       </c>
       <c r="T32" s="3">
         <v>100</v>
       </c>
       <c r="U32" s="3">
+        <v>100</v>
+      </c>
+      <c r="V32" s="3">
+        <v>100</v>
+      </c>
+      <c r="W32" s="3">
         <v>200</v>
       </c>
-      <c r="V32" s="3">
+      <c r="X32" s="3">
         <v>300</v>
       </c>
     </row>
-    <row r="33" spans="2:22" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-8800</v>
+      </c>
+      <c r="E33" s="3">
+        <v>-6000</v>
+      </c>
+      <c r="F33" s="3">
         <v>-2200</v>
       </c>
-      <c r="E33" s="3">
+      <c r="G33" s="3">
         <v>-4200</v>
       </c>
-      <c r="F33" s="3">
+      <c r="H33" s="3">
         <v>-9000</v>
       </c>
-      <c r="G33" s="3">
-        <v>-34400</v>
-      </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
+        <v>-35500</v>
+      </c>
+      <c r="J33" s="3">
         <v>-6800</v>
       </c>
-      <c r="I33" s="3">
+      <c r="K33" s="3">
         <v>8900</v>
       </c>
-      <c r="J33" s="3">
+      <c r="L33" s="3">
         <v>-15000</v>
       </c>
-      <c r="K33" s="3">
+      <c r="M33" s="3">
         <v>10300</v>
       </c>
-      <c r="L33" s="3">
+      <c r="N33" s="3">
         <v>-7600</v>
       </c>
-      <c r="M33" s="3">
+      <c r="O33" s="3">
         <v>7500</v>
       </c>
-      <c r="N33" s="3">
+      <c r="P33" s="3">
         <v>2300</v>
       </c>
-      <c r="O33" s="3">
+      <c r="Q33" s="3">
         <v>-15500</v>
       </c>
-      <c r="P33" s="3">
+      <c r="R33" s="3">
         <v>-10500</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="S33" s="3">
         <v>-6400</v>
       </c>
-      <c r="R33" s="3">
+      <c r="T33" s="3">
         <v>-2500</v>
       </c>
-      <c r="S33" s="3">
+      <c r="U33" s="3">
         <v>2900</v>
       </c>
-      <c r="T33" s="3">
+      <c r="V33" s="3">
         <v>-1500</v>
       </c>
-      <c r="U33" s="3">
+      <c r="W33" s="3">
         <v>-1700</v>
       </c>
-      <c r="V33" s="3">
+      <c r="X33" s="3">
         <v>-2100</v>
       </c>
     </row>
-    <row r="34" spans="2:22" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2308,137 +2459,155 @@
       <c r="V34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W34" s="3">
+        <v>0</v>
+      </c>
+      <c r="X34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-8800</v>
+      </c>
+      <c r="E35" s="3">
+        <v>-6000</v>
+      </c>
+      <c r="F35" s="3">
         <v>-2200</v>
       </c>
-      <c r="E35" s="3">
+      <c r="G35" s="3">
         <v>-4200</v>
       </c>
-      <c r="F35" s="3">
+      <c r="H35" s="3">
         <v>-9000</v>
       </c>
-      <c r="G35" s="3">
-        <v>-34400</v>
-      </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
+        <v>-35500</v>
+      </c>
+      <c r="J35" s="3">
         <v>-6800</v>
       </c>
-      <c r="I35" s="3">
+      <c r="K35" s="3">
         <v>8900</v>
       </c>
-      <c r="J35" s="3">
+      <c r="L35" s="3">
         <v>-15000</v>
       </c>
-      <c r="K35" s="3">
+      <c r="M35" s="3">
         <v>10300</v>
       </c>
-      <c r="L35" s="3">
+      <c r="N35" s="3">
         <v>-7600</v>
       </c>
-      <c r="M35" s="3">
+      <c r="O35" s="3">
         <v>7500</v>
       </c>
-      <c r="N35" s="3">
+      <c r="P35" s="3">
         <v>2300</v>
       </c>
-      <c r="O35" s="3">
+      <c r="Q35" s="3">
         <v>-15500</v>
       </c>
-      <c r="P35" s="3">
+      <c r="R35" s="3">
         <v>-10500</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="S35" s="3">
         <v>-6400</v>
       </c>
-      <c r="R35" s="3">
+      <c r="T35" s="3">
         <v>-2500</v>
       </c>
-      <c r="S35" s="3">
+      <c r="U35" s="3">
         <v>2900</v>
       </c>
-      <c r="T35" s="3">
+      <c r="V35" s="3">
         <v>-1500</v>
       </c>
-      <c r="U35" s="3">
+      <c r="W35" s="3">
         <v>-1700</v>
       </c>
-      <c r="V35" s="3">
+      <c r="X35" s="3">
         <v>-2100</v>
       </c>
     </row>
-    <row r="37" spans="2:22" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:24" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:22" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45747</v>
+      </c>
+      <c r="E38" s="2">
+        <v>45657</v>
+      </c>
+      <c r="F38" s="2">
         <v>45565</v>
       </c>
-      <c r="E38" s="2">
+      <c r="G38" s="2">
         <v>45473</v>
       </c>
-      <c r="F38" s="2">
+      <c r="H38" s="2">
         <v>45382</v>
       </c>
-      <c r="G38" s="2">
+      <c r="I38" s="2">
         <v>45291</v>
       </c>
-      <c r="H38" s="2">
+      <c r="J38" s="2">
         <v>45199</v>
       </c>
-      <c r="I38" s="2">
+      <c r="K38" s="2">
         <v>45107</v>
       </c>
-      <c r="J38" s="2">
+      <c r="L38" s="2">
         <v>45016</v>
       </c>
-      <c r="K38" s="2">
+      <c r="M38" s="2">
         <v>44926</v>
       </c>
-      <c r="L38" s="2">
+      <c r="N38" s="2">
         <v>44834</v>
       </c>
-      <c r="M38" s="2">
+      <c r="O38" s="2">
         <v>44742</v>
       </c>
-      <c r="N38" s="2">
+      <c r="P38" s="2">
         <v>44651</v>
       </c>
-      <c r="O38" s="2">
+      <c r="Q38" s="2">
         <v>44561</v>
       </c>
-      <c r="P38" s="2">
+      <c r="R38" s="2">
         <v>44469</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="S38" s="2">
         <v>44377</v>
       </c>
-      <c r="R38" s="2">
+      <c r="T38" s="2">
         <v>44286</v>
       </c>
-      <c r="S38" s="2">
+      <c r="U38" s="2">
         <v>44196</v>
       </c>
-      <c r="T38" s="2">
+      <c r="V38" s="2">
         <v>44104</v>
       </c>
-      <c r="U38" s="2">
+      <c r="W38" s="2">
         <v>44012</v>
       </c>
-      <c r="V38" s="2">
+      <c r="X38" s="2">
         <v>43921</v>
       </c>
     </row>
-    <row r="39" spans="2:22" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2461,8 +2630,10 @@
       <c r="T39" s="3"/>
       <c r="U39" s="3"/>
       <c r="V39" s="3"/>
-    </row>
-    <row r="40" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W39" s="3"/>
+      <c r="X39" s="3"/>
+    </row>
+    <row r="40" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2485,194 +2656,214 @@
       <c r="T40" s="3"/>
       <c r="U40" s="3"/>
       <c r="V40" s="3"/>
-    </row>
-    <row r="41" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W40" s="3"/>
+      <c r="X40" s="3"/>
+    </row>
+    <row r="41" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>2200</v>
+      </c>
+      <c r="E41" s="3">
+        <v>2600</v>
+      </c>
+      <c r="F41" s="3">
         <v>2400</v>
       </c>
-      <c r="E41" s="3">
+      <c r="G41" s="3">
         <v>3500</v>
       </c>
-      <c r="F41" s="3">
+      <c r="H41" s="3">
         <v>4200</v>
       </c>
-      <c r="G41" s="3">
+      <c r="I41" s="3">
         <v>5700</v>
       </c>
-      <c r="H41" s="3">
+      <c r="J41" s="3">
         <v>11100</v>
       </c>
-      <c r="I41" s="3">
+      <c r="K41" s="3">
         <v>4700</v>
       </c>
-      <c r="J41" s="3">
+      <c r="L41" s="3">
         <v>8300</v>
       </c>
-      <c r="K41" s="3">
+      <c r="M41" s="3">
         <v>8000</v>
       </c>
-      <c r="L41" s="3">
+      <c r="N41" s="3">
         <v>18900</v>
       </c>
-      <c r="M41" s="3">
+      <c r="O41" s="3">
         <v>40700</v>
       </c>
-      <c r="N41" s="3">
+      <c r="P41" s="3">
         <v>51900</v>
       </c>
-      <c r="O41" s="3">
+      <c r="Q41" s="3">
         <v>58600</v>
       </c>
-      <c r="P41" s="3">
+      <c r="R41" s="3">
         <v>61200</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="S41" s="3">
         <v>11500</v>
       </c>
-      <c r="R41" s="3">
+      <c r="T41" s="3">
         <v>16000</v>
       </c>
-      <c r="S41" s="3">
+      <c r="U41" s="3">
         <v>4200</v>
       </c>
-      <c r="T41" s="3">
+      <c r="V41" s="3">
         <v>4700</v>
       </c>
-      <c r="U41" s="3">
+      <c r="W41" s="3">
         <v>3600</v>
       </c>
-      <c r="V41" s="3">
+      <c r="X41" s="3">
         <v>4600</v>
       </c>
     </row>
-    <row r="42" spans="2:22" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>0</v>
+      </c>
+      <c r="E42" s="3">
+        <v>0</v>
+      </c>
+      <c r="F42" s="3">
         <v>100</v>
       </c>
-      <c r="E42" s="3">
+      <c r="G42" s="3">
         <v>200</v>
       </c>
-      <c r="F42" s="3">
+      <c r="H42" s="3">
         <v>600</v>
       </c>
-      <c r="G42" s="3">
+      <c r="I42" s="3">
         <v>500</v>
       </c>
-      <c r="H42" s="3">
+      <c r="J42" s="3">
         <v>500</v>
       </c>
-      <c r="I42" s="3">
+      <c r="K42" s="3">
         <v>900</v>
       </c>
-      <c r="J42" s="3">
+      <c r="L42" s="3">
         <v>1200</v>
       </c>
-      <c r="K42" s="3">
+      <c r="M42" s="3">
         <v>400</v>
       </c>
-      <c r="L42" s="3">
+      <c r="N42" s="3">
         <v>700</v>
       </c>
-      <c r="M42" s="3">
+      <c r="O42" s="3">
         <v>1100</v>
       </c>
-      <c r="N42" s="3">
+      <c r="P42" s="3">
         <v>2100</v>
       </c>
-      <c r="O42" s="3">
+      <c r="Q42" s="3">
         <v>1800</v>
       </c>
-      <c r="P42" s="3">
+      <c r="R42" s="3">
         <v>2300</v>
       </c>
-      <c r="Q42" s="3">
+      <c r="S42" s="3">
         <v>2300</v>
       </c>
-      <c r="R42" s="3">
+      <c r="T42" s="3">
         <v>3500</v>
       </c>
-      <c r="S42" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="T42" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="U42" s="3" t="s">
         <v>4</v>
       </c>
       <c r="V42" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="43" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W42" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="X42" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="43" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>600</v>
+      </c>
+      <c r="E43" s="3">
+        <v>900</v>
+      </c>
+      <c r="F43" s="3">
         <v>200</v>
       </c>
-      <c r="E43" s="3">
+      <c r="G43" s="3">
         <v>300</v>
       </c>
-      <c r="F43" s="3">
+      <c r="H43" s="3">
         <v>400</v>
       </c>
-      <c r="G43" s="3">
+      <c r="I43" s="3">
         <v>800</v>
       </c>
-      <c r="H43" s="3">
+      <c r="J43" s="3">
         <v>700</v>
       </c>
-      <c r="I43" s="3">
+      <c r="K43" s="3">
         <v>600</v>
       </c>
-      <c r="J43" s="3">
+      <c r="L43" s="3">
         <v>900</v>
       </c>
-      <c r="K43" s="3">
+      <c r="M43" s="3">
         <v>3100</v>
       </c>
-      <c r="L43" s="3">
+      <c r="N43" s="3">
         <v>3500</v>
       </c>
-      <c r="M43" s="3">
+      <c r="O43" s="3">
         <v>1700</v>
       </c>
-      <c r="N43" s="3">
+      <c r="P43" s="3">
         <v>1300</v>
       </c>
-      <c r="O43" s="3">
+      <c r="Q43" s="3">
         <v>1000</v>
       </c>
-      <c r="P43" s="3">
+      <c r="R43" s="3">
         <v>1100</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="S43" s="3">
         <v>600</v>
       </c>
-      <c r="R43" s="3">
+      <c r="T43" s="3">
         <v>400</v>
       </c>
-      <c r="S43" s="3">
+      <c r="U43" s="3">
         <v>200</v>
       </c>
-      <c r="T43" s="3">
+      <c r="V43" s="3">
         <v>200</v>
       </c>
-      <c r="U43" s="3">
+      <c r="W43" s="3">
         <v>100</v>
       </c>
-      <c r="V43" s="3">
+      <c r="X43" s="3">
         <v>400</v>
       </c>
     </row>
-    <row r="44" spans="2:22" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -2697,11 +2888,11 @@
       <c r="J44" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="K44" s="3">
-        <v>0</v>
-      </c>
-      <c r="L44" s="3">
-        <v>0</v>
+      <c r="K44" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="L44" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="M44" s="3">
         <v>0</v>
@@ -2733,8 +2924,14 @@
       <c r="V44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W44" s="3">
+        <v>0</v>
+      </c>
+      <c r="X44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
@@ -2759,106 +2956,118 @@
       <c r="J45" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="K45" s="3">
-        <v>2100</v>
-      </c>
-      <c r="L45" s="3">
-        <v>2500</v>
+      <c r="K45" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="L45" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="M45" s="3">
         <v>2100</v>
       </c>
       <c r="N45" s="3">
+        <v>2500</v>
+      </c>
+      <c r="O45" s="3">
+        <v>2100</v>
+      </c>
+      <c r="P45" s="3">
         <v>1300</v>
       </c>
-      <c r="O45" s="3">
+      <c r="Q45" s="3">
         <v>600</v>
       </c>
-      <c r="P45" s="3">
+      <c r="R45" s="3">
         <v>400</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="S45" s="3">
         <v>1000</v>
       </c>
-      <c r="R45" s="3">
+      <c r="T45" s="3">
         <v>900</v>
       </c>
-      <c r="S45" s="3">
+      <c r="U45" s="3">
         <v>6100</v>
-      </c>
-      <c r="T45" s="3">
-        <v>600</v>
-      </c>
-      <c r="U45" s="3">
-        <v>400</v>
       </c>
       <c r="V45" s="3">
         <v>600</v>
       </c>
-    </row>
-    <row r="46" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W45" s="3">
+        <v>400</v>
+      </c>
+      <c r="X45" s="3">
+        <v>600</v>
+      </c>
+    </row>
+    <row r="46" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>3700</v>
+      </c>
+      <c r="E46" s="3">
+        <v>4000</v>
+      </c>
+      <c r="F46" s="3">
         <v>3400</v>
       </c>
-      <c r="E46" s="3">
+      <c r="G46" s="3">
         <v>5100</v>
       </c>
-      <c r="F46" s="3">
+      <c r="H46" s="3">
         <v>6500</v>
       </c>
-      <c r="G46" s="3">
+      <c r="I46" s="3">
         <v>8000</v>
       </c>
-      <c r="H46" s="3">
+      <c r="J46" s="3">
         <v>12900</v>
       </c>
-      <c r="I46" s="3">
+      <c r="K46" s="3">
         <v>6500</v>
       </c>
-      <c r="J46" s="3">
+      <c r="L46" s="3">
         <v>10700</v>
       </c>
-      <c r="K46" s="3">
+      <c r="M46" s="3">
         <v>13500</v>
       </c>
-      <c r="L46" s="3">
+      <c r="N46" s="3">
         <v>25700</v>
       </c>
-      <c r="M46" s="3">
+      <c r="O46" s="3">
         <v>45600</v>
       </c>
-      <c r="N46" s="3">
+      <c r="P46" s="3">
         <v>56600</v>
       </c>
-      <c r="O46" s="3">
+      <c r="Q46" s="3">
         <v>61900</v>
       </c>
-      <c r="P46" s="3">
+      <c r="R46" s="3">
         <v>64900</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="S46" s="3">
         <v>15300</v>
       </c>
-      <c r="R46" s="3">
+      <c r="T46" s="3">
         <v>20700</v>
       </c>
-      <c r="S46" s="3">
+      <c r="U46" s="3">
         <v>10500</v>
       </c>
-      <c r="T46" s="3">
+      <c r="V46" s="3">
         <v>5500</v>
       </c>
-      <c r="U46" s="3">
+      <c r="W46" s="3">
         <v>4100</v>
       </c>
-      <c r="V46" s="3">
+      <c r="X46" s="3">
         <v>5600</v>
       </c>
     </row>
-    <row r="47" spans="2:22" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -2883,11 +3092,11 @@
       <c r="J47" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="K47" s="3">
-        <v>0</v>
-      </c>
-      <c r="L47" s="3">
-        <v>0</v>
+      <c r="K47" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="L47" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="M47" s="3">
         <v>0</v>
@@ -2919,58 +3128,64 @@
       <c r="V47" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W47" s="3">
+        <v>0</v>
+      </c>
+      <c r="X47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>100700</v>
+      </c>
+      <c r="E48" s="3">
+        <v>100400</v>
+      </c>
+      <c r="F48" s="3">
         <v>102800</v>
       </c>
-      <c r="E48" s="3">
+      <c r="G48" s="3">
         <v>102300</v>
       </c>
-      <c r="F48" s="3">
+      <c r="H48" s="3">
         <v>102900</v>
       </c>
-      <c r="G48" s="3">
+      <c r="I48" s="3">
         <v>103700</v>
       </c>
-      <c r="H48" s="3">
+      <c r="J48" s="3">
         <v>142600</v>
       </c>
-      <c r="I48" s="3">
+      <c r="K48" s="3">
         <v>142100</v>
       </c>
-      <c r="J48" s="3">
+      <c r="L48" s="3">
         <v>133700</v>
       </c>
-      <c r="K48" s="3">
+      <c r="M48" s="3">
         <v>173100</v>
       </c>
-      <c r="L48" s="3">
+      <c r="N48" s="3">
         <v>144300</v>
       </c>
-      <c r="M48" s="3">
+      <c r="O48" s="3">
         <v>129800</v>
       </c>
-      <c r="N48" s="3">
+      <c r="P48" s="3">
         <v>113700</v>
       </c>
-      <c r="O48" s="3">
+      <c r="Q48" s="3">
         <v>104700</v>
       </c>
-      <c r="P48" s="3">
+      <c r="R48" s="3">
         <v>95000</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="S48" s="3">
         <v>93900</v>
-      </c>
-      <c r="R48" s="3">
-        <v>92300</v>
-      </c>
-      <c r="S48" s="3">
-        <v>92300</v>
       </c>
       <c r="T48" s="3">
         <v>92300</v>
@@ -2981,8 +3196,14 @@
       <c r="V48" s="3">
         <v>92300</v>
       </c>
-    </row>
-    <row r="49" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W48" s="3">
+        <v>92300</v>
+      </c>
+      <c r="X48" s="3">
+        <v>92300</v>
+      </c>
+    </row>
+    <row r="49" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
@@ -3043,8 +3264,14 @@
       <c r="V49" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="50" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W49" s="3">
+        <v>0</v>
+      </c>
+      <c r="X49" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -3105,8 +3332,14 @@
       <c r="V50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W50" s="3">
+        <v>0</v>
+      </c>
+      <c r="X50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -3167,8 +3400,14 @@
       <c r="V51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W51" s="3">
+        <v>0</v>
+      </c>
+      <c r="X51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
@@ -3184,20 +3423,20 @@
       <c r="G52" s="3">
         <v>900</v>
       </c>
-      <c r="H52" s="3" t="s">
-        <v>4</v>
+      <c r="H52" s="3">
+        <v>900</v>
       </c>
       <c r="I52" s="3">
+        <v>900</v>
+      </c>
+      <c r="J52" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="K52" s="3">
         <v>1700</v>
       </c>
-      <c r="J52" s="3">
+      <c r="L52" s="3">
         <v>2500</v>
-      </c>
-      <c r="K52" s="3">
-        <v>900</v>
-      </c>
-      <c r="L52" s="3">
-        <v>900</v>
       </c>
       <c r="M52" s="3">
         <v>900</v>
@@ -3229,8 +3468,14 @@
       <c r="V52" s="3">
         <v>900</v>
       </c>
-    </row>
-    <row r="53" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W52" s="3">
+        <v>900</v>
+      </c>
+      <c r="X52" s="3">
+        <v>900</v>
+      </c>
+    </row>
+    <row r="53" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -3291,70 +3536,82 @@
       <c r="V53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W53" s="3">
+        <v>0</v>
+      </c>
+      <c r="X53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>105400</v>
+      </c>
+      <c r="E54" s="3">
+        <v>105300</v>
+      </c>
+      <c r="F54" s="3">
         <v>107100</v>
       </c>
-      <c r="E54" s="3">
+      <c r="G54" s="3">
         <v>108300</v>
       </c>
-      <c r="F54" s="3">
+      <c r="H54" s="3">
         <v>110300</v>
       </c>
-      <c r="G54" s="3">
+      <c r="I54" s="3">
         <v>112600</v>
       </c>
-      <c r="H54" s="3">
+      <c r="J54" s="3">
         <v>155500</v>
       </c>
-      <c r="I54" s="3">
+      <c r="K54" s="3">
         <v>150300</v>
       </c>
-      <c r="J54" s="3">
+      <c r="L54" s="3">
         <v>146900</v>
       </c>
-      <c r="K54" s="3">
+      <c r="M54" s="3">
         <v>187500</v>
       </c>
-      <c r="L54" s="3">
+      <c r="N54" s="3">
         <v>170900</v>
       </c>
-      <c r="M54" s="3">
+      <c r="O54" s="3">
         <v>176400</v>
       </c>
-      <c r="N54" s="3">
+      <c r="P54" s="3">
         <v>171300</v>
       </c>
-      <c r="O54" s="3">
+      <c r="Q54" s="3">
         <v>167600</v>
       </c>
-      <c r="P54" s="3">
+      <c r="R54" s="3">
         <v>160800</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="S54" s="3">
         <v>110100</v>
       </c>
-      <c r="R54" s="3">
+      <c r="T54" s="3">
         <v>114000</v>
       </c>
-      <c r="S54" s="3">
+      <c r="U54" s="3">
         <v>103700</v>
       </c>
-      <c r="T54" s="3">
+      <c r="V54" s="3">
         <v>98700</v>
       </c>
-      <c r="U54" s="3">
+      <c r="W54" s="3">
         <v>97300</v>
       </c>
-      <c r="V54" s="3">
+      <c r="X54" s="3">
         <v>98800</v>
       </c>
     </row>
-    <row r="55" spans="3:22" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -3377,8 +3634,10 @@
       <c r="T55" s="3"/>
       <c r="U55" s="3"/>
       <c r="V55" s="3"/>
-    </row>
-    <row r="56" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W55" s="3"/>
+      <c r="X55" s="3"/>
+    </row>
+    <row r="56" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -3401,103 +3660,111 @@
       <c r="T56" s="3"/>
       <c r="U56" s="3"/>
       <c r="V56" s="3"/>
-    </row>
-    <row r="57" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W56" s="3"/>
+      <c r="X56" s="3"/>
+    </row>
+    <row r="57" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>4900</v>
+      </c>
+      <c r="E57" s="3">
+        <v>2500</v>
+      </c>
+      <c r="F57" s="3">
         <v>3200</v>
       </c>
-      <c r="E57" s="3">
+      <c r="G57" s="3">
         <v>3500</v>
       </c>
-      <c r="F57" s="3">
+      <c r="H57" s="3">
         <v>5700</v>
       </c>
-      <c r="G57" s="3">
+      <c r="I57" s="3">
         <v>6700</v>
       </c>
-      <c r="H57" s="3">
+      <c r="J57" s="3">
         <v>7100</v>
       </c>
-      <c r="I57" s="3">
+      <c r="K57" s="3">
         <v>12900</v>
       </c>
-      <c r="J57" s="3">
+      <c r="L57" s="3">
         <v>11300</v>
       </c>
-      <c r="K57" s="3">
+      <c r="M57" s="3">
         <v>18900</v>
       </c>
-      <c r="L57" s="3">
+      <c r="N57" s="3">
         <v>8200</v>
       </c>
-      <c r="M57" s="3">
+      <c r="O57" s="3">
         <v>9900</v>
       </c>
-      <c r="N57" s="3">
+      <c r="P57" s="3">
         <v>5600</v>
       </c>
-      <c r="O57" s="3">
+      <c r="Q57" s="3">
         <v>3500</v>
       </c>
-      <c r="P57" s="3">
+      <c r="R57" s="3">
         <v>2000</v>
       </c>
-      <c r="Q57" s="3">
-        <v>0</v>
-      </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
+        <v>0</v>
+      </c>
+      <c r="T57" s="3">
         <v>200</v>
       </c>
-      <c r="S57" s="3">
+      <c r="U57" s="3">
         <v>400</v>
       </c>
-      <c r="T57" s="3">
-        <v>0</v>
-      </c>
-      <c r="U57" s="3">
-        <v>0</v>
-      </c>
       <c r="V57" s="3">
+        <v>0</v>
+      </c>
+      <c r="W57" s="3">
+        <v>0</v>
+      </c>
+      <c r="X57" s="3">
         <v>100</v>
       </c>
     </row>
-    <row r="58" spans="3:22" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>47400</v>
+      </c>
+      <c r="E58" s="3">
+        <v>44500</v>
+      </c>
+      <c r="F58" s="3">
         <v>34300</v>
       </c>
-      <c r="E58" s="3">
+      <c r="G58" s="3">
         <v>35300</v>
       </c>
-      <c r="F58" s="3">
+      <c r="H58" s="3">
         <v>35000</v>
       </c>
-      <c r="G58" s="3">
-        <v>0</v>
-      </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
+        <v>30400</v>
+      </c>
+      <c r="J58" s="3">
         <v>40900</v>
       </c>
-      <c r="I58" s="3">
-        <v>0</v>
-      </c>
-      <c r="J58" s="3">
-        <v>0</v>
-      </c>
       <c r="K58" s="3">
+        <v>0</v>
+      </c>
+      <c r="L58" s="3">
+        <v>0</v>
+      </c>
+      <c r="M58" s="3">
         <v>25700</v>
       </c>
-      <c r="L58" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="M58" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="N58" s="3" t="s">
         <v>4</v>
       </c>
@@ -3507,274 +3774,304 @@
       <c r="P58" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="Q58" s="3">
-        <v>0</v>
-      </c>
-      <c r="R58" s="3">
-        <v>0</v>
-      </c>
-      <c r="S58" s="3" t="s">
-        <v>4</v>
+      <c r="Q58" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="R58" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="S58" s="3">
+        <v>0</v>
       </c>
       <c r="T58" s="3">
+        <v>0</v>
+      </c>
+      <c r="U58" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="V58" s="3">
         <v>7000</v>
       </c>
-      <c r="U58" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="V58" s="3" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="59" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W58" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="X58" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="59" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>500</v>
+      </c>
+      <c r="E59" s="3">
+        <v>1100</v>
+      </c>
+      <c r="F59" s="3">
         <v>2700</v>
       </c>
-      <c r="E59" s="3">
+      <c r="G59" s="3">
         <v>2600</v>
       </c>
-      <c r="F59" s="3">
+      <c r="H59" s="3">
         <v>1500</v>
       </c>
-      <c r="G59" s="3">
+      <c r="I59" s="3">
         <v>1100</v>
       </c>
-      <c r="H59" s="3">
+      <c r="J59" s="3">
         <v>3000</v>
       </c>
-      <c r="I59" s="3">
+      <c r="K59" s="3">
         <v>4000</v>
       </c>
-      <c r="J59" s="3">
+      <c r="L59" s="3">
         <v>9100</v>
       </c>
-      <c r="K59" s="3">
+      <c r="M59" s="3">
         <v>9600</v>
       </c>
-      <c r="L59" s="3">
+      <c r="N59" s="3">
         <v>400</v>
-      </c>
-      <c r="M59" s="3">
-        <v>1200</v>
-      </c>
-      <c r="N59" s="3">
-        <v>500</v>
       </c>
       <c r="O59" s="3">
         <v>1200</v>
       </c>
       <c r="P59" s="3">
+        <v>500</v>
+      </c>
+      <c r="Q59" s="3">
+        <v>1200</v>
+      </c>
+      <c r="R59" s="3">
         <v>100</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="S59" s="3">
         <v>600</v>
       </c>
-      <c r="R59" s="3">
+      <c r="T59" s="3">
         <v>400</v>
       </c>
-      <c r="S59" s="3">
+      <c r="U59" s="3">
         <v>2400</v>
       </c>
-      <c r="T59" s="3">
+      <c r="V59" s="3">
         <v>1000</v>
       </c>
-      <c r="U59" s="3">
-        <v>0</v>
-      </c>
-      <c r="V59" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="60" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W59" s="3">
+        <v>0</v>
+      </c>
+      <c r="X59" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="60" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>57000</v>
+      </c>
+      <c r="E60" s="3">
+        <v>50000</v>
+      </c>
+      <c r="F60" s="3">
         <v>47400</v>
       </c>
-      <c r="E60" s="3">
+      <c r="G60" s="3">
         <v>47200</v>
       </c>
-      <c r="F60" s="3">
+      <c r="H60" s="3">
         <v>46900</v>
       </c>
-      <c r="G60" s="3">
-        <v>12100</v>
-      </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
+        <v>42500</v>
+      </c>
+      <c r="J60" s="3">
         <v>53900</v>
       </c>
-      <c r="I60" s="3">
+      <c r="K60" s="3">
         <v>18800</v>
       </c>
-      <c r="J60" s="3">
+      <c r="L60" s="3">
         <v>21100</v>
       </c>
-      <c r="K60" s="3">
+      <c r="M60" s="3">
         <v>54100</v>
       </c>
-      <c r="L60" s="3">
+      <c r="N60" s="3">
         <v>8700</v>
       </c>
-      <c r="M60" s="3">
+      <c r="O60" s="3">
         <v>11100</v>
       </c>
-      <c r="N60" s="3">
+      <c r="P60" s="3">
         <v>6000</v>
       </c>
-      <c r="O60" s="3">
+      <c r="Q60" s="3">
         <v>4700</v>
       </c>
-      <c r="P60" s="3">
+      <c r="R60" s="3">
         <v>2100</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="S60" s="3">
         <v>600</v>
       </c>
-      <c r="R60" s="3">
+      <c r="T60" s="3">
         <v>500</v>
       </c>
-      <c r="S60" s="3">
+      <c r="U60" s="3">
         <v>2800</v>
       </c>
-      <c r="T60" s="3">
+      <c r="V60" s="3">
         <v>8000</v>
       </c>
-      <c r="U60" s="3">
-        <v>0</v>
-      </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
+        <v>0</v>
+      </c>
+      <c r="X60" s="3">
         <v>100</v>
       </c>
     </row>
-    <row r="61" spans="3:22" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>5600</v>
+      </c>
+      <c r="E61" s="3">
+        <v>5500</v>
+      </c>
+      <c r="F61" s="3">
         <v>5800</v>
       </c>
-      <c r="E61" s="3">
+      <c r="G61" s="3">
         <v>5300</v>
       </c>
-      <c r="F61" s="3">
+      <c r="H61" s="3">
         <v>4100</v>
       </c>
-      <c r="G61" s="3">
-        <v>33800</v>
-      </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
+        <v>3400</v>
+      </c>
+      <c r="J61" s="3">
         <v>2700</v>
       </c>
-      <c r="I61" s="3">
+      <c r="K61" s="3">
         <v>39300</v>
       </c>
-      <c r="J61" s="3">
+      <c r="L61" s="3">
         <v>45100</v>
       </c>
-      <c r="K61" s="3">
+      <c r="M61" s="3">
         <v>5100</v>
       </c>
-      <c r="L61" s="3">
+      <c r="N61" s="3">
         <v>30000</v>
       </c>
-      <c r="M61" s="3">
+      <c r="O61" s="3">
         <v>27600</v>
       </c>
-      <c r="N61" s="3">
+      <c r="P61" s="3">
         <v>26200</v>
       </c>
-      <c r="O61" s="3">
+      <c r="Q61" s="3">
         <v>23600</v>
       </c>
-      <c r="P61" s="3">
+      <c r="R61" s="3">
         <v>22400</v>
       </c>
-      <c r="Q61" s="3">
-        <v>0</v>
-      </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
+        <v>0</v>
+      </c>
+      <c r="T61" s="3">
         <v>6700</v>
       </c>
-      <c r="S61" s="3">
+      <c r="U61" s="3">
         <v>6700</v>
       </c>
-      <c r="T61" s="3">
-        <v>0</v>
-      </c>
-      <c r="U61" s="3">
+      <c r="V61" s="3">
+        <v>0</v>
+      </c>
+      <c r="W61" s="3">
         <v>7000</v>
       </c>
-      <c r="V61" s="3">
+      <c r="X61" s="3">
         <v>7000</v>
       </c>
     </row>
-    <row r="62" spans="3:22" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
-        <v>3200</v>
+        <v>3100</v>
       </c>
       <c r="E62" s="3">
         <v>2900</v>
       </c>
       <c r="F62" s="3">
+        <v>3200</v>
+      </c>
+      <c r="G62" s="3">
+        <v>2900</v>
+      </c>
+      <c r="H62" s="3">
         <v>2800</v>
       </c>
-      <c r="G62" s="3">
+      <c r="I62" s="3">
         <v>3000</v>
       </c>
-      <c r="H62" s="3">
+      <c r="J62" s="3">
         <v>1200</v>
       </c>
-      <c r="I62" s="3">
+      <c r="K62" s="3">
         <v>1400</v>
       </c>
-      <c r="J62" s="3">
+      <c r="L62" s="3">
         <v>1300</v>
       </c>
-      <c r="K62" s="3">
+      <c r="M62" s="3">
         <v>1800</v>
       </c>
-      <c r="L62" s="3">
+      <c r="N62" s="3">
         <v>20100</v>
       </c>
-      <c r="M62" s="3">
+      <c r="O62" s="3">
         <v>19500</v>
       </c>
-      <c r="N62" s="3">
+      <c r="P62" s="3">
         <v>34900</v>
       </c>
-      <c r="O62" s="3">
+      <c r="Q62" s="3">
         <v>39400</v>
       </c>
-      <c r="P62" s="3">
+      <c r="R62" s="3">
         <v>29300</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="S62" s="3">
         <v>1300</v>
       </c>
-      <c r="R62" s="3">
+      <c r="T62" s="3">
         <v>2000</v>
       </c>
-      <c r="S62" s="3">
+      <c r="U62" s="3">
         <v>2000</v>
       </c>
-      <c r="T62" s="3">
+      <c r="V62" s="3">
         <v>2700</v>
       </c>
-      <c r="U62" s="3">
+      <c r="W62" s="3">
         <v>3200</v>
       </c>
-      <c r="V62" s="3">
+      <c r="X62" s="3">
         <v>3000</v>
       </c>
     </row>
-    <row r="63" spans="3:22" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -3835,8 +4132,14 @@
       <c r="V63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W63" s="3">
+        <v>0</v>
+      </c>
+      <c r="X63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -3897,8 +4200,14 @@
       <c r="V64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W64" s="3">
+        <v>0</v>
+      </c>
+      <c r="X64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -3959,70 +4268,82 @@
       <c r="V65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W65" s="3">
+        <v>0</v>
+      </c>
+      <c r="X65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>67900</v>
+      </c>
+      <c r="E66" s="3">
+        <v>60600</v>
+      </c>
+      <c r="F66" s="3">
         <v>58600</v>
       </c>
-      <c r="E66" s="3">
+      <c r="G66" s="3">
         <v>57100</v>
       </c>
-      <c r="F66" s="3">
+      <c r="H66" s="3">
         <v>55300</v>
       </c>
-      <c r="G66" s="3">
+      <c r="I66" s="3">
         <v>49500</v>
       </c>
-      <c r="H66" s="3">
+      <c r="J66" s="3">
         <v>58500</v>
       </c>
-      <c r="I66" s="3">
+      <c r="K66" s="3">
         <v>60300</v>
       </c>
-      <c r="J66" s="3">
+      <c r="L66" s="3">
         <v>68200</v>
       </c>
-      <c r="K66" s="3">
+      <c r="M66" s="3">
         <v>61000</v>
       </c>
-      <c r="L66" s="3">
+      <c r="N66" s="3">
         <v>58800</v>
       </c>
-      <c r="M66" s="3">
+      <c r="O66" s="3">
         <v>58200</v>
       </c>
-      <c r="N66" s="3">
+      <c r="P66" s="3">
         <v>67100</v>
       </c>
-      <c r="O66" s="3">
+      <c r="Q66" s="3">
         <v>67600</v>
       </c>
-      <c r="P66" s="3">
+      <c r="R66" s="3">
         <v>53900</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="S66" s="3">
         <v>1900</v>
       </c>
-      <c r="R66" s="3">
+      <c r="T66" s="3">
         <v>9300</v>
       </c>
-      <c r="S66" s="3">
+      <c r="U66" s="3">
         <v>11500</v>
       </c>
-      <c r="T66" s="3">
+      <c r="V66" s="3">
         <v>10700</v>
       </c>
-      <c r="U66" s="3">
+      <c r="W66" s="3">
         <v>10200</v>
       </c>
-      <c r="V66" s="3">
+      <c r="X66" s="3">
         <v>10100</v>
       </c>
     </row>
-    <row r="67" spans="2:22" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -4045,8 +4366,10 @@
       <c r="T67" s="3"/>
       <c r="U67" s="3"/>
       <c r="V67" s="3"/>
-    </row>
-    <row r="68" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W67" s="3"/>
+      <c r="X67" s="3"/>
+    </row>
+    <row r="68" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -4107,8 +4430,14 @@
       <c r="V68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W68" s="3">
+        <v>0</v>
+      </c>
+      <c r="X68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -4169,8 +4498,14 @@
       <c r="V69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W69" s="3">
+        <v>0</v>
+      </c>
+      <c r="X69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -4231,8 +4566,14 @@
       <c r="V70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W70" s="3">
+        <v>0</v>
+      </c>
+      <c r="X70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -4293,70 +4634,82 @@
       <c r="V71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W71" s="3">
+        <v>0</v>
+      </c>
+      <c r="X71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-200100</v>
+      </c>
+      <c r="E72" s="3">
+        <v>-191100</v>
+      </c>
+      <c r="F72" s="3">
         <v>-197100</v>
       </c>
-      <c r="E72" s="3">
+      <c r="G72" s="3">
         <v>-192400</v>
       </c>
-      <c r="F72" s="3">
+      <c r="H72" s="3">
         <v>-190200</v>
       </c>
-      <c r="G72" s="3">
+      <c r="I72" s="3">
         <v>-185900</v>
       </c>
-      <c r="H72" s="3">
+      <c r="J72" s="3">
         <v>-147800</v>
       </c>
-      <c r="I72" s="3">
+      <c r="K72" s="3">
         <v>-144100</v>
       </c>
-      <c r="J72" s="3">
+      <c r="L72" s="3">
         <v>-149700</v>
       </c>
-      <c r="K72" s="3">
+      <c r="M72" s="3">
         <v>-162900</v>
       </c>
-      <c r="L72" s="3">
+      <c r="N72" s="3">
         <v>-173900</v>
       </c>
-      <c r="M72" s="3">
+      <c r="O72" s="3">
         <v>-166600</v>
       </c>
-      <c r="N72" s="3">
+      <c r="P72" s="3">
         <v>-174000</v>
       </c>
-      <c r="O72" s="3">
+      <c r="Q72" s="3">
         <v>-176800</v>
       </c>
-      <c r="P72" s="3">
+      <c r="R72" s="3">
         <v>-161500</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="S72" s="3">
         <v>-151200</v>
       </c>
-      <c r="R72" s="3">
+      <c r="T72" s="3">
         <v>-145000</v>
       </c>
-      <c r="S72" s="3">
+      <c r="U72" s="3">
         <v>-143000</v>
       </c>
-      <c r="T72" s="3">
+      <c r="V72" s="3">
         <v>-145900</v>
       </c>
-      <c r="U72" s="3">
+      <c r="W72" s="3">
         <v>-145200</v>
       </c>
-      <c r="V72" s="3">
+      <c r="X72" s="3">
         <v>-143600</v>
       </c>
     </row>
-    <row r="73" spans="2:22" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -4417,8 +4770,14 @@
       <c r="V73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W73" s="3">
+        <v>0</v>
+      </c>
+      <c r="X73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -4479,8 +4838,14 @@
       <c r="V74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W74" s="3">
+        <v>0</v>
+      </c>
+      <c r="X74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -4541,70 +4906,82 @@
       <c r="V75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W75" s="3">
+        <v>0</v>
+      </c>
+      <c r="X75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>37400</v>
+      </c>
+      <c r="E76" s="3">
+        <v>44700</v>
+      </c>
+      <c r="F76" s="3">
         <v>48500</v>
       </c>
-      <c r="E76" s="3">
+      <c r="G76" s="3">
         <v>51200</v>
       </c>
-      <c r="F76" s="3">
+      <c r="H76" s="3">
         <v>55000</v>
       </c>
-      <c r="G76" s="3">
+      <c r="I76" s="3">
         <v>63100</v>
       </c>
-      <c r="H76" s="3">
+      <c r="J76" s="3">
         <v>96900</v>
       </c>
-      <c r="I76" s="3">
+      <c r="K76" s="3">
         <v>90000</v>
       </c>
-      <c r="J76" s="3">
+      <c r="L76" s="3">
         <v>78700</v>
       </c>
-      <c r="K76" s="3">
+      <c r="M76" s="3">
         <v>126500</v>
       </c>
-      <c r="L76" s="3">
+      <c r="N76" s="3">
         <v>112100</v>
       </c>
-      <c r="M76" s="3">
+      <c r="O76" s="3">
         <v>118200</v>
       </c>
-      <c r="N76" s="3">
+      <c r="P76" s="3">
         <v>104200</v>
       </c>
-      <c r="O76" s="3">
+      <c r="Q76" s="3">
         <v>100000</v>
       </c>
-      <c r="P76" s="3">
+      <c r="R76" s="3">
         <v>107000</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="S76" s="3">
         <v>108200</v>
       </c>
-      <c r="R76" s="3">
+      <c r="T76" s="3">
         <v>104700</v>
       </c>
-      <c r="S76" s="3">
+      <c r="U76" s="3">
         <v>92200</v>
       </c>
-      <c r="T76" s="3">
+      <c r="V76" s="3">
         <v>88000</v>
       </c>
-      <c r="U76" s="3">
+      <c r="W76" s="3">
         <v>87200</v>
       </c>
-      <c r="V76" s="3">
+      <c r="X76" s="3">
         <v>88700</v>
       </c>
     </row>
-    <row r="77" spans="2:22" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -4665,137 +5042,155 @@
       <c r="V77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W77" s="3">
+        <v>0</v>
+      </c>
+      <c r="X77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:24" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:22" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45747</v>
+      </c>
+      <c r="E80" s="2">
+        <v>45657</v>
+      </c>
+      <c r="F80" s="2">
         <v>45565</v>
       </c>
-      <c r="E80" s="2">
+      <c r="G80" s="2">
         <v>45473</v>
       </c>
-      <c r="F80" s="2">
+      <c r="H80" s="2">
         <v>45382</v>
       </c>
-      <c r="G80" s="2">
+      <c r="I80" s="2">
         <v>45291</v>
       </c>
-      <c r="H80" s="2">
+      <c r="J80" s="2">
         <v>45199</v>
       </c>
-      <c r="I80" s="2">
+      <c r="K80" s="2">
         <v>45107</v>
       </c>
-      <c r="J80" s="2">
+      <c r="L80" s="2">
         <v>45016</v>
       </c>
-      <c r="K80" s="2">
+      <c r="M80" s="2">
         <v>44926</v>
       </c>
-      <c r="L80" s="2">
+      <c r="N80" s="2">
         <v>44834</v>
       </c>
-      <c r="M80" s="2">
+      <c r="O80" s="2">
         <v>44742</v>
       </c>
-      <c r="N80" s="2">
+      <c r="P80" s="2">
         <v>44651</v>
       </c>
-      <c r="O80" s="2">
+      <c r="Q80" s="2">
         <v>44561</v>
       </c>
-      <c r="P80" s="2">
+      <c r="R80" s="2">
         <v>44469</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="S80" s="2">
         <v>44377</v>
       </c>
-      <c r="R80" s="2">
+      <c r="T80" s="2">
         <v>44286</v>
       </c>
-      <c r="S80" s="2">
+      <c r="U80" s="2">
         <v>44196</v>
       </c>
-      <c r="T80" s="2">
+      <c r="V80" s="2">
         <v>44104</v>
       </c>
-      <c r="U80" s="2">
+      <c r="W80" s="2">
         <v>44012</v>
       </c>
-      <c r="V80" s="2">
+      <c r="X80" s="2">
         <v>43921</v>
       </c>
     </row>
-    <row r="81" spans="3:22" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-8800</v>
+      </c>
+      <c r="E81" s="3">
+        <v>-6000</v>
+      </c>
+      <c r="F81" s="3">
         <v>-2200</v>
       </c>
-      <c r="E81" s="3">
+      <c r="G81" s="3">
         <v>-4200</v>
       </c>
-      <c r="F81" s="3">
+      <c r="H81" s="3">
         <v>-9000</v>
       </c>
-      <c r="G81" s="3">
-        <v>-34400</v>
-      </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
+        <v>-35500</v>
+      </c>
+      <c r="J81" s="3">
         <v>-6800</v>
       </c>
-      <c r="I81" s="3">
+      <c r="K81" s="3">
         <v>8900</v>
       </c>
-      <c r="J81" s="3">
+      <c r="L81" s="3">
         <v>-15000</v>
       </c>
-      <c r="K81" s="3">
+      <c r="M81" s="3">
         <v>10300</v>
       </c>
-      <c r="L81" s="3">
+      <c r="N81" s="3">
         <v>-7600</v>
       </c>
-      <c r="M81" s="3">
+      <c r="O81" s="3">
         <v>7500</v>
       </c>
-      <c r="N81" s="3">
+      <c r="P81" s="3">
         <v>2300</v>
       </c>
-      <c r="O81" s="3">
+      <c r="Q81" s="3">
         <v>-15500</v>
       </c>
-      <c r="P81" s="3">
+      <c r="R81" s="3">
         <v>-10500</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="S81" s="3">
         <v>-6400</v>
       </c>
-      <c r="R81" s="3">
+      <c r="T81" s="3">
         <v>-2500</v>
       </c>
-      <c r="S81" s="3">
+      <c r="U81" s="3">
         <v>2900</v>
       </c>
-      <c r="T81" s="3">
+      <c r="V81" s="3">
         <v>-1500</v>
       </c>
-      <c r="U81" s="3">
+      <c r="W81" s="3">
         <v>-1700</v>
       </c>
-      <c r="V81" s="3">
+      <c r="X81" s="3">
         <v>-2100</v>
       </c>
     </row>
-    <row r="82" spans="3:22" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -4818,8 +5213,10 @@
       <c r="T82" s="3"/>
       <c r="U82" s="3"/>
       <c r="V82" s="3"/>
-    </row>
-    <row r="83" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W82" s="3"/>
+      <c r="X82" s="3"/>
+    </row>
+    <row r="83" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
@@ -4835,35 +5232,35 @@
       <c r="G83" s="3">
         <v>0</v>
       </c>
-      <c r="H83" s="3" t="s">
-        <v>4</v>
+      <c r="H83" s="3">
+        <v>0</v>
       </c>
       <c r="I83" s="3">
         <v>0</v>
       </c>
-      <c r="J83" s="3">
-        <v>0</v>
-      </c>
-      <c r="K83" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="L83" s="3" t="s">
-        <v>4</v>
+      <c r="J83" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="K83" s="3">
+        <v>0</v>
+      </c>
+      <c r="L83" s="3">
+        <v>0</v>
       </c>
       <c r="M83" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="N83" s="3">
-        <v>0</v>
-      </c>
-      <c r="O83" s="3">
-        <v>0</v>
-      </c>
-      <c r="P83" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="Q83" s="3" t="s">
-        <v>4</v>
+      <c r="N83" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="O83" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="P83" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q83" s="3">
+        <v>0</v>
       </c>
       <c r="R83" s="3" t="s">
         <v>4</v>
@@ -4880,8 +5277,14 @@
       <c r="V83" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="84" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W83" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="X83" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="84" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -4942,8 +5345,14 @@
       <c r="V84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W84" s="3">
+        <v>0</v>
+      </c>
+      <c r="X84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -5004,8 +5413,14 @@
       <c r="V85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W85" s="3">
+        <v>0</v>
+      </c>
+      <c r="X85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -5066,8 +5481,14 @@
       <c r="V86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W86" s="3">
+        <v>0</v>
+      </c>
+      <c r="X86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -5128,8 +5549,14 @@
       <c r="V87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W87" s="3">
+        <v>0</v>
+      </c>
+      <c r="X87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -5190,70 +5617,82 @@
       <c r="V88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W88" s="3">
+        <v>0</v>
+      </c>
+      <c r="X88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>-100</v>
+      </c>
+      <c r="E89" s="3">
+        <v>-4300</v>
+      </c>
+      <c r="F89" s="3">
         <v>-2200</v>
       </c>
-      <c r="E89" s="3">
+      <c r="G89" s="3">
         <v>-2800</v>
       </c>
-      <c r="F89" s="3">
+      <c r="H89" s="3">
         <v>-3000</v>
       </c>
-      <c r="G89" s="3">
+      <c r="I89" s="3">
         <v>-4500</v>
       </c>
-      <c r="H89" s="3">
+      <c r="J89" s="3">
         <v>-8900</v>
       </c>
-      <c r="I89" s="3">
+      <c r="K89" s="3">
         <v>-3000</v>
       </c>
-      <c r="J89" s="3">
+      <c r="L89" s="3">
         <v>-700</v>
       </c>
-      <c r="K89" s="3">
+      <c r="M89" s="3">
         <v>-6600</v>
       </c>
-      <c r="L89" s="3">
+      <c r="N89" s="3">
         <v>-500</v>
       </c>
-      <c r="M89" s="3">
+      <c r="O89" s="3">
         <v>-5300</v>
       </c>
-      <c r="N89" s="3">
+      <c r="P89" s="3">
         <v>-3500</v>
       </c>
-      <c r="O89" s="3">
+      <c r="Q89" s="3">
         <v>-4900</v>
       </c>
-      <c r="P89" s="3">
+      <c r="R89" s="3">
         <v>-5300</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="S89" s="3">
         <v>-3600</v>
       </c>
-      <c r="R89" s="3">
+      <c r="T89" s="3">
         <v>-3100</v>
       </c>
-      <c r="S89" s="3">
+      <c r="U89" s="3">
         <v>-1500</v>
       </c>
-      <c r="T89" s="3">
+      <c r="V89" s="3">
         <v>-1200</v>
       </c>
-      <c r="U89" s="3">
+      <c r="W89" s="3">
         <v>-1100</v>
       </c>
-      <c r="V89" s="3">
+      <c r="X89" s="3">
         <v>-1800</v>
       </c>
     </row>
-    <row r="90" spans="3:22" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -5276,70 +5715,78 @@
       <c r="T90" s="3"/>
       <c r="U90" s="3"/>
       <c r="V90" s="3"/>
-    </row>
-    <row r="91" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W90" s="3"/>
+      <c r="X90" s="3"/>
+    </row>
+    <row r="91" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-200</v>
+      </c>
+      <c r="E91" s="3">
         <v>-100</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
+        <v>-100</v>
+      </c>
+      <c r="G91" s="3">
         <v>200</v>
       </c>
-      <c r="F91" s="3">
+      <c r="H91" s="3">
         <v>-400</v>
       </c>
-      <c r="G91" s="3">
+      <c r="I91" s="3">
         <v>400</v>
       </c>
-      <c r="H91" s="3">
+      <c r="J91" s="3">
         <v>400</v>
       </c>
-      <c r="I91" s="3">
+      <c r="K91" s="3">
         <v>-1900</v>
       </c>
-      <c r="J91" s="3">
+      <c r="L91" s="3">
         <v>-9100</v>
       </c>
-      <c r="K91" s="3">
+      <c r="M91" s="3">
         <v>-15600</v>
       </c>
-      <c r="L91" s="3">
+      <c r="N91" s="3">
         <v>-18800</v>
       </c>
-      <c r="M91" s="3">
+      <c r="O91" s="3">
         <v>-8700</v>
       </c>
-      <c r="N91" s="3">
+      <c r="P91" s="3">
         <v>-4500</v>
       </c>
-      <c r="O91" s="3">
+      <c r="Q91" s="3">
         <v>-6100</v>
       </c>
-      <c r="P91" s="3">
+      <c r="R91" s="3">
         <v>-600</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="S91" s="3">
         <v>500</v>
       </c>
-      <c r="R91" s="3">
+      <c r="T91" s="3">
         <v>-500</v>
       </c>
-      <c r="S91" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="T91" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="U91" s="3" t="s">
         <v>4</v>
       </c>
       <c r="V91" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="92" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W91" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="X91" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="92" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -5400,8 +5847,14 @@
       <c r="V92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W92" s="3">
+        <v>0</v>
+      </c>
+      <c r="X92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -5462,59 +5915,65 @@
       <c r="V93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W93" s="3">
+        <v>0</v>
+      </c>
+      <c r="X93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-200</v>
+      </c>
+      <c r="E94" s="3">
+        <v>-100</v>
+      </c>
+      <c r="F94" s="3">
         <v>300</v>
       </c>
-      <c r="E94" s="3">
+      <c r="G94" s="3">
         <v>700</v>
       </c>
-      <c r="F94" s="3">
-        <v>0</v>
-      </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
+        <v>0</v>
+      </c>
+      <c r="I94" s="3">
         <v>-1200</v>
       </c>
-      <c r="H94" s="3">
+      <c r="J94" s="3">
         <v>600</v>
       </c>
-      <c r="I94" s="3">
+      <c r="K94" s="3">
         <v>-800</v>
       </c>
-      <c r="J94" s="3">
+      <c r="L94" s="3">
         <v>-9100</v>
       </c>
-      <c r="K94" s="3">
+      <c r="M94" s="3">
         <v>-10900</v>
       </c>
-      <c r="L94" s="3">
+      <c r="N94" s="3">
         <v>-18800</v>
       </c>
-      <c r="M94" s="3">
+      <c r="O94" s="3">
         <v>-8700</v>
       </c>
-      <c r="N94" s="3">
+      <c r="P94" s="3">
         <v>-5100</v>
       </c>
-      <c r="O94" s="3">
+      <c r="Q94" s="3">
         <v>-6100</v>
       </c>
-      <c r="P94" s="3">
+      <c r="R94" s="3">
         <v>-500</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="S94" s="3">
         <v>-1500</v>
       </c>
-      <c r="R94" s="3">
-        <v>0</v>
-      </c>
-      <c r="S94" s="3">
-        <v>0</v>
-      </c>
       <c r="T94" s="3">
         <v>0</v>
       </c>
@@ -5524,8 +5983,14 @@
       <c r="V94" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="95" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W94" s="3">
+        <v>0</v>
+      </c>
+      <c r="X94" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="95" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -5548,8 +6013,10 @@
       <c r="T95" s="3"/>
       <c r="U95" s="3"/>
       <c r="V95" s="3"/>
-    </row>
-    <row r="96" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W95" s="3"/>
+      <c r="X95" s="3"/>
+    </row>
+    <row r="96" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -5574,11 +6041,11 @@
       <c r="J96" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="K96" s="3">
-        <v>0</v>
-      </c>
-      <c r="L96" s="3">
-        <v>0</v>
+      <c r="K96" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="L96" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="M96" s="3">
         <v>0</v>
@@ -5610,8 +6077,14 @@
       <c r="V96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W96" s="3">
+        <v>0</v>
+      </c>
+      <c r="X96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -5672,8 +6145,14 @@
       <c r="V97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W97" s="3">
+        <v>0</v>
+      </c>
+      <c r="X97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -5734,8 +6213,14 @@
       <c r="V98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W98" s="3">
+        <v>0</v>
+      </c>
+      <c r="X98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -5796,70 +6281,82 @@
       <c r="V99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W99" s="3">
+        <v>0</v>
+      </c>
+      <c r="X99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>0</v>
+      </c>
+      <c r="E100" s="3">
+        <v>4700</v>
+      </c>
+      <c r="F100" s="3">
         <v>700</v>
       </c>
-      <c r="E100" s="3">
+      <c r="G100" s="3">
         <v>1400</v>
       </c>
-      <c r="F100" s="3">
+      <c r="H100" s="3">
         <v>1700</v>
       </c>
-      <c r="G100" s="3">
-        <v>0</v>
-      </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
+        <v>0</v>
+      </c>
+      <c r="J100" s="3">
         <v>14900</v>
       </c>
-      <c r="I100" s="3">
-        <v>0</v>
-      </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
+        <v>0</v>
+      </c>
+      <c r="L100" s="3">
         <v>12200</v>
       </c>
-      <c r="K100" s="3">
+      <c r="M100" s="3">
         <v>6500</v>
       </c>
-      <c r="L100" s="3">
+      <c r="N100" s="3">
         <v>-2500</v>
       </c>
-      <c r="M100" s="3">
+      <c r="O100" s="3">
         <v>2900</v>
       </c>
-      <c r="N100" s="3">
+      <c r="P100" s="3">
         <v>1600</v>
       </c>
-      <c r="O100" s="3">
+      <c r="Q100" s="3">
         <v>8500</v>
       </c>
-      <c r="P100" s="3">
+      <c r="R100" s="3">
         <v>54900</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="S100" s="3">
         <v>600</v>
       </c>
-      <c r="R100" s="3">
+      <c r="T100" s="3">
         <v>14900</v>
       </c>
-      <c r="S100" s="3">
+      <c r="U100" s="3">
         <v>1100</v>
       </c>
-      <c r="T100" s="3">
+      <c r="V100" s="3">
         <v>2400</v>
       </c>
-      <c r="U100" s="3">
-        <v>0</v>
-      </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
+        <v>0</v>
+      </c>
+      <c r="X100" s="3">
         <v>2100</v>
       </c>
     </row>
-    <row r="101" spans="3:22" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -5867,7 +6364,7 @@
         <v>0</v>
       </c>
       <c r="E101" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="F101" s="3">
         <v>0</v>
@@ -5882,104 +6379,116 @@
         <v>0</v>
       </c>
       <c r="J101" s="3">
+        <v>0</v>
+      </c>
+      <c r="K101" s="3">
+        <v>0</v>
+      </c>
+      <c r="L101" s="3">
         <v>200</v>
       </c>
-      <c r="K101" s="3">
-        <v>0</v>
-      </c>
-      <c r="L101" s="3">
-        <v>0</v>
-      </c>
       <c r="M101" s="3">
         <v>0</v>
       </c>
       <c r="N101" s="3">
+        <v>0</v>
+      </c>
+      <c r="O101" s="3">
+        <v>0</v>
+      </c>
+      <c r="P101" s="3">
         <v>200</v>
       </c>
-      <c r="O101" s="3">
+      <c r="Q101" s="3">
         <v>-100</v>
       </c>
-      <c r="P101" s="3">
+      <c r="R101" s="3">
         <v>600</v>
       </c>
-      <c r="Q101" s="3">
-        <v>0</v>
-      </c>
-      <c r="R101" s="3">
-        <v>0</v>
-      </c>
       <c r="S101" s="3">
+        <v>0</v>
+      </c>
+      <c r="T101" s="3">
+        <v>0</v>
+      </c>
+      <c r="U101" s="3">
         <v>-100</v>
       </c>
-      <c r="T101" s="3">
-        <v>0</v>
-      </c>
-      <c r="U101" s="3">
-        <v>0</v>
-      </c>
       <c r="V101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W101" s="3">
+        <v>0</v>
+      </c>
+      <c r="X101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-300</v>
+      </c>
+      <c r="E102" s="3">
+        <v>300</v>
+      </c>
+      <c r="F102" s="3">
         <v>-1100</v>
       </c>
-      <c r="E102" s="3">
+      <c r="G102" s="3">
         <v>-600</v>
       </c>
-      <c r="F102" s="3">
+      <c r="H102" s="3">
         <v>-1400</v>
       </c>
-      <c r="G102" s="3">
+      <c r="I102" s="3">
         <v>-5700</v>
       </c>
-      <c r="H102" s="3">
+      <c r="J102" s="3">
         <v>6500</v>
       </c>
-      <c r="I102" s="3">
+      <c r="K102" s="3">
         <v>-3800</v>
       </c>
-      <c r="J102" s="3">
+      <c r="L102" s="3">
         <v>2400</v>
       </c>
-      <c r="K102" s="3">
+      <c r="M102" s="3">
         <v>-11000</v>
       </c>
-      <c r="L102" s="3">
+      <c r="N102" s="3">
         <v>-21800</v>
       </c>
-      <c r="M102" s="3">
+      <c r="O102" s="3">
         <v>-11200</v>
       </c>
-      <c r="N102" s="3">
+      <c r="P102" s="3">
         <v>-6700</v>
       </c>
-      <c r="O102" s="3">
+      <c r="Q102" s="3">
         <v>-2600</v>
       </c>
-      <c r="P102" s="3">
+      <c r="R102" s="3">
         <v>49700</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="S102" s="3">
         <v>-4500</v>
       </c>
-      <c r="R102" s="3">
+      <c r="T102" s="3">
         <v>11800</v>
       </c>
-      <c r="S102" s="3">
+      <c r="U102" s="3">
         <v>-500</v>
       </c>
-      <c r="T102" s="3">
+      <c r="V102" s="3">
         <v>1100</v>
       </c>
-      <c r="U102" s="3">
+      <c r="W102" s="3">
         <v>-1100</v>
       </c>
-      <c r="V102" s="3">
+      <c r="X102" s="3">
         <v>200</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/ELBM_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/ELBM_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="249" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="257" uniqueCount="92">
   <si>
     <t>ELBM</t>
   </si>
@@ -656,110 +656,114 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:X102"/>
+  <dimension ref="A5:Y102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.42578125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="22" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="19" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="23" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:25" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:25" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45838</v>
+      </c>
+      <c r="E7" s="2">
         <v>45747</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45657</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45565</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45473</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45382</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45291</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45199</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45107</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>45016</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44926</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44834</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44742</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44651</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44561</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44469</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44377</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44286</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>44196</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>44104</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>44012</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>43921</v>
       </c>
     </row>
-    <row r="8" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:25" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
@@ -790,8 +794,8 @@
       <c r="L8" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="M8" s="3">
-        <v>0</v>
+      <c r="M8" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="N8" s="3">
         <v>0</v>
@@ -826,8 +830,11 @@
       <c r="X8" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="9" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="Y8" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:25" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
@@ -894,8 +901,11 @@
       <c r="X9" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="10" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="Y9" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="10" spans="1:25" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
@@ -962,8 +972,11 @@
       <c r="X10" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="11" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="Y10" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="11" spans="1:25" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -988,8 +1001,9 @@
       <c r="V11" s="3"/>
       <c r="W11" s="3"/>
       <c r="X11" s="3"/>
-    </row>
-    <row r="12" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="Y11" s="3"/>
+    </row>
+    <row r="12" spans="1:25" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -1020,44 +1034,47 @@
       <c r="L12" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="M12" s="3">
+      <c r="M12" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="N12" s="3">
         <v>600</v>
       </c>
-      <c r="N12" s="3">
+      <c r="O12" s="3">
         <v>1300</v>
       </c>
-      <c r="O12" s="3">
+      <c r="P12" s="3">
         <v>1100</v>
       </c>
-      <c r="P12" s="3">
+      <c r="Q12" s="3">
         <v>400</v>
       </c>
-      <c r="Q12" s="3">
+      <c r="R12" s="3">
         <v>2900</v>
       </c>
-      <c r="R12" s="3">
+      <c r="S12" s="3">
         <v>1200</v>
       </c>
-      <c r="S12" s="3">
+      <c r="T12" s="3">
         <v>400</v>
       </c>
-      <c r="T12" s="3">
+      <c r="U12" s="3">
         <v>100</v>
       </c>
-      <c r="U12" s="3">
+      <c r="V12" s="3">
         <v>300</v>
       </c>
-      <c r="V12" s="3">
+      <c r="W12" s="3">
         <v>100</v>
       </c>
-      <c r="W12" s="3">
-        <v>0</v>
-      </c>
       <c r="X12" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="13" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="Y12" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" spans="1:25" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1124,13 +1141,16 @@
       <c r="X13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="Y13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:25" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="E14" s="3">
         <v>0</v>
@@ -1139,61 +1159,64 @@
         <v>0</v>
       </c>
       <c r="G14" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="H14" s="3">
         <v>-100</v>
       </c>
       <c r="I14" s="3">
+        <v>-100</v>
+      </c>
+      <c r="J14" s="3">
         <v>39300</v>
       </c>
-      <c r="J14" s="3">
+      <c r="K14" s="3">
         <v>200</v>
       </c>
-      <c r="K14" s="3">
-        <v>0</v>
-      </c>
       <c r="L14" s="3">
+        <v>0</v>
+      </c>
+      <c r="M14" s="3">
         <v>13800</v>
       </c>
-      <c r="M14" s="3">
+      <c r="N14" s="3">
         <v>-1300</v>
       </c>
-      <c r="N14" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="O14" s="3" t="s">
         <v>4</v>
       </c>
       <c r="P14" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="Q14" s="3">
-        <v>0</v>
+      <c r="Q14" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="R14" s="3">
         <v>0</v>
       </c>
       <c r="S14" s="3">
+        <v>0</v>
+      </c>
+      <c r="T14" s="3">
         <v>1600</v>
       </c>
-      <c r="T14" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="U14" s="3">
+      <c r="U14" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="V14" s="3">
         <v>-5700</v>
       </c>
-      <c r="V14" s="3">
-        <v>0</v>
-      </c>
-      <c r="W14" s="3" t="s">
-        <v>4</v>
+      <c r="W14" s="3">
+        <v>0</v>
       </c>
       <c r="X14" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="15" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="Y14" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="15" spans="1:25" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1260,8 +1283,11 @@
       <c r="X15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="Y15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:25" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1283,8 +1309,9 @@
       <c r="V16" s="3"/>
       <c r="W16" s="3"/>
       <c r="X16" s="3"/>
-    </row>
-    <row r="17" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y16" s="3"/>
+    </row>
+    <row r="17" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
@@ -1292,7 +1319,7 @@
         <v>2500</v>
       </c>
       <c r="E17" s="3">
-        <v>2400</v>
+        <v>2500</v>
       </c>
       <c r="F17" s="3">
         <v>2400</v>
@@ -1301,58 +1328,61 @@
         <v>2400</v>
       </c>
       <c r="H17" s="3">
+        <v>2400</v>
+      </c>
+      <c r="I17" s="3">
         <v>2300</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>900</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>2900</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>3300</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>2800</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>4200</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>4800</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>3900</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>2500</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>6600</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>6500</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>5300</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>2300</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>-3000</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>1400</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>1500</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>1800</v>
       </c>
     </row>
-    <row r="18" spans="3:24" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
@@ -1360,7 +1390,7 @@
         <v>-2500</v>
       </c>
       <c r="E18" s="3">
-        <v>-2400</v>
+        <v>-2500</v>
       </c>
       <c r="F18" s="3">
         <v>-2400</v>
@@ -1369,58 +1399,61 @@
         <v>-2400</v>
       </c>
       <c r="H18" s="3">
+        <v>-2400</v>
+      </c>
+      <c r="I18" s="3">
         <v>-2300</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>-900</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>-2900</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>-3300</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>-2800</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>-4200</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>-4800</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>-3900</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>-2500</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>-6600</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>-6500</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>-5300</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>-2300</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>3000</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>-1400</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>-1500</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>-1800</v>
       </c>
     </row>
-    <row r="19" spans="3:24" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1445,61 +1478,62 @@
       <c r="V19" s="3"/>
       <c r="W19" s="3"/>
       <c r="X19" s="3"/>
-    </row>
-    <row r="20" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y19" s="3"/>
+    </row>
+    <row r="20" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
-        <v>6300</v>
+        <v>-3700</v>
       </c>
       <c r="E20" s="3">
+        <v>3600</v>
+      </c>
+      <c r="F20" s="3">
         <v>2100</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>-2200</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>900</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>6000</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>-11100</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>3700</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>-12100</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>-1500</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>14500</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>-2800</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>11400</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>4800</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>-8900</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>-4000</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>-1100</v>
-      </c>
-      <c r="T20" s="3">
-        <v>-100</v>
       </c>
       <c r="U20" s="3">
         <v>-100</v>
@@ -1508,116 +1542,122 @@
         <v>-100</v>
       </c>
       <c r="W20" s="3">
+        <v>-100</v>
+      </c>
+      <c r="X20" s="3">
         <v>-200</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Y20" s="3">
         <v>-300</v>
       </c>
     </row>
-    <row r="21" spans="3:24" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
-        <v>-8800</v>
+        <v>1200</v>
       </c>
       <c r="E21" s="3">
+        <v>-6100</v>
+      </c>
+      <c r="F21" s="3">
         <v>-4500</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>-200</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>-3300</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>-8300</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>10100</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>-6700</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>8800</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>-1300</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>10400</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>-7600</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>7500</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>2300</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>-15500</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>-10500</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>-6400</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>-2400</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>2900</v>
       </c>
-      <c r="V21" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="W21" s="3" t="s">
         <v>4</v>
       </c>
       <c r="X21" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="22" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y21" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="22" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="D22" s="3" t="s">
-        <v>4</v>
+      <c r="D22" s="3">
+        <v>1900</v>
       </c>
       <c r="E22" s="3">
+        <v>2700</v>
+      </c>
+      <c r="F22" s="3">
         <v>1500</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>2000</v>
       </c>
-      <c r="G22" s="3">
+      <c r="H22" s="3">
         <v>1000</v>
       </c>
-      <c r="H22" s="3">
+      <c r="I22" s="3">
         <v>700</v>
       </c>
-      <c r="I22" s="3">
+      <c r="J22" s="3">
         <v>6200</v>
       </c>
-      <c r="J22" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="K22" s="3" t="s">
         <v>4</v>
       </c>
       <c r="L22" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="M22" s="3">
-        <v>0</v>
-      </c>
-      <c r="N22" s="3" t="s">
-        <v>4</v>
+      <c r="M22" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="N22" s="3">
+        <v>0</v>
       </c>
       <c r="O22" s="3" t="s">
         <v>4</v>
@@ -1628,18 +1668,18 @@
       <c r="Q22" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="R22" s="3">
-        <v>0</v>
+      <c r="R22" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="S22" s="3">
         <v>0</v>
       </c>
       <c r="T22" s="3">
+        <v>0</v>
+      </c>
+      <c r="U22" s="3">
         <v>100</v>
       </c>
-      <c r="U22" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="V22" s="3" t="s">
         <v>4</v>
       </c>
@@ -1649,76 +1689,82 @@
       <c r="X22" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="23" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y22" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="23" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-500</v>
+      </c>
+      <c r="E23" s="3">
         <v>-8800</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>-6000</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>-2200</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>-4200</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>-9000</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>-35500</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>-6800</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>8900</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>-15000</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>10300</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>-7600</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>7500</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>2300</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>-15500</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>-10500</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>-6400</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>-2500</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>2900</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>-1500</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>-1700</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>-2100</v>
       </c>
     </row>
-    <row r="24" spans="3:24" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
@@ -1749,8 +1795,8 @@
       <c r="L24" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="M24" s="3">
-        <v>0</v>
+      <c r="M24" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="N24" s="3">
         <v>0</v>
@@ -1785,8 +1831,11 @@
       <c r="X24" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="25" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y24" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1853,144 +1902,153 @@
       <c r="X25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-500</v>
+      </c>
+      <c r="E26" s="3">
         <v>-8800</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>-6000</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>-2200</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>-4200</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>-9000</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>-35500</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>-6800</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>8900</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>-15000</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>10300</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>-7600</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>7500</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>2300</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>-15500</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>-10500</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>-6400</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>-2500</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>2900</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>-1500</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>-1700</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>-2100</v>
       </c>
     </row>
-    <row r="27" spans="3:24" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-500</v>
+      </c>
+      <c r="E27" s="3">
         <v>-8800</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>-6000</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>-2200</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>-4200</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>-9000</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>-35500</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>-6800</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>8900</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>-15000</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>10300</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>-7600</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>7500</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>2300</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>-15500</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>-10500</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>-6400</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>-2500</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>2900</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>-1500</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>-1700</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>-2100</v>
       </c>
     </row>
-    <row r="28" spans="3:24" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2057,8 +2115,11 @@
       <c r="X28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2125,8 +2186,11 @@
       <c r="X29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2193,8 +2257,11 @@
       <c r="X30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2261,61 +2328,64 @@
       <c r="X31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
-        <v>-6300</v>
+        <v>3700</v>
       </c>
       <c r="E32" s="3">
+        <v>-3600</v>
+      </c>
+      <c r="F32" s="3">
         <v>-2100</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>2200</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>-900</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>-6000</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>11100</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>-3700</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>12100</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>1500</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>-14500</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>2800</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>-11400</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>-4800</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>8900</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>4000</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>1100</v>
-      </c>
-      <c r="T32" s="3">
-        <v>100</v>
       </c>
       <c r="U32" s="3">
         <v>100</v>
@@ -2324,81 +2394,87 @@
         <v>100</v>
       </c>
       <c r="W32" s="3">
+        <v>100</v>
+      </c>
+      <c r="X32" s="3">
         <v>200</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Y32" s="3">
         <v>300</v>
       </c>
     </row>
-    <row r="33" spans="2:24" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-500</v>
+      </c>
+      <c r="E33" s="3">
         <v>-8800</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>-6000</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>-2200</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>-4200</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>-9000</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>-35500</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>-6800</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>8900</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>-15000</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>10300</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>-7600</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>7500</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>2300</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>-15500</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>-10500</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>-6400</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>-2500</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>2900</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>-1500</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>-1700</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>-2100</v>
       </c>
     </row>
-    <row r="34" spans="2:24" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2465,149 +2541,158 @@
       <c r="X34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-500</v>
+      </c>
+      <c r="E35" s="3">
         <v>-8800</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>-6000</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>-2200</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>-4200</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>-9000</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>-35500</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>-6800</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>8900</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>-15000</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>10300</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>-7600</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>7500</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>2300</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>-15500</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>-10500</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>-6400</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>-2500</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>2900</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>-1500</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>-1700</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>-2100</v>
       </c>
     </row>
-    <row r="37" spans="2:24" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:25" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:24" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45838</v>
+      </c>
+      <c r="E38" s="2">
         <v>45747</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45657</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45565</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45473</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45382</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45291</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45199</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45107</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>45016</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44926</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44834</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44742</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44651</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44561</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44469</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44377</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44286</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>44196</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>44104</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>44012</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>43921</v>
       </c>
     </row>
-    <row r="39" spans="2:24" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2632,8 +2717,9 @@
       <c r="V39" s="3"/>
       <c r="W39" s="3"/>
       <c r="X39" s="3"/>
-    </row>
-    <row r="40" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y39" s="3"/>
+    </row>
+    <row r="40" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2658,76 +2744,80 @@
       <c r="V40" s="3"/>
       <c r="W40" s="3"/>
       <c r="X40" s="3"/>
-    </row>
-    <row r="41" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y40" s="3"/>
+    </row>
+    <row r="41" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>2100</v>
+      </c>
+      <c r="E41" s="3">
         <v>2200</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>2600</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>2400</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>3500</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>4200</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>5700</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>11100</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>4700</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>8300</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>8000</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>18900</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>40700</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>51900</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>58600</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>61200</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>11500</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>16000</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>4200</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>4700</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>3600</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>4600</v>
       </c>
     </row>
-    <row r="42" spans="2:24" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -2738,53 +2828,53 @@
         <v>0</v>
       </c>
       <c r="F42" s="3">
+        <v>0</v>
+      </c>
+      <c r="G42" s="3">
         <v>100</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>200</v>
       </c>
-      <c r="H42" s="3">
+      <c r="I42" s="3">
         <v>600</v>
-      </c>
-      <c r="I42" s="3">
-        <v>500</v>
       </c>
       <c r="J42" s="3">
         <v>500</v>
       </c>
       <c r="K42" s="3">
+        <v>500</v>
+      </c>
+      <c r="L42" s="3">
         <v>900</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>1200</v>
       </c>
-      <c r="M42" s="3">
+      <c r="N42" s="3">
         <v>400</v>
       </c>
-      <c r="N42" s="3">
+      <c r="O42" s="3">
         <v>700</v>
       </c>
-      <c r="O42" s="3">
+      <c r="P42" s="3">
         <v>1100</v>
       </c>
-      <c r="P42" s="3">
+      <c r="Q42" s="3">
         <v>2100</v>
       </c>
-      <c r="Q42" s="3">
+      <c r="R42" s="3">
         <v>1800</v>
-      </c>
-      <c r="R42" s="3">
-        <v>2300</v>
       </c>
       <c r="S42" s="3">
         <v>2300</v>
       </c>
       <c r="T42" s="3">
+        <v>2300</v>
+      </c>
+      <c r="U42" s="3">
         <v>3500</v>
       </c>
-      <c r="U42" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="V42" s="3" t="s">
         <v>4</v>
       </c>
@@ -2794,76 +2884,82 @@
       <c r="X42" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="43" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y42" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="43" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>300</v>
+      </c>
+      <c r="E43" s="3">
         <v>600</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>900</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>200</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>300</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>400</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>800</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>700</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>600</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>900</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>3100</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>3500</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>1700</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>1300</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>1000</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>1100</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>600</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>400</v>
-      </c>
-      <c r="U43" s="3">
-        <v>200</v>
       </c>
       <c r="V43" s="3">
         <v>200</v>
       </c>
       <c r="W43" s="3">
+        <v>200</v>
+      </c>
+      <c r="X43" s="3">
         <v>100</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Y43" s="3">
         <v>400</v>
       </c>
     </row>
-    <row r="44" spans="2:24" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -2894,8 +2990,8 @@
       <c r="L44" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="M44" s="3">
-        <v>0</v>
+      <c r="M44" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="N44" s="3">
         <v>0</v>
@@ -2930,8 +3026,11 @@
       <c r="X44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
@@ -2962,112 +3061,118 @@
       <c r="L45" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="M45" s="3">
+      <c r="M45" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="N45" s="3">
         <v>2100</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>2500</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>2100</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>1300</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>600</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>400</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>1000</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>900</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>6100</v>
       </c>
-      <c r="V45" s="3">
+      <c r="W45" s="3">
         <v>600</v>
       </c>
-      <c r="W45" s="3">
+      <c r="X45" s="3">
         <v>400</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Y45" s="3">
         <v>600</v>
       </c>
     </row>
-    <row r="46" spans="2:24" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>3100</v>
+      </c>
+      <c r="E46" s="3">
         <v>3700</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>4000</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>3400</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>5100</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>6500</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>8000</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>12900</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>6500</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>10700</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>13500</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>25700</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>45600</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>56600</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>61900</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>64900</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>15300</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>20700</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>10500</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>5500</v>
       </c>
-      <c r="W46" s="3">
+      <c r="X46" s="3">
         <v>4100</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Y46" s="3">
         <v>5600</v>
       </c>
     </row>
-    <row r="47" spans="2:24" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -3098,8 +3203,8 @@
       <c r="L47" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="M47" s="3">
-        <v>0</v>
+      <c r="M47" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="N47" s="3">
         <v>0</v>
@@ -3134,61 +3239,64 @@
       <c r="X47" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>102600</v>
+      </c>
+      <c r="E48" s="3">
         <v>100700</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>100400</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>102800</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>102300</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>102900</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>103700</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>142600</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>142100</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>133700</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>173100</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>144300</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>129800</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>113700</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>104700</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>95000</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>93900</v>
-      </c>
-      <c r="T48" s="3">
-        <v>92300</v>
       </c>
       <c r="U48" s="3">
         <v>92300</v>
@@ -3202,8 +3310,11 @@
       <c r="X48" s="3">
         <v>92300</v>
       </c>
-    </row>
-    <row r="49" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y48" s="3">
+        <v>92300</v>
+      </c>
+    </row>
+    <row r="49" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
@@ -3270,8 +3381,11 @@
       <c r="X49" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="50" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y49" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -3338,8 +3452,11 @@
       <c r="X50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -3406,13 +3523,16 @@
       <c r="X51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
-        <v>900</v>
+        <v>1000</v>
       </c>
       <c r="E52" s="3">
         <v>900</v>
@@ -3429,17 +3549,17 @@
       <c r="I52" s="3">
         <v>900</v>
       </c>
-      <c r="J52" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="K52" s="3">
+      <c r="J52" s="3">
+        <v>900</v>
+      </c>
+      <c r="K52" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="L52" s="3">
         <v>1700</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>2500</v>
-      </c>
-      <c r="M52" s="3">
-        <v>900</v>
       </c>
       <c r="N52" s="3">
         <v>900</v>
@@ -3474,8 +3594,11 @@
       <c r="X52" s="3">
         <v>900</v>
       </c>
-    </row>
-    <row r="53" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y52" s="3">
+        <v>900</v>
+      </c>
+    </row>
+    <row r="53" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -3542,76 +3665,82 @@
       <c r="X53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>106800</v>
+      </c>
+      <c r="E54" s="3">
         <v>105400</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>105300</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>107100</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>108300</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>110300</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>112600</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>155500</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>150300</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>146900</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>187500</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>170900</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>176400</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>171300</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>167600</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>160800</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>110100</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>114000</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>103700</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>98700</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>97300</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>98800</v>
       </c>
     </row>
-    <row r="55" spans="3:24" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -3636,8 +3765,9 @@
       <c r="V55" s="3"/>
       <c r="W55" s="3"/>
       <c r="X55" s="3"/>
-    </row>
-    <row r="56" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y55" s="3"/>
+    </row>
+    <row r="56" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -3662,76 +3792,80 @@
       <c r="V56" s="3"/>
       <c r="W56" s="3"/>
       <c r="X56" s="3"/>
-    </row>
-    <row r="57" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y56" s="3"/>
+    </row>
+    <row r="57" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
-        <v>4900</v>
+        <v>2700</v>
       </c>
       <c r="E57" s="3">
+        <v>4200</v>
+      </c>
+      <c r="F57" s="3">
         <v>2500</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>3200</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>3500</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>5700</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>6700</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>7100</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>12900</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>11300</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>18900</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>8200</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>9900</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>5600</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>3500</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>2000</v>
       </c>
-      <c r="S57" s="3">
-        <v>0</v>
-      </c>
       <c r="T57" s="3">
+        <v>0</v>
+      </c>
+      <c r="U57" s="3">
         <v>200</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>400</v>
       </c>
-      <c r="V57" s="3">
-        <v>0</v>
-      </c>
       <c r="W57" s="3">
         <v>0</v>
       </c>
       <c r="X57" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y57" s="3">
         <v>100</v>
       </c>
     </row>
-    <row r="58" spans="3:24" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
@@ -3739,35 +3873,35 @@
         <v>47400</v>
       </c>
       <c r="E58" s="3">
+        <v>47400</v>
+      </c>
+      <c r="F58" s="3">
         <v>44500</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>34300</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>35300</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>35000</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>30400</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>40900</v>
       </c>
-      <c r="K58" s="3">
-        <v>0</v>
-      </c>
       <c r="L58" s="3">
         <v>0</v>
       </c>
       <c r="M58" s="3">
+        <v>0</v>
+      </c>
+      <c r="N58" s="3">
         <v>25700</v>
       </c>
-      <c r="N58" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="O58" s="3" t="s">
         <v>4</v>
       </c>
@@ -3780,298 +3914,313 @@
       <c r="R58" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="S58" s="3">
-        <v>0</v>
+      <c r="S58" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="T58" s="3">
         <v>0</v>
       </c>
-      <c r="U58" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="V58" s="3">
+      <c r="U58" s="3">
+        <v>0</v>
+      </c>
+      <c r="V58" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="W58" s="3">
         <v>7000</v>
       </c>
-      <c r="W58" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="X58" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="59" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y58" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="59" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>1300</v>
+      </c>
+      <c r="E59" s="3">
+        <v>600</v>
+      </c>
+      <c r="F59" s="3">
+        <v>1100</v>
+      </c>
+      <c r="G59" s="3">
+        <v>2700</v>
+      </c>
+      <c r="H59" s="3">
+        <v>2600</v>
+      </c>
+      <c r="I59" s="3">
+        <v>1500</v>
+      </c>
+      <c r="J59" s="3">
+        <v>1100</v>
+      </c>
+      <c r="K59" s="3">
+        <v>3000</v>
+      </c>
+      <c r="L59" s="3">
+        <v>4000</v>
+      </c>
+      <c r="M59" s="3">
+        <v>9100</v>
+      </c>
+      <c r="N59" s="3">
+        <v>9600</v>
+      </c>
+      <c r="O59" s="3">
+        <v>400</v>
+      </c>
+      <c r="P59" s="3">
+        <v>1200</v>
+      </c>
+      <c r="Q59" s="3">
         <v>500</v>
       </c>
-      <c r="E59" s="3">
-        <v>1100</v>
-      </c>
-      <c r="F59" s="3">
-        <v>2700</v>
-      </c>
-      <c r="G59" s="3">
-        <v>2600</v>
-      </c>
-      <c r="H59" s="3">
-        <v>1500</v>
-      </c>
-      <c r="I59" s="3">
-        <v>1100</v>
-      </c>
-      <c r="J59" s="3">
-        <v>3000</v>
-      </c>
-      <c r="K59" s="3">
-        <v>4000</v>
-      </c>
-      <c r="L59" s="3">
-        <v>9100</v>
-      </c>
-      <c r="M59" s="3">
-        <v>9600</v>
-      </c>
-      <c r="N59" s="3">
+      <c r="R59" s="3">
+        <v>1200</v>
+      </c>
+      <c r="S59" s="3">
+        <v>100</v>
+      </c>
+      <c r="T59" s="3">
+        <v>600</v>
+      </c>
+      <c r="U59" s="3">
         <v>400</v>
       </c>
-      <c r="O59" s="3">
-        <v>1200</v>
-      </c>
-      <c r="P59" s="3">
-        <v>500</v>
-      </c>
-      <c r="Q59" s="3">
-        <v>1200</v>
-      </c>
-      <c r="R59" s="3">
-        <v>100</v>
-      </c>
-      <c r="S59" s="3">
-        <v>600</v>
-      </c>
-      <c r="T59" s="3">
-        <v>400</v>
-      </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>2400</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>1000</v>
       </c>
-      <c r="W59" s="3">
-        <v>0</v>
-      </c>
       <c r="X59" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="60" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y59" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="60" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>58400</v>
+      </c>
+      <c r="E60" s="3">
         <v>57000</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>50000</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>47400</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>47200</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>46900</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>42500</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>53900</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>18800</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>21100</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>54100</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>8700</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>11100</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>6000</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>4700</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>2100</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>600</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>500</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>2800</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>8000</v>
       </c>
-      <c r="W60" s="3">
-        <v>0</v>
-      </c>
       <c r="X60" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y60" s="3">
         <v>100</v>
       </c>
     </row>
-    <row r="61" spans="3:24" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>4400</v>
+      </c>
+      <c r="E61" s="3">
         <v>5600</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>5500</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>5800</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>5300</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>4100</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>3400</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>2700</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>39300</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>45100</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>5100</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>30000</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>27600</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>26200</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>23600</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>22400</v>
       </c>
-      <c r="S61" s="3">
-        <v>0</v>
-      </c>
       <c r="T61" s="3">
-        <v>6700</v>
+        <v>0</v>
       </c>
       <c r="U61" s="3">
         <v>6700</v>
       </c>
       <c r="V61" s="3">
-        <v>0</v>
+        <v>6700</v>
       </c>
       <c r="W61" s="3">
-        <v>7000</v>
+        <v>0</v>
       </c>
       <c r="X61" s="3">
         <v>7000</v>
       </c>
-    </row>
-    <row r="62" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y61" s="3">
+        <v>7000</v>
+      </c>
+    </row>
+    <row r="62" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>2700</v>
+      </c>
+      <c r="E62" s="3">
         <v>3100</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>2900</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>3200</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>2900</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>2800</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>3000</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>1200</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>1400</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>1300</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>1800</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>20100</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>19500</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>34900</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>39400</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>29300</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>1300</v>
-      </c>
-      <c r="T62" s="3">
-        <v>2000</v>
       </c>
       <c r="U62" s="3">
         <v>2000</v>
       </c>
       <c r="V62" s="3">
+        <v>2000</v>
+      </c>
+      <c r="W62" s="3">
         <v>2700</v>
       </c>
-      <c r="W62" s="3">
+      <c r="X62" s="3">
         <v>3200</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Y62" s="3">
         <v>3000</v>
       </c>
     </row>
-    <row r="63" spans="3:24" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -4138,8 +4287,11 @@
       <c r="X63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -4206,8 +4358,11 @@
       <c r="X64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -4274,76 +4429,82 @@
       <c r="X65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>69300</v>
+      </c>
+      <c r="E66" s="3">
         <v>67900</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>60600</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>58600</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>57100</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>55300</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>49500</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>58500</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>60300</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>68200</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>61000</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>58800</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>58200</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>67100</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>67600</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>53900</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>1900</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>9300</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>11500</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>10700</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>10200</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>10100</v>
       </c>
     </row>
-    <row r="67" spans="2:24" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -4368,8 +4529,9 @@
       <c r="V67" s="3"/>
       <c r="W67" s="3"/>
       <c r="X67" s="3"/>
-    </row>
-    <row r="68" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y67" s="3"/>
+    </row>
+    <row r="68" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -4436,8 +4598,11 @@
       <c r="X68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -4504,8 +4669,11 @@
       <c r="X69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -4572,8 +4740,11 @@
       <c r="X70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -4640,76 +4811,82 @@
       <c r="X71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-211400</v>
+      </c>
+      <c r="E72" s="3">
         <v>-200100</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-191100</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-197100</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-192400</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-190200</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-185900</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>-147800</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-144100</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>-149700</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>-162900</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>-173900</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>-166600</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>-174000</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>-176800</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>-161500</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>-151200</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>-145000</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>-143000</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>-145900</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>-145200</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>-143600</v>
       </c>
     </row>
-    <row r="73" spans="2:24" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -4776,8 +4953,11 @@
       <c r="X73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -4844,8 +5024,11 @@
       <c r="X74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -4912,76 +5095,82 @@
       <c r="X75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>37500</v>
+      </c>
+      <c r="E76" s="3">
         <v>37400</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>44700</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>48500</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>51200</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>55000</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>63100</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>96900</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>90000</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>78700</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>126500</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>112100</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>118200</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>104200</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>100000</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>107000</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>108200</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>104700</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>92200</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>88000</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>87200</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>88700</v>
       </c>
     </row>
-    <row r="77" spans="2:24" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -5048,149 +5237,158 @@
       <c r="X77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:25" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:24" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45838</v>
+      </c>
+      <c r="E80" s="2">
         <v>45747</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45657</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45565</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45473</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45382</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45291</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45199</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45107</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>45016</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44926</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44834</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44742</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44651</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44561</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44469</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44377</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44286</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>44196</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>44104</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>44012</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>43921</v>
       </c>
     </row>
-    <row r="81" spans="3:24" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-500</v>
+      </c>
+      <c r="E81" s="3">
         <v>-8800</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>-6000</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>-2200</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>-4200</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>-9000</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>-35500</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>-6800</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>8900</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>-15000</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>10300</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>-7600</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>7500</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>2300</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>-15500</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>-10500</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>-6400</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>-2500</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>2900</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>-1500</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>-1700</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>-2100</v>
       </c>
     </row>
-    <row r="82" spans="3:24" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -5215,8 +5413,9 @@
       <c r="V82" s="3"/>
       <c r="W82" s="3"/>
       <c r="X82" s="3"/>
-    </row>
-    <row r="83" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y82" s="3"/>
+    </row>
+    <row r="83" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
@@ -5238,17 +5437,17 @@
       <c r="I83" s="3">
         <v>0</v>
       </c>
-      <c r="J83" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="K83" s="3">
-        <v>0</v>
+      <c r="J83" s="3">
+        <v>0</v>
+      </c>
+      <c r="K83" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="L83" s="3">
         <v>0</v>
       </c>
-      <c r="M83" s="3" t="s">
-        <v>4</v>
+      <c r="M83" s="3">
+        <v>0</v>
       </c>
       <c r="N83" s="3" t="s">
         <v>4</v>
@@ -5256,14 +5455,14 @@
       <c r="O83" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="P83" s="3">
-        <v>0</v>
+      <c r="P83" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="Q83" s="3">
         <v>0</v>
       </c>
-      <c r="R83" s="3" t="s">
-        <v>4</v>
+      <c r="R83" s="3">
+        <v>0</v>
       </c>
       <c r="S83" s="3" t="s">
         <v>4</v>
@@ -5283,8 +5482,11 @@
       <c r="X83" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="84" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y83" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="84" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -5351,8 +5553,11 @@
       <c r="X84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -5419,8 +5624,11 @@
       <c r="X85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -5487,8 +5695,11 @@
       <c r="X86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -5555,8 +5766,11 @@
       <c r="X87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -5623,76 +5837,82 @@
       <c r="X88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>-3300</v>
+      </c>
+      <c r="E89" s="3">
         <v>-100</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>-4300</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>-2200</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>-2800</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>-3000</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>-4500</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>-8900</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>-3000</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>-700</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>-6600</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>-500</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>-5300</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>-3500</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>-4900</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>-5300</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>-3600</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>-3100</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>-1500</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>-1200</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>-1100</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>-1800</v>
       </c>
     </row>
-    <row r="90" spans="3:24" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -5717,65 +5937,66 @@
       <c r="V90" s="3"/>
       <c r="W90" s="3"/>
       <c r="X90" s="3"/>
-    </row>
-    <row r="91" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y90" s="3"/>
+    </row>
+    <row r="91" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-300</v>
+      </c>
+      <c r="E91" s="3">
         <v>-200</v>
-      </c>
-      <c r="E91" s="3">
-        <v>-100</v>
       </c>
       <c r="F91" s="3">
         <v>-100</v>
       </c>
       <c r="G91" s="3">
+        <v>-100</v>
+      </c>
+      <c r="H91" s="3">
         <v>200</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-400</v>
-      </c>
-      <c r="I91" s="3">
-        <v>400</v>
       </c>
       <c r="J91" s="3">
         <v>400</v>
       </c>
       <c r="K91" s="3">
+        <v>400</v>
+      </c>
+      <c r="L91" s="3">
         <v>-1900</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-9100</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-15600</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-18800</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-8700</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-4500</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-6100</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-600</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>500</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>-500</v>
       </c>
-      <c r="U91" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="V91" s="3" t="s">
         <v>4</v>
       </c>
@@ -5785,8 +6006,11 @@
       <c r="X91" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="92" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y91" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="92" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -5853,8 +6077,11 @@
       <c r="X92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -5921,62 +6148,65 @@
       <c r="X93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-300</v>
+      </c>
+      <c r="E94" s="3">
         <v>-200</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-100</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>300</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>700</v>
       </c>
-      <c r="H94" s="3">
-        <v>0</v>
-      </c>
       <c r="I94" s="3">
+        <v>0</v>
+      </c>
+      <c r="J94" s="3">
         <v>-1200</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>600</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-800</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-9100</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-10900</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-18800</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-8700</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-5100</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-6100</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-500</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-1500</v>
       </c>
-      <c r="T94" s="3">
-        <v>0</v>
-      </c>
       <c r="U94" s="3">
         <v>0</v>
       </c>
@@ -5989,8 +6219,11 @@
       <c r="X94" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="95" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y94" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="95" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -6015,8 +6248,9 @@
       <c r="V95" s="3"/>
       <c r="W95" s="3"/>
       <c r="X95" s="3"/>
-    </row>
-    <row r="96" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y95" s="3"/>
+    </row>
+    <row r="96" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -6047,8 +6281,8 @@
       <c r="L96" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="M96" s="3">
-        <v>0</v>
+      <c r="M96" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="N96" s="3">
         <v>0</v>
@@ -6083,8 +6317,11 @@
       <c r="X96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -6151,8 +6388,11 @@
       <c r="X97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -6219,8 +6459,11 @@
       <c r="X98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -6287,76 +6530,82 @@
       <c r="X99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
-        <v>0</v>
+        <v>3400</v>
       </c>
       <c r="E100" s="3">
+        <v>0</v>
+      </c>
+      <c r="F100" s="3">
         <v>4700</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>700</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>1400</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>1700</v>
       </c>
-      <c r="I100" s="3">
-        <v>0</v>
-      </c>
       <c r="J100" s="3">
+        <v>0</v>
+      </c>
+      <c r="K100" s="3">
         <v>14900</v>
       </c>
-      <c r="K100" s="3">
-        <v>0</v>
-      </c>
       <c r="L100" s="3">
+        <v>0</v>
+      </c>
+      <c r="M100" s="3">
         <v>12200</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>6500</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-2500</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>2900</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>1600</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>8500</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>54900</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>600</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>14900</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>1100</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>2400</v>
       </c>
-      <c r="W100" s="3">
-        <v>0</v>
-      </c>
       <c r="X100" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y100" s="3">
         <v>2100</v>
       </c>
     </row>
-    <row r="101" spans="3:24" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -6364,11 +6613,11 @@
         <v>0</v>
       </c>
       <c r="E101" s="3">
+        <v>0</v>
+      </c>
+      <c r="F101" s="3">
         <v>100</v>
       </c>
-      <c r="F101" s="3">
-        <v>0</v>
-      </c>
       <c r="G101" s="3">
         <v>0</v>
       </c>
@@ -6385,11 +6634,11 @@
         <v>0</v>
       </c>
       <c r="L101" s="3">
+        <v>0</v>
+      </c>
+      <c r="M101" s="3">
         <v>200</v>
       </c>
-      <c r="M101" s="3">
-        <v>0</v>
-      </c>
       <c r="N101" s="3">
         <v>0</v>
       </c>
@@ -6397,98 +6646,104 @@
         <v>0</v>
       </c>
       <c r="P101" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q101" s="3">
         <v>200</v>
       </c>
-      <c r="Q101" s="3">
+      <c r="R101" s="3">
         <v>-100</v>
       </c>
-      <c r="R101" s="3">
+      <c r="S101" s="3">
         <v>600</v>
       </c>
-      <c r="S101" s="3">
-        <v>0</v>
-      </c>
       <c r="T101" s="3">
         <v>0</v>
       </c>
       <c r="U101" s="3">
+        <v>0</v>
+      </c>
+      <c r="V101" s="3">
         <v>-100</v>
       </c>
-      <c r="V101" s="3">
-        <v>0</v>
-      </c>
       <c r="W101" s="3">
         <v>0</v>
       </c>
       <c r="X101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-200</v>
+      </c>
+      <c r="E102" s="3">
         <v>-300</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>300</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-1100</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-600</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-1400</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-5700</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>6500</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-3800</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>2400</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-11000</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-21800</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-11200</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>-6700</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>-2600</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>49700</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>-4500</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>11800</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>-500</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>1100</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>-1100</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>200</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/ELBM_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/ELBM_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="266" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="285" uniqueCount="92">
   <si>
     <t>ELBM</t>
   </si>
@@ -656,118 +656,125 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:Z102"/>
+  <dimension ref="A5:AB102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.42578125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="16" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="20" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="24" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="22" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="26" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:28" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:28" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>46112</v>
+      </c>
+      <c r="E7" s="2">
+        <v>46022</v>
+      </c>
+      <c r="F7" s="2">
         <v>45930</v>
       </c>
-      <c r="E7" s="2">
+      <c r="G7" s="2">
         <v>45838</v>
       </c>
-      <c r="F7" s="2">
+      <c r="H7" s="2">
         <v>45747</v>
       </c>
-      <c r="G7" s="2">
+      <c r="I7" s="2">
         <v>45657</v>
       </c>
-      <c r="H7" s="2">
+      <c r="J7" s="2">
         <v>45565</v>
       </c>
-      <c r="I7" s="2">
+      <c r="K7" s="2">
         <v>45473</v>
       </c>
-      <c r="J7" s="2">
+      <c r="L7" s="2">
         <v>45382</v>
       </c>
-      <c r="K7" s="2">
+      <c r="M7" s="2">
         <v>45291</v>
       </c>
-      <c r="L7" s="2">
+      <c r="N7" s="2">
         <v>45199</v>
       </c>
-      <c r="M7" s="2">
+      <c r="O7" s="2">
         <v>45107</v>
       </c>
-      <c r="N7" s="2">
+      <c r="P7" s="2">
         <v>45016</v>
       </c>
-      <c r="O7" s="2">
+      <c r="Q7" s="2">
         <v>44926</v>
       </c>
-      <c r="P7" s="2">
+      <c r="R7" s="2">
         <v>44834</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="S7" s="2">
         <v>44742</v>
       </c>
-      <c r="R7" s="2">
+      <c r="T7" s="2">
         <v>44651</v>
       </c>
-      <c r="S7" s="2">
+      <c r="U7" s="2">
         <v>44561</v>
       </c>
-      <c r="T7" s="2">
+      <c r="V7" s="2">
         <v>44469</v>
       </c>
-      <c r="U7" s="2">
+      <c r="W7" s="2">
         <v>44377</v>
       </c>
-      <c r="V7" s="2">
+      <c r="X7" s="2">
         <v>44286</v>
       </c>
-      <c r="W7" s="2">
+      <c r="Y7" s="2">
         <v>44196</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Z7" s="2">
         <v>44104</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="AA7" s="2">
         <v>44012</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AB7" s="2">
         <v>43921</v>
       </c>
     </row>
-    <row r="8" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:28" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
@@ -804,11 +811,11 @@
       <c r="N8" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="O8" s="3">
-        <v>0</v>
-      </c>
-      <c r="P8" s="3">
-        <v>0</v>
+      <c r="O8" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="P8" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="Q8" s="3">
         <v>0</v>
@@ -840,8 +847,14 @@
       <c r="Z8" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="9" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="AA8" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB8" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:28" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
@@ -914,8 +927,14 @@
       <c r="Z9" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="10" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="AA9" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AB9" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="10" spans="1:28" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
@@ -988,8 +1007,14 @@
       <c r="Z10" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="11" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="AA10" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AB10" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="11" spans="1:28" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -1016,8 +1041,10 @@
       <c r="X11" s="3"/>
       <c r="Y11" s="3"/>
       <c r="Z11" s="3"/>
-    </row>
-    <row r="12" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="AA11" s="3"/>
+      <c r="AB11" s="3"/>
+    </row>
+    <row r="12" spans="1:28" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -1054,44 +1081,50 @@
       <c r="N12" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="O12" s="3">
+      <c r="O12" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="P12" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Q12" s="3">
         <v>600</v>
       </c>
-      <c r="P12" s="3">
+      <c r="R12" s="3">
         <v>1300</v>
       </c>
-      <c r="Q12" s="3">
+      <c r="S12" s="3">
         <v>1100</v>
       </c>
-      <c r="R12" s="3">
+      <c r="T12" s="3">
         <v>400</v>
       </c>
-      <c r="S12" s="3">
+      <c r="U12" s="3">
         <v>2900</v>
       </c>
-      <c r="T12" s="3">
+      <c r="V12" s="3">
         <v>1200</v>
       </c>
-      <c r="U12" s="3">
+      <c r="W12" s="3">
         <v>400</v>
-      </c>
-      <c r="V12" s="3">
-        <v>100</v>
-      </c>
-      <c r="W12" s="3">
-        <v>300</v>
       </c>
       <c r="X12" s="3">
         <v>100</v>
       </c>
       <c r="Y12" s="3">
-        <v>0</v>
+        <v>300</v>
       </c>
       <c r="Z12" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="13" spans="1:26" x14ac:dyDescent="0.2">
+        <v>100</v>
+      </c>
+      <c r="AA12" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB12" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" spans="1:28" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1164,20 +1197,26 @@
       <c r="Z13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="AA13" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:28" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="D14" s="3">
+      <c r="D14" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="E14" s="3">
+        <v>123400</v>
+      </c>
+      <c r="F14" s="3">
         <v>-2400</v>
       </c>
-      <c r="E14" s="3">
-        <v>0</v>
-      </c>
-      <c r="F14" s="3">
-        <v>0</v>
-      </c>
       <c r="G14" s="3">
         <v>0</v>
       </c>
@@ -1185,61 +1224,67 @@
         <v>0</v>
       </c>
       <c r="I14" s="3">
+        <v>0</v>
+      </c>
+      <c r="J14" s="3">
+        <v>0</v>
+      </c>
+      <c r="K14" s="3">
         <v>-100</v>
       </c>
-      <c r="J14" s="3">
+      <c r="L14" s="3">
         <v>-100</v>
       </c>
-      <c r="K14" s="3">
+      <c r="M14" s="3">
         <v>39300</v>
       </c>
-      <c r="L14" s="3">
+      <c r="N14" s="3">
         <v>200</v>
       </c>
-      <c r="M14" s="3">
-        <v>0</v>
-      </c>
-      <c r="N14" s="3">
+      <c r="O14" s="3">
+        <v>0</v>
+      </c>
+      <c r="P14" s="3">
         <v>13800</v>
       </c>
-      <c r="O14" s="3">
+      <c r="Q14" s="3">
         <v>-1300</v>
       </c>
-      <c r="P14" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="Q14" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="R14" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="S14" s="3">
-        <v>0</v>
-      </c>
-      <c r="T14" s="3">
-        <v>0</v>
+      <c r="S14" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="T14" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="U14" s="3">
+        <v>0</v>
+      </c>
+      <c r="V14" s="3">
+        <v>0</v>
+      </c>
+      <c r="W14" s="3">
         <v>1600</v>
       </c>
-      <c r="V14" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="W14" s="3">
+      <c r="X14" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Y14" s="3">
         <v>-5700</v>
       </c>
-      <c r="X14" s="3">
-        <v>0</v>
-      </c>
-      <c r="Y14" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="Z14" s="3" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="15" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="Z14" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA14" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AB14" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="15" spans="1:28" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1259,7 +1304,7 @@
         <v>0</v>
       </c>
       <c r="I15" s="3">
-        <v>0</v>
+        <v>300</v>
       </c>
       <c r="J15" s="3">
         <v>0</v>
@@ -1312,8 +1357,14 @@
       <c r="Z15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="AA15" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:28" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1337,156 +1388,170 @@
       <c r="X16" s="3"/>
       <c r="Y16" s="3"/>
       <c r="Z16" s="3"/>
-    </row>
-    <row r="17" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA16" s="3"/>
+      <c r="AB16" s="3"/>
+    </row>
+    <row r="17" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>2700</v>
+      </c>
+      <c r="E17" s="3">
+        <v>4000</v>
+      </c>
+      <c r="F17" s="3">
         <v>2800</v>
       </c>
-      <c r="E17" s="3">
+      <c r="G17" s="3">
         <v>2500</v>
       </c>
-      <c r="F17" s="3">
+      <c r="H17" s="3">
         <v>2500</v>
-      </c>
-      <c r="G17" s="3">
-        <v>2400</v>
-      </c>
-      <c r="H17" s="3">
-        <v>2400</v>
       </c>
       <c r="I17" s="3">
         <v>2400</v>
       </c>
       <c r="J17" s="3">
+        <v>2400</v>
+      </c>
+      <c r="K17" s="3">
+        <v>2400</v>
+      </c>
+      <c r="L17" s="3">
         <v>2300</v>
       </c>
-      <c r="K17" s="3">
+      <c r="M17" s="3">
         <v>900</v>
       </c>
-      <c r="L17" s="3">
+      <c r="N17" s="3">
         <v>2900</v>
       </c>
-      <c r="M17" s="3">
+      <c r="O17" s="3">
         <v>3300</v>
       </c>
-      <c r="N17" s="3">
+      <c r="P17" s="3">
         <v>2800</v>
       </c>
-      <c r="O17" s="3">
+      <c r="Q17" s="3">
         <v>4200</v>
       </c>
-      <c r="P17" s="3">
+      <c r="R17" s="3">
         <v>4800</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="S17" s="3">
         <v>3900</v>
       </c>
-      <c r="R17" s="3">
+      <c r="T17" s="3">
         <v>2500</v>
       </c>
-      <c r="S17" s="3">
+      <c r="U17" s="3">
         <v>6600</v>
       </c>
-      <c r="T17" s="3">
+      <c r="V17" s="3">
         <v>6500</v>
       </c>
-      <c r="U17" s="3">
+      <c r="W17" s="3">
         <v>5300</v>
       </c>
-      <c r="V17" s="3">
+      <c r="X17" s="3">
         <v>2300</v>
       </c>
-      <c r="W17" s="3">
+      <c r="Y17" s="3">
         <v>-3000</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Z17" s="3">
         <v>1400</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="AA17" s="3">
         <v>1500</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AB17" s="3">
         <v>1800</v>
       </c>
     </row>
-    <row r="18" spans="3:26" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>-2700</v>
+      </c>
+      <c r="E18" s="3">
+        <v>-4000</v>
+      </c>
+      <c r="F18" s="3">
         <v>-2800</v>
       </c>
-      <c r="E18" s="3">
+      <c r="G18" s="3">
         <v>-2500</v>
       </c>
-      <c r="F18" s="3">
+      <c r="H18" s="3">
         <v>-2500</v>
-      </c>
-      <c r="G18" s="3">
-        <v>-2400</v>
-      </c>
-      <c r="H18" s="3">
-        <v>-2400</v>
       </c>
       <c r="I18" s="3">
         <v>-2400</v>
       </c>
       <c r="J18" s="3">
+        <v>-2400</v>
+      </c>
+      <c r="K18" s="3">
+        <v>-2400</v>
+      </c>
+      <c r="L18" s="3">
         <v>-2300</v>
       </c>
-      <c r="K18" s="3">
+      <c r="M18" s="3">
         <v>-900</v>
       </c>
-      <c r="L18" s="3">
+      <c r="N18" s="3">
         <v>-2900</v>
       </c>
-      <c r="M18" s="3">
+      <c r="O18" s="3">
         <v>-3300</v>
       </c>
-      <c r="N18" s="3">
+      <c r="P18" s="3">
         <v>-2800</v>
       </c>
-      <c r="O18" s="3">
+      <c r="Q18" s="3">
         <v>-4200</v>
       </c>
-      <c r="P18" s="3">
+      <c r="R18" s="3">
         <v>-4800</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="S18" s="3">
         <v>-3900</v>
       </c>
-      <c r="R18" s="3">
+      <c r="T18" s="3">
         <v>-2500</v>
       </c>
-      <c r="S18" s="3">
+      <c r="U18" s="3">
         <v>-6600</v>
       </c>
-      <c r="T18" s="3">
+      <c r="V18" s="3">
         <v>-6500</v>
       </c>
-      <c r="U18" s="3">
+      <c r="W18" s="3">
         <v>-5300</v>
       </c>
-      <c r="V18" s="3">
+      <c r="X18" s="3">
         <v>-2300</v>
       </c>
-      <c r="W18" s="3">
+      <c r="Y18" s="3">
         <v>3000</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Z18" s="3">
         <v>-1400</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="AA18" s="3">
         <v>-1500</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AB18" s="3">
         <v>-1800</v>
       </c>
     </row>
-    <row r="19" spans="3:26" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1513,200 +1578,214 @@
       <c r="X19" s="3"/>
       <c r="Y19" s="3"/>
       <c r="Z19" s="3"/>
-    </row>
-    <row r="20" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA19" s="3"/>
+      <c r="AB19" s="3"/>
+    </row>
+    <row r="20" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>-23800</v>
+      </c>
+      <c r="E20" s="3">
+        <v>-45500</v>
+      </c>
+      <c r="F20" s="3">
         <v>1200</v>
       </c>
-      <c r="E20" s="3">
+      <c r="G20" s="3">
         <v>-2900</v>
       </c>
-      <c r="F20" s="3">
+      <c r="H20" s="3">
         <v>3600</v>
       </c>
-      <c r="G20" s="3">
+      <c r="I20" s="3">
         <v>2100</v>
       </c>
-      <c r="H20" s="3">
+      <c r="J20" s="3">
         <v>-2200</v>
       </c>
-      <c r="I20" s="3">
+      <c r="K20" s="3">
         <v>900</v>
       </c>
-      <c r="J20" s="3">
+      <c r="L20" s="3">
         <v>6000</v>
       </c>
-      <c r="K20" s="3">
+      <c r="M20" s="3">
         <v>-11100</v>
       </c>
-      <c r="L20" s="3">
+      <c r="N20" s="3">
         <v>3700</v>
       </c>
-      <c r="M20" s="3">
+      <c r="O20" s="3">
         <v>-12100</v>
       </c>
-      <c r="N20" s="3">
+      <c r="P20" s="3">
         <v>-1500</v>
       </c>
-      <c r="O20" s="3">
+      <c r="Q20" s="3">
         <v>14500</v>
       </c>
-      <c r="P20" s="3">
+      <c r="R20" s="3">
         <v>-2800</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="S20" s="3">
         <v>11400</v>
       </c>
-      <c r="R20" s="3">
+      <c r="T20" s="3">
         <v>4800</v>
       </c>
-      <c r="S20" s="3">
+      <c r="U20" s="3">
         <v>-8900</v>
       </c>
-      <c r="T20" s="3">
+      <c r="V20" s="3">
         <v>-4000</v>
       </c>
-      <c r="U20" s="3">
+      <c r="W20" s="3">
         <v>-1100</v>
-      </c>
-      <c r="V20" s="3">
-        <v>-100</v>
-      </c>
-      <c r="W20" s="3">
-        <v>-100</v>
       </c>
       <c r="X20" s="3">
         <v>-100</v>
       </c>
       <c r="Y20" s="3">
+        <v>-100</v>
+      </c>
+      <c r="Z20" s="3">
+        <v>-100</v>
+      </c>
+      <c r="AA20" s="3">
         <v>-200</v>
       </c>
-      <c r="Z20" s="3">
+      <c r="AB20" s="3">
         <v>-300</v>
       </c>
     </row>
-    <row r="21" spans="3:26" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>21200</v>
+      </c>
+      <c r="E21" s="3">
+        <v>41600</v>
+      </c>
+      <c r="F21" s="3">
         <v>-4000</v>
       </c>
-      <c r="E21" s="3">
+      <c r="G21" s="3">
         <v>400</v>
       </c>
-      <c r="F21" s="3">
+      <c r="H21" s="3">
         <v>-6100</v>
       </c>
-      <c r="G21" s="3">
-        <v>-4500</v>
-      </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
+        <v>-4200</v>
+      </c>
+      <c r="J21" s="3">
         <v>-200</v>
       </c>
-      <c r="I21" s="3">
+      <c r="K21" s="3">
         <v>-3300</v>
       </c>
-      <c r="J21" s="3">
+      <c r="L21" s="3">
         <v>-8300</v>
       </c>
-      <c r="K21" s="3">
+      <c r="M21" s="3">
         <v>10100</v>
       </c>
-      <c r="L21" s="3">
+      <c r="N21" s="3">
         <v>-6700</v>
       </c>
-      <c r="M21" s="3">
+      <c r="O21" s="3">
         <v>8800</v>
       </c>
-      <c r="N21" s="3">
+      <c r="P21" s="3">
         <v>-1300</v>
       </c>
-      <c r="O21" s="3">
+      <c r="Q21" s="3">
         <v>10400</v>
       </c>
-      <c r="P21" s="3">
+      <c r="R21" s="3">
         <v>-7600</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="S21" s="3">
         <v>7500</v>
       </c>
-      <c r="R21" s="3">
+      <c r="T21" s="3">
         <v>2300</v>
       </c>
-      <c r="S21" s="3">
+      <c r="U21" s="3">
         <v>-15500</v>
       </c>
-      <c r="T21" s="3">
+      <c r="V21" s="3">
         <v>-10500</v>
       </c>
-      <c r="U21" s="3">
+      <c r="W21" s="3">
         <v>-6400</v>
       </c>
-      <c r="V21" s="3">
+      <c r="X21" s="3">
         <v>-2400</v>
       </c>
-      <c r="W21" s="3">
+      <c r="Y21" s="3">
         <v>2900</v>
       </c>
-      <c r="X21" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="Y21" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="Z21" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="22" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA21" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AB21" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="22" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>1000</v>
+      </c>
+      <c r="E22" s="3">
+        <v>1400</v>
+      </c>
+      <c r="F22" s="3">
         <v>1700</v>
       </c>
-      <c r="E22" s="3">
+      <c r="G22" s="3">
         <v>1900</v>
       </c>
-      <c r="F22" s="3">
+      <c r="H22" s="3">
         <v>2700</v>
       </c>
-      <c r="G22" s="3">
+      <c r="I22" s="3">
         <v>1500</v>
       </c>
-      <c r="H22" s="3">
+      <c r="J22" s="3">
         <v>2000</v>
       </c>
-      <c r="I22" s="3">
+      <c r="K22" s="3">
         <v>1000</v>
       </c>
-      <c r="J22" s="3">
+      <c r="L22" s="3">
         <v>700</v>
       </c>
-      <c r="K22" s="3">
+      <c r="M22" s="3">
         <v>6200</v>
       </c>
-      <c r="L22" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="M22" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="N22" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="O22" s="3">
-        <v>0</v>
+      <c r="O22" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="P22" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="Q22" s="3" t="s">
-        <v>4</v>
+      <c r="Q22" s="3">
+        <v>0</v>
       </c>
       <c r="R22" s="3" t="s">
         <v>4</v>
@@ -1714,103 +1793,115 @@
       <c r="S22" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="T22" s="3">
-        <v>0</v>
-      </c>
-      <c r="U22" s="3">
-        <v>0</v>
+      <c r="T22" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="U22" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="V22" s="3">
+        <v>0</v>
+      </c>
+      <c r="W22" s="3">
+        <v>0</v>
+      </c>
+      <c r="X22" s="3">
         <v>100</v>
       </c>
-      <c r="W22" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="X22" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="Y22" s="3" t="s">
         <v>4</v>
       </c>
       <c r="Z22" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="23" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA22" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AB22" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="23" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>20200</v>
+      </c>
+      <c r="E23" s="3">
+        <v>-83200</v>
+      </c>
+      <c r="F23" s="3">
         <v>-3400</v>
       </c>
-      <c r="E23" s="3">
+      <c r="G23" s="3">
         <v>-1500</v>
       </c>
-      <c r="F23" s="3">
+      <c r="H23" s="3">
         <v>-8800</v>
       </c>
-      <c r="G23" s="3">
+      <c r="I23" s="3">
         <v>-6000</v>
       </c>
-      <c r="H23" s="3">
+      <c r="J23" s="3">
         <v>-2200</v>
       </c>
-      <c r="I23" s="3">
+      <c r="K23" s="3">
         <v>-4200</v>
       </c>
-      <c r="J23" s="3">
+      <c r="L23" s="3">
         <v>-9000</v>
       </c>
-      <c r="K23" s="3">
+      <c r="M23" s="3">
         <v>-35500</v>
       </c>
-      <c r="L23" s="3">
+      <c r="N23" s="3">
         <v>-6800</v>
       </c>
-      <c r="M23" s="3">
+      <c r="O23" s="3">
         <v>8900</v>
       </c>
-      <c r="N23" s="3">
+      <c r="P23" s="3">
         <v>-15000</v>
       </c>
-      <c r="O23" s="3">
+      <c r="Q23" s="3">
         <v>10300</v>
       </c>
-      <c r="P23" s="3">
+      <c r="R23" s="3">
         <v>-7600</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="S23" s="3">
         <v>7500</v>
       </c>
-      <c r="R23" s="3">
+      <c r="T23" s="3">
         <v>2300</v>
       </c>
-      <c r="S23" s="3">
+      <c r="U23" s="3">
         <v>-15500</v>
       </c>
-      <c r="T23" s="3">
+      <c r="V23" s="3">
         <v>-10500</v>
       </c>
-      <c r="U23" s="3">
+      <c r="W23" s="3">
         <v>-6400</v>
       </c>
-      <c r="V23" s="3">
+      <c r="X23" s="3">
         <v>-2500</v>
       </c>
-      <c r="W23" s="3">
+      <c r="Y23" s="3">
         <v>2900</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Z23" s="3">
         <v>-1500</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="AA23" s="3">
         <v>-1700</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AB23" s="3">
         <v>-2100</v>
       </c>
     </row>
-    <row r="24" spans="3:26" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
@@ -1847,11 +1938,11 @@
       <c r="N24" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="O24" s="3">
-        <v>0</v>
-      </c>
-      <c r="P24" s="3">
-        <v>0</v>
+      <c r="O24" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="P24" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="Q24" s="3">
         <v>0</v>
@@ -1883,8 +1974,14 @@
       <c r="Z24" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="25" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA24" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB24" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1957,156 +2054,174 @@
       <c r="Z25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA25" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>20200</v>
+      </c>
+      <c r="E26" s="3">
+        <v>-83200</v>
+      </c>
+      <c r="F26" s="3">
         <v>-3400</v>
       </c>
-      <c r="E26" s="3">
+      <c r="G26" s="3">
         <v>-1500</v>
       </c>
-      <c r="F26" s="3">
+      <c r="H26" s="3">
         <v>-8800</v>
       </c>
-      <c r="G26" s="3">
+      <c r="I26" s="3">
         <v>-6000</v>
       </c>
-      <c r="H26" s="3">
+      <c r="J26" s="3">
         <v>-2200</v>
       </c>
-      <c r="I26" s="3">
+      <c r="K26" s="3">
         <v>-4200</v>
       </c>
-      <c r="J26" s="3">
+      <c r="L26" s="3">
         <v>-9000</v>
       </c>
-      <c r="K26" s="3">
+      <c r="M26" s="3">
         <v>-35500</v>
       </c>
-      <c r="L26" s="3">
+      <c r="N26" s="3">
         <v>-6800</v>
       </c>
-      <c r="M26" s="3">
+      <c r="O26" s="3">
         <v>8900</v>
       </c>
-      <c r="N26" s="3">
+      <c r="P26" s="3">
         <v>-15000</v>
       </c>
-      <c r="O26" s="3">
+      <c r="Q26" s="3">
         <v>10300</v>
       </c>
-      <c r="P26" s="3">
+      <c r="R26" s="3">
         <v>-7600</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="S26" s="3">
         <v>7500</v>
       </c>
-      <c r="R26" s="3">
+      <c r="T26" s="3">
         <v>2300</v>
       </c>
-      <c r="S26" s="3">
+      <c r="U26" s="3">
         <v>-15500</v>
       </c>
-      <c r="T26" s="3">
+      <c r="V26" s="3">
         <v>-10500</v>
       </c>
-      <c r="U26" s="3">
+      <c r="W26" s="3">
         <v>-6400</v>
       </c>
-      <c r="V26" s="3">
+      <c r="X26" s="3">
         <v>-2500</v>
       </c>
-      <c r="W26" s="3">
+      <c r="Y26" s="3">
         <v>2900</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Z26" s="3">
         <v>-1500</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="AA26" s="3">
         <v>-1700</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AB26" s="3">
         <v>-2100</v>
       </c>
     </row>
-    <row r="27" spans="3:26" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>20200</v>
+      </c>
+      <c r="E27" s="3">
+        <v>-83200</v>
+      </c>
+      <c r="F27" s="3">
         <v>-3400</v>
       </c>
-      <c r="E27" s="3">
+      <c r="G27" s="3">
         <v>-1500</v>
       </c>
-      <c r="F27" s="3">
+      <c r="H27" s="3">
         <v>-8800</v>
       </c>
-      <c r="G27" s="3">
+      <c r="I27" s="3">
         <v>-6000</v>
       </c>
-      <c r="H27" s="3">
+      <c r="J27" s="3">
         <v>-2200</v>
       </c>
-      <c r="I27" s="3">
+      <c r="K27" s="3">
         <v>-4200</v>
       </c>
-      <c r="J27" s="3">
+      <c r="L27" s="3">
         <v>-9000</v>
       </c>
-      <c r="K27" s="3">
+      <c r="M27" s="3">
         <v>-35500</v>
       </c>
-      <c r="L27" s="3">
+      <c r="N27" s="3">
         <v>-6800</v>
       </c>
-      <c r="M27" s="3">
+      <c r="O27" s="3">
         <v>8900</v>
       </c>
-      <c r="N27" s="3">
+      <c r="P27" s="3">
         <v>-15000</v>
       </c>
-      <c r="O27" s="3">
+      <c r="Q27" s="3">
         <v>10300</v>
       </c>
-      <c r="P27" s="3">
+      <c r="R27" s="3">
         <v>-7600</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="S27" s="3">
         <v>7500</v>
       </c>
-      <c r="R27" s="3">
+      <c r="T27" s="3">
         <v>2300</v>
       </c>
-      <c r="S27" s="3">
+      <c r="U27" s="3">
         <v>-15500</v>
       </c>
-      <c r="T27" s="3">
+      <c r="V27" s="3">
         <v>-10500</v>
       </c>
-      <c r="U27" s="3">
+      <c r="W27" s="3">
         <v>-6400</v>
       </c>
-      <c r="V27" s="3">
+      <c r="X27" s="3">
         <v>-2500</v>
       </c>
-      <c r="W27" s="3">
+      <c r="Y27" s="3">
         <v>2900</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Z27" s="3">
         <v>-1500</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="AA27" s="3">
         <v>-1700</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AB27" s="3">
         <v>-2100</v>
       </c>
     </row>
-    <row r="28" spans="3:26" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2179,8 +2294,14 @@
       <c r="Z28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA28" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2253,8 +2374,14 @@
       <c r="Z29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA29" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2327,8 +2454,14 @@
       <c r="Z30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA30" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2401,156 +2534,174 @@
       <c r="Z31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA31" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>23800</v>
+      </c>
+      <c r="E32" s="3">
+        <v>45500</v>
+      </c>
+      <c r="F32" s="3">
         <v>-1200</v>
       </c>
-      <c r="E32" s="3">
+      <c r="G32" s="3">
         <v>2900</v>
       </c>
-      <c r="F32" s="3">
+      <c r="H32" s="3">
         <v>-3600</v>
       </c>
-      <c r="G32" s="3">
+      <c r="I32" s="3">
         <v>-2100</v>
       </c>
-      <c r="H32" s="3">
+      <c r="J32" s="3">
         <v>2200</v>
       </c>
-      <c r="I32" s="3">
+      <c r="K32" s="3">
         <v>-900</v>
       </c>
-      <c r="J32" s="3">
+      <c r="L32" s="3">
         <v>-6000</v>
       </c>
-      <c r="K32" s="3">
+      <c r="M32" s="3">
         <v>11100</v>
       </c>
-      <c r="L32" s="3">
+      <c r="N32" s="3">
         <v>-3700</v>
       </c>
-      <c r="M32" s="3">
+      <c r="O32" s="3">
         <v>12100</v>
       </c>
-      <c r="N32" s="3">
+      <c r="P32" s="3">
         <v>1500</v>
       </c>
-      <c r="O32" s="3">
+      <c r="Q32" s="3">
         <v>-14500</v>
       </c>
-      <c r="P32" s="3">
+      <c r="R32" s="3">
         <v>2800</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="S32" s="3">
         <v>-11400</v>
       </c>
-      <c r="R32" s="3">
+      <c r="T32" s="3">
         <v>-4800</v>
       </c>
-      <c r="S32" s="3">
+      <c r="U32" s="3">
         <v>8900</v>
       </c>
-      <c r="T32" s="3">
+      <c r="V32" s="3">
         <v>4000</v>
       </c>
-      <c r="U32" s="3">
+      <c r="W32" s="3">
         <v>1100</v>
-      </c>
-      <c r="V32" s="3">
-        <v>100</v>
-      </c>
-      <c r="W32" s="3">
-        <v>100</v>
       </c>
       <c r="X32" s="3">
         <v>100</v>
       </c>
       <c r="Y32" s="3">
+        <v>100</v>
+      </c>
+      <c r="Z32" s="3">
+        <v>100</v>
+      </c>
+      <c r="AA32" s="3">
         <v>200</v>
       </c>
-      <c r="Z32" s="3">
+      <c r="AB32" s="3">
         <v>300</v>
       </c>
     </row>
-    <row r="33" spans="2:26" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>20200</v>
+      </c>
+      <c r="E33" s="3">
+        <v>-83200</v>
+      </c>
+      <c r="F33" s="3">
         <v>-3400</v>
       </c>
-      <c r="E33" s="3">
+      <c r="G33" s="3">
         <v>-1500</v>
       </c>
-      <c r="F33" s="3">
+      <c r="H33" s="3">
         <v>-8800</v>
       </c>
-      <c r="G33" s="3">
+      <c r="I33" s="3">
         <v>-6000</v>
       </c>
-      <c r="H33" s="3">
+      <c r="J33" s="3">
         <v>-2200</v>
       </c>
-      <c r="I33" s="3">
+      <c r="K33" s="3">
         <v>-4200</v>
       </c>
-      <c r="J33" s="3">
+      <c r="L33" s="3">
         <v>-9000</v>
       </c>
-      <c r="K33" s="3">
+      <c r="M33" s="3">
         <v>-35500</v>
       </c>
-      <c r="L33" s="3">
+      <c r="N33" s="3">
         <v>-6800</v>
       </c>
-      <c r="M33" s="3">
+      <c r="O33" s="3">
         <v>8900</v>
       </c>
-      <c r="N33" s="3">
+      <c r="P33" s="3">
         <v>-15000</v>
       </c>
-      <c r="O33" s="3">
+      <c r="Q33" s="3">
         <v>10300</v>
       </c>
-      <c r="P33" s="3">
+      <c r="R33" s="3">
         <v>-7600</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="S33" s="3">
         <v>7500</v>
       </c>
-      <c r="R33" s="3">
+      <c r="T33" s="3">
         <v>2300</v>
       </c>
-      <c r="S33" s="3">
+      <c r="U33" s="3">
         <v>-15500</v>
       </c>
-      <c r="T33" s="3">
+      <c r="V33" s="3">
         <v>-10500</v>
       </c>
-      <c r="U33" s="3">
+      <c r="W33" s="3">
         <v>-6400</v>
       </c>
-      <c r="V33" s="3">
+      <c r="X33" s="3">
         <v>-2500</v>
       </c>
-      <c r="W33" s="3">
+      <c r="Y33" s="3">
         <v>2900</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Z33" s="3">
         <v>-1500</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="AA33" s="3">
         <v>-1700</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AB33" s="3">
         <v>-2100</v>
       </c>
     </row>
-    <row r="34" spans="2:26" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2623,161 +2774,179 @@
       <c r="Z34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA34" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>20200</v>
+      </c>
+      <c r="E35" s="3">
+        <v>-83200</v>
+      </c>
+      <c r="F35" s="3">
         <v>-3400</v>
       </c>
-      <c r="E35" s="3">
+      <c r="G35" s="3">
         <v>-1500</v>
       </c>
-      <c r="F35" s="3">
+      <c r="H35" s="3">
         <v>-8800</v>
       </c>
-      <c r="G35" s="3">
+      <c r="I35" s="3">
         <v>-6000</v>
       </c>
-      <c r="H35" s="3">
+      <c r="J35" s="3">
         <v>-2200</v>
       </c>
-      <c r="I35" s="3">
+      <c r="K35" s="3">
         <v>-4200</v>
       </c>
-      <c r="J35" s="3">
+      <c r="L35" s="3">
         <v>-9000</v>
       </c>
-      <c r="K35" s="3">
+      <c r="M35" s="3">
         <v>-35500</v>
       </c>
-      <c r="L35" s="3">
+      <c r="N35" s="3">
         <v>-6800</v>
       </c>
-      <c r="M35" s="3">
+      <c r="O35" s="3">
         <v>8900</v>
       </c>
-      <c r="N35" s="3">
+      <c r="P35" s="3">
         <v>-15000</v>
       </c>
-      <c r="O35" s="3">
+      <c r="Q35" s="3">
         <v>10300</v>
       </c>
-      <c r="P35" s="3">
+      <c r="R35" s="3">
         <v>-7600</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="S35" s="3">
         <v>7500</v>
       </c>
-      <c r="R35" s="3">
+      <c r="T35" s="3">
         <v>2300</v>
       </c>
-      <c r="S35" s="3">
+      <c r="U35" s="3">
         <v>-15500</v>
       </c>
-      <c r="T35" s="3">
+      <c r="V35" s="3">
         <v>-10500</v>
       </c>
-      <c r="U35" s="3">
+      <c r="W35" s="3">
         <v>-6400</v>
       </c>
-      <c r="V35" s="3">
+      <c r="X35" s="3">
         <v>-2500</v>
       </c>
-      <c r="W35" s="3">
+      <c r="Y35" s="3">
         <v>2900</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Z35" s="3">
         <v>-1500</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="AA35" s="3">
         <v>-1700</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AB35" s="3">
         <v>-2100</v>
       </c>
     </row>
-    <row r="37" spans="2:26" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:28" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:26" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>46112</v>
+      </c>
+      <c r="E38" s="2">
+        <v>46022</v>
+      </c>
+      <c r="F38" s="2">
         <v>45930</v>
       </c>
-      <c r="E38" s="2">
+      <c r="G38" s="2">
         <v>45838</v>
       </c>
-      <c r="F38" s="2">
+      <c r="H38" s="2">
         <v>45747</v>
       </c>
-      <c r="G38" s="2">
+      <c r="I38" s="2">
         <v>45657</v>
       </c>
-      <c r="H38" s="2">
+      <c r="J38" s="2">
         <v>45565</v>
       </c>
-      <c r="I38" s="2">
+      <c r="K38" s="2">
         <v>45473</v>
       </c>
-      <c r="J38" s="2">
+      <c r="L38" s="2">
         <v>45382</v>
       </c>
-      <c r="K38" s="2">
+      <c r="M38" s="2">
         <v>45291</v>
       </c>
-      <c r="L38" s="2">
+      <c r="N38" s="2">
         <v>45199</v>
       </c>
-      <c r="M38" s="2">
+      <c r="O38" s="2">
         <v>45107</v>
       </c>
-      <c r="N38" s="2">
+      <c r="P38" s="2">
         <v>45016</v>
       </c>
-      <c r="O38" s="2">
+      <c r="Q38" s="2">
         <v>44926</v>
       </c>
-      <c r="P38" s="2">
+      <c r="R38" s="2">
         <v>44834</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="S38" s="2">
         <v>44742</v>
       </c>
-      <c r="R38" s="2">
+      <c r="T38" s="2">
         <v>44651</v>
       </c>
-      <c r="S38" s="2">
+      <c r="U38" s="2">
         <v>44561</v>
       </c>
-      <c r="T38" s="2">
+      <c r="V38" s="2">
         <v>44469</v>
       </c>
-      <c r="U38" s="2">
+      <c r="W38" s="2">
         <v>44377</v>
       </c>
-      <c r="V38" s="2">
+      <c r="X38" s="2">
         <v>44286</v>
       </c>
-      <c r="W38" s="2">
+      <c r="Y38" s="2">
         <v>44196</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Z38" s="2">
         <v>44104</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="AA38" s="2">
         <v>44012</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AB38" s="2">
         <v>43921</v>
       </c>
     </row>
-    <row r="39" spans="2:26" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2804,8 +2973,10 @@
       <c r="X39" s="3"/>
       <c r="Y39" s="3"/>
       <c r="Z39" s="3"/>
-    </row>
-    <row r="40" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA39" s="3"/>
+      <c r="AB39" s="3"/>
+    </row>
+    <row r="40" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2832,82 +3003,90 @@
       <c r="X40" s="3"/>
       <c r="Y40" s="3"/>
       <c r="Z40" s="3"/>
-    </row>
-    <row r="41" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA40" s="3"/>
+      <c r="AB40" s="3"/>
+    </row>
+    <row r="41" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
-        <v>2200</v>
+        <v>28800</v>
       </c>
       <c r="E41" s="3">
-        <v>2100</v>
+        <v>28500</v>
       </c>
       <c r="F41" s="3">
         <v>2200</v>
       </c>
       <c r="G41" s="3">
+        <v>2100</v>
+      </c>
+      <c r="H41" s="3">
+        <v>2200</v>
+      </c>
+      <c r="I41" s="3">
         <v>2600</v>
       </c>
-      <c r="H41" s="3">
+      <c r="J41" s="3">
         <v>2400</v>
       </c>
-      <c r="I41" s="3">
+      <c r="K41" s="3">
         <v>3500</v>
       </c>
-      <c r="J41" s="3">
+      <c r="L41" s="3">
         <v>4200</v>
       </c>
-      <c r="K41" s="3">
+      <c r="M41" s="3">
         <v>5700</v>
       </c>
-      <c r="L41" s="3">
+      <c r="N41" s="3">
         <v>11100</v>
       </c>
-      <c r="M41" s="3">
+      <c r="O41" s="3">
         <v>4700</v>
       </c>
-      <c r="N41" s="3">
+      <c r="P41" s="3">
         <v>8300</v>
       </c>
-      <c r="O41" s="3">
+      <c r="Q41" s="3">
         <v>8000</v>
       </c>
-      <c r="P41" s="3">
+      <c r="R41" s="3">
         <v>18900</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="S41" s="3">
         <v>40700</v>
       </c>
-      <c r="R41" s="3">
+      <c r="T41" s="3">
         <v>51900</v>
       </c>
-      <c r="S41" s="3">
+      <c r="U41" s="3">
         <v>58600</v>
       </c>
-      <c r="T41" s="3">
+      <c r="V41" s="3">
         <v>61200</v>
       </c>
-      <c r="U41" s="3">
+      <c r="W41" s="3">
         <v>11500</v>
       </c>
-      <c r="V41" s="3">
+      <c r="X41" s="3">
         <v>16000</v>
       </c>
-      <c r="W41" s="3">
+      <c r="Y41" s="3">
         <v>4200</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Z41" s="3">
         <v>4700</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="AA41" s="3">
         <v>3600</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AB41" s="3">
         <v>4600</v>
       </c>
     </row>
-    <row r="42" spans="2:26" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -2924,138 +3103,150 @@
         <v>0</v>
       </c>
       <c r="H42" s="3">
+        <v>0</v>
+      </c>
+      <c r="I42" s="3">
+        <v>0</v>
+      </c>
+      <c r="J42" s="3">
         <v>100</v>
       </c>
-      <c r="I42" s="3">
+      <c r="K42" s="3">
         <v>200</v>
       </c>
-      <c r="J42" s="3">
+      <c r="L42" s="3">
         <v>600</v>
       </c>
-      <c r="K42" s="3">
+      <c r="M42" s="3">
         <v>500</v>
       </c>
-      <c r="L42" s="3">
+      <c r="N42" s="3">
         <v>500</v>
       </c>
-      <c r="M42" s="3">
+      <c r="O42" s="3">
         <v>900</v>
       </c>
-      <c r="N42" s="3">
+      <c r="P42" s="3">
         <v>1200</v>
       </c>
-      <c r="O42" s="3">
+      <c r="Q42" s="3">
         <v>400</v>
       </c>
-      <c r="P42" s="3">
+      <c r="R42" s="3">
         <v>700</v>
       </c>
-      <c r="Q42" s="3">
+      <c r="S42" s="3">
         <v>1100</v>
       </c>
-      <c r="R42" s="3">
+      <c r="T42" s="3">
         <v>2100</v>
       </c>
-      <c r="S42" s="3">
+      <c r="U42" s="3">
         <v>1800</v>
       </c>
-      <c r="T42" s="3">
+      <c r="V42" s="3">
         <v>2300</v>
       </c>
-      <c r="U42" s="3">
+      <c r="W42" s="3">
         <v>2300</v>
       </c>
-      <c r="V42" s="3">
+      <c r="X42" s="3">
         <v>3500</v>
       </c>
-      <c r="W42" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="X42" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="Y42" s="3" t="s">
         <v>4</v>
       </c>
       <c r="Z42" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="43" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA42" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AB42" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="43" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>600</v>
+      </c>
+      <c r="E43" s="3">
+        <v>500</v>
+      </c>
+      <c r="F43" s="3">
         <v>300</v>
       </c>
-      <c r="E43" s="3">
+      <c r="G43" s="3">
         <v>300</v>
       </c>
-      <c r="F43" s="3">
+      <c r="H43" s="3">
         <v>600</v>
       </c>
-      <c r="G43" s="3">
+      <c r="I43" s="3">
         <v>900</v>
       </c>
-      <c r="H43" s="3">
+      <c r="J43" s="3">
         <v>200</v>
       </c>
-      <c r="I43" s="3">
+      <c r="K43" s="3">
         <v>300</v>
       </c>
-      <c r="J43" s="3">
+      <c r="L43" s="3">
         <v>400</v>
       </c>
-      <c r="K43" s="3">
+      <c r="M43" s="3">
         <v>800</v>
       </c>
-      <c r="L43" s="3">
+      <c r="N43" s="3">
         <v>700</v>
       </c>
-      <c r="M43" s="3">
+      <c r="O43" s="3">
         <v>600</v>
       </c>
-      <c r="N43" s="3">
+      <c r="P43" s="3">
         <v>900</v>
       </c>
-      <c r="O43" s="3">
+      <c r="Q43" s="3">
         <v>3100</v>
       </c>
-      <c r="P43" s="3">
+      <c r="R43" s="3">
         <v>3500</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="S43" s="3">
         <v>1700</v>
       </c>
-      <c r="R43" s="3">
+      <c r="T43" s="3">
         <v>1300</v>
       </c>
-      <c r="S43" s="3">
+      <c r="U43" s="3">
         <v>1000</v>
       </c>
-      <c r="T43" s="3">
+      <c r="V43" s="3">
         <v>1100</v>
       </c>
-      <c r="U43" s="3">
+      <c r="W43" s="3">
         <v>600</v>
       </c>
-      <c r="V43" s="3">
+      <c r="X43" s="3">
         <v>400</v>
       </c>
-      <c r="W43" s="3">
+      <c r="Y43" s="3">
         <v>200</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Z43" s="3">
         <v>200</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="AA43" s="3">
         <v>100</v>
       </c>
-      <c r="Z43" s="3">
+      <c r="AB43" s="3">
         <v>400</v>
       </c>
     </row>
-    <row r="44" spans="2:26" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -3092,11 +3283,11 @@
       <c r="N44" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="O44" s="3">
-        <v>0</v>
-      </c>
-      <c r="P44" s="3">
-        <v>0</v>
+      <c r="O44" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="P44" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="Q44" s="3">
         <v>0</v>
@@ -3128,8 +3319,14 @@
       <c r="Z44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA44" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
@@ -3166,118 +3363,130 @@
       <c r="N45" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="O45" s="3">
-        <v>2100</v>
-      </c>
-      <c r="P45" s="3">
-        <v>2500</v>
+      <c r="O45" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="P45" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="Q45" s="3">
         <v>2100</v>
       </c>
       <c r="R45" s="3">
+        <v>2500</v>
+      </c>
+      <c r="S45" s="3">
+        <v>2100</v>
+      </c>
+      <c r="T45" s="3">
         <v>1300</v>
       </c>
-      <c r="S45" s="3">
+      <c r="U45" s="3">
         <v>600</v>
       </c>
-      <c r="T45" s="3">
+      <c r="V45" s="3">
         <v>400</v>
       </c>
-      <c r="U45" s="3">
+      <c r="W45" s="3">
         <v>1000</v>
       </c>
-      <c r="V45" s="3">
+      <c r="X45" s="3">
         <v>900</v>
       </c>
-      <c r="W45" s="3">
+      <c r="Y45" s="3">
         <v>6100</v>
-      </c>
-      <c r="X45" s="3">
-        <v>600</v>
-      </c>
-      <c r="Y45" s="3">
-        <v>400</v>
       </c>
       <c r="Z45" s="3">
         <v>600</v>
       </c>
-    </row>
-    <row r="46" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA45" s="3">
+        <v>400</v>
+      </c>
+      <c r="AB45" s="3">
+        <v>600</v>
+      </c>
+    </row>
+    <row r="46" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>30700</v>
+      </c>
+      <c r="E46" s="3">
+        <v>29500</v>
+      </c>
+      <c r="F46" s="3">
         <v>3400</v>
       </c>
-      <c r="E46" s="3">
+      <c r="G46" s="3">
         <v>3100</v>
       </c>
-      <c r="F46" s="3">
+      <c r="H46" s="3">
         <v>3700</v>
       </c>
-      <c r="G46" s="3">
+      <c r="I46" s="3">
         <v>4000</v>
       </c>
-      <c r="H46" s="3">
+      <c r="J46" s="3">
         <v>3400</v>
       </c>
-      <c r="I46" s="3">
+      <c r="K46" s="3">
         <v>5100</v>
       </c>
-      <c r="J46" s="3">
+      <c r="L46" s="3">
         <v>6500</v>
       </c>
-      <c r="K46" s="3">
+      <c r="M46" s="3">
         <v>8000</v>
       </c>
-      <c r="L46" s="3">
+      <c r="N46" s="3">
         <v>12900</v>
       </c>
-      <c r="M46" s="3">
+      <c r="O46" s="3">
         <v>6500</v>
       </c>
-      <c r="N46" s="3">
+      <c r="P46" s="3">
         <v>10700</v>
       </c>
-      <c r="O46" s="3">
+      <c r="Q46" s="3">
         <v>13500</v>
       </c>
-      <c r="P46" s="3">
+      <c r="R46" s="3">
         <v>25700</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="S46" s="3">
         <v>45600</v>
       </c>
-      <c r="R46" s="3">
+      <c r="T46" s="3">
         <v>56600</v>
       </c>
-      <c r="S46" s="3">
+      <c r="U46" s="3">
         <v>61900</v>
       </c>
-      <c r="T46" s="3">
+      <c r="V46" s="3">
         <v>64900</v>
       </c>
-      <c r="U46" s="3">
+      <c r="W46" s="3">
         <v>15300</v>
       </c>
-      <c r="V46" s="3">
+      <c r="X46" s="3">
         <v>20700</v>
       </c>
-      <c r="W46" s="3">
+      <c r="Y46" s="3">
         <v>10500</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Z46" s="3">
         <v>5500</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="AA46" s="3">
         <v>4100</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AB46" s="3">
         <v>5600</v>
       </c>
     </row>
-    <row r="47" spans="2:26" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -3314,11 +3523,11 @@
       <c r="N47" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="O47" s="3">
-        <v>0</v>
-      </c>
-      <c r="P47" s="3">
-        <v>0</v>
+      <c r="O47" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="P47" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="Q47" s="3">
         <v>0</v>
@@ -3350,70 +3559,76 @@
       <c r="Z47" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA47" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>106600</v>
+      </c>
+      <c r="E48" s="3">
+        <v>104900</v>
+      </c>
+      <c r="F48" s="3">
         <v>102000</v>
       </c>
-      <c r="E48" s="3">
+      <c r="G48" s="3">
         <v>102600</v>
       </c>
-      <c r="F48" s="3">
+      <c r="H48" s="3">
         <v>100700</v>
       </c>
-      <c r="G48" s="3">
+      <c r="I48" s="3">
         <v>100400</v>
       </c>
-      <c r="H48" s="3">
+      <c r="J48" s="3">
         <v>102800</v>
       </c>
-      <c r="I48" s="3">
+      <c r="K48" s="3">
         <v>102300</v>
       </c>
-      <c r="J48" s="3">
+      <c r="L48" s="3">
         <v>102900</v>
       </c>
-      <c r="K48" s="3">
+      <c r="M48" s="3">
         <v>103700</v>
       </c>
-      <c r="L48" s="3">
+      <c r="N48" s="3">
         <v>142600</v>
       </c>
-      <c r="M48" s="3">
+      <c r="O48" s="3">
         <v>142100</v>
       </c>
-      <c r="N48" s="3">
+      <c r="P48" s="3">
         <v>133700</v>
       </c>
-      <c r="O48" s="3">
+      <c r="Q48" s="3">
         <v>173100</v>
       </c>
-      <c r="P48" s="3">
+      <c r="R48" s="3">
         <v>144300</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="S48" s="3">
         <v>129800</v>
       </c>
-      <c r="R48" s="3">
+      <c r="T48" s="3">
         <v>113700</v>
       </c>
-      <c r="S48" s="3">
+      <c r="U48" s="3">
         <v>104700</v>
       </c>
-      <c r="T48" s="3">
+      <c r="V48" s="3">
         <v>95000</v>
       </c>
-      <c r="U48" s="3">
+      <c r="W48" s="3">
         <v>93900</v>
-      </c>
-      <c r="V48" s="3">
-        <v>92300</v>
-      </c>
-      <c r="W48" s="3">
-        <v>92300</v>
       </c>
       <c r="X48" s="3">
         <v>92300</v>
@@ -3424,8 +3639,14 @@
       <c r="Z48" s="3">
         <v>92300</v>
       </c>
-    </row>
-    <row r="49" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA48" s="3">
+        <v>92300</v>
+      </c>
+      <c r="AB48" s="3">
+        <v>92300</v>
+      </c>
+    </row>
+    <row r="49" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
@@ -3498,8 +3719,14 @@
       <c r="Z49" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="50" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA49" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB49" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -3572,8 +3799,14 @@
       <c r="Z50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA50" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -3646,22 +3879,28 @@
       <c r="Z51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA51" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>900</v>
+      </c>
+      <c r="E52" s="3">
+        <v>900</v>
+      </c>
+      <c r="F52" s="3">
         <v>1000</v>
       </c>
-      <c r="E52" s="3">
+      <c r="G52" s="3">
         <v>1000</v>
-      </c>
-      <c r="F52" s="3">
-        <v>900</v>
-      </c>
-      <c r="G52" s="3">
-        <v>900</v>
       </c>
       <c r="H52" s="3">
         <v>900</v>
@@ -3675,20 +3914,20 @@
       <c r="K52" s="3">
         <v>900</v>
       </c>
-      <c r="L52" s="3" t="s">
-        <v>4</v>
+      <c r="L52" s="3">
+        <v>900</v>
       </c>
       <c r="M52" s="3">
+        <v>900</v>
+      </c>
+      <c r="N52" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="O52" s="3">
         <v>1700</v>
       </c>
-      <c r="N52" s="3">
+      <c r="P52" s="3">
         <v>2500</v>
-      </c>
-      <c r="O52" s="3">
-        <v>900</v>
-      </c>
-      <c r="P52" s="3">
-        <v>900</v>
       </c>
       <c r="Q52" s="3">
         <v>900</v>
@@ -3720,8 +3959,14 @@
       <c r="Z52" s="3">
         <v>900</v>
       </c>
-    </row>
-    <row r="53" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA52" s="3">
+        <v>900</v>
+      </c>
+      <c r="AB52" s="3">
+        <v>900</v>
+      </c>
+    </row>
+    <row r="53" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -3794,82 +4039,94 @@
       <c r="Z53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA53" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>138100</v>
+      </c>
+      <c r="E54" s="3">
+        <v>135300</v>
+      </c>
+      <c r="F54" s="3">
         <v>106300</v>
       </c>
-      <c r="E54" s="3">
+      <c r="G54" s="3">
         <v>106800</v>
       </c>
-      <c r="F54" s="3">
+      <c r="H54" s="3">
         <v>105400</v>
       </c>
-      <c r="G54" s="3">
+      <c r="I54" s="3">
         <v>105300</v>
       </c>
-      <c r="H54" s="3">
+      <c r="J54" s="3">
         <v>107100</v>
       </c>
-      <c r="I54" s="3">
+      <c r="K54" s="3">
         <v>108300</v>
       </c>
-      <c r="J54" s="3">
+      <c r="L54" s="3">
         <v>110300</v>
       </c>
-      <c r="K54" s="3">
+      <c r="M54" s="3">
         <v>112600</v>
       </c>
-      <c r="L54" s="3">
+      <c r="N54" s="3">
         <v>155500</v>
       </c>
-      <c r="M54" s="3">
+      <c r="O54" s="3">
         <v>150300</v>
       </c>
-      <c r="N54" s="3">
+      <c r="P54" s="3">
         <v>146900</v>
       </c>
-      <c r="O54" s="3">
+      <c r="Q54" s="3">
         <v>187500</v>
       </c>
-      <c r="P54" s="3">
+      <c r="R54" s="3">
         <v>170900</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="S54" s="3">
         <v>176400</v>
       </c>
-      <c r="R54" s="3">
+      <c r="T54" s="3">
         <v>171300</v>
       </c>
-      <c r="S54" s="3">
+      <c r="U54" s="3">
         <v>167600</v>
       </c>
-      <c r="T54" s="3">
+      <c r="V54" s="3">
         <v>160800</v>
       </c>
-      <c r="U54" s="3">
+      <c r="W54" s="3">
         <v>110100</v>
       </c>
-      <c r="V54" s="3">
+      <c r="X54" s="3">
         <v>114000</v>
       </c>
-      <c r="W54" s="3">
+      <c r="Y54" s="3">
         <v>103700</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Z54" s="3">
         <v>98700</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="AA54" s="3">
         <v>97300</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AB54" s="3">
         <v>98800</v>
       </c>
     </row>
-    <row r="55" spans="3:26" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -3896,8 +4153,10 @@
       <c r="X55" s="3"/>
       <c r="Y55" s="3"/>
       <c r="Z55" s="3"/>
-    </row>
-    <row r="56" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA55" s="3"/>
+      <c r="AB55" s="3"/>
+    </row>
+    <row r="56" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -3924,127 +4183,135 @@
       <c r="X56" s="3"/>
       <c r="Y56" s="3"/>
       <c r="Z56" s="3"/>
-    </row>
-    <row r="57" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA56" s="3"/>
+      <c r="AB56" s="3"/>
+    </row>
+    <row r="57" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>3000</v>
+      </c>
+      <c r="E57" s="3">
+        <v>3100</v>
+      </c>
+      <c r="F57" s="3">
         <v>3600</v>
       </c>
-      <c r="E57" s="3">
+      <c r="G57" s="3">
         <v>2700</v>
       </c>
-      <c r="F57" s="3">
+      <c r="H57" s="3">
         <v>4200</v>
       </c>
-      <c r="G57" s="3">
-        <v>2500</v>
-      </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
+        <v>2400</v>
+      </c>
+      <c r="J57" s="3">
         <v>3200</v>
       </c>
-      <c r="I57" s="3">
+      <c r="K57" s="3">
         <v>3500</v>
       </c>
-      <c r="J57" s="3">
+      <c r="L57" s="3">
         <v>5700</v>
       </c>
-      <c r="K57" s="3">
+      <c r="M57" s="3">
         <v>6700</v>
       </c>
-      <c r="L57" s="3">
+      <c r="N57" s="3">
         <v>7100</v>
       </c>
-      <c r="M57" s="3">
+      <c r="O57" s="3">
         <v>12900</v>
       </c>
-      <c r="N57" s="3">
+      <c r="P57" s="3">
         <v>11300</v>
       </c>
-      <c r="O57" s="3">
+      <c r="Q57" s="3">
         <v>18900</v>
       </c>
-      <c r="P57" s="3">
+      <c r="R57" s="3">
         <v>8200</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="S57" s="3">
         <v>9900</v>
       </c>
-      <c r="R57" s="3">
+      <c r="T57" s="3">
         <v>5600</v>
       </c>
-      <c r="S57" s="3">
+      <c r="U57" s="3">
         <v>3500</v>
       </c>
-      <c r="T57" s="3">
+      <c r="V57" s="3">
         <v>2000</v>
       </c>
-      <c r="U57" s="3">
-        <v>0</v>
-      </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
+        <v>0</v>
+      </c>
+      <c r="X57" s="3">
         <v>200</v>
       </c>
-      <c r="W57" s="3">
+      <c r="Y57" s="3">
         <v>400</v>
       </c>
-      <c r="X57" s="3">
-        <v>0</v>
-      </c>
-      <c r="Y57" s="3">
-        <v>0</v>
-      </c>
       <c r="Z57" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA57" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB57" s="3">
         <v>100</v>
       </c>
     </row>
-    <row r="58" spans="3:26" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>0</v>
+      </c>
+      <c r="E58" s="3">
+        <v>0</v>
+      </c>
+      <c r="F58" s="3">
         <v>49300</v>
       </c>
-      <c r="E58" s="3">
+      <c r="G58" s="3">
         <v>47400</v>
       </c>
-      <c r="F58" s="3">
+      <c r="H58" s="3">
         <v>47400</v>
       </c>
-      <c r="G58" s="3">
+      <c r="I58" s="3">
         <v>44500</v>
       </c>
-      <c r="H58" s="3">
+      <c r="J58" s="3">
         <v>34300</v>
       </c>
-      <c r="I58" s="3">
+      <c r="K58" s="3">
         <v>35300</v>
       </c>
-      <c r="J58" s="3">
+      <c r="L58" s="3">
         <v>35000</v>
       </c>
-      <c r="K58" s="3">
+      <c r="M58" s="3">
         <v>30400</v>
       </c>
-      <c r="L58" s="3">
+      <c r="N58" s="3">
         <v>40900</v>
       </c>
-      <c r="M58" s="3">
-        <v>0</v>
-      </c>
-      <c r="N58" s="3">
-        <v>0</v>
-      </c>
       <c r="O58" s="3">
+        <v>0</v>
+      </c>
+      <c r="P58" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q58" s="3">
         <v>25700</v>
       </c>
-      <c r="P58" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="Q58" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="R58" s="3" t="s">
         <v>4</v>
       </c>
@@ -4054,322 +4321,352 @@
       <c r="T58" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="U58" s="3">
-        <v>0</v>
-      </c>
-      <c r="V58" s="3">
-        <v>0</v>
-      </c>
-      <c r="W58" s="3" t="s">
-        <v>4</v>
+      <c r="U58" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="V58" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="W58" s="3">
+        <v>0</v>
       </c>
       <c r="X58" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y58" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Z58" s="3">
         <v>7000</v>
       </c>
-      <c r="Y58" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="Z58" s="3" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="59" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA58" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AB58" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="59" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>36900</v>
+      </c>
+      <c r="E59" s="3">
+        <v>60000</v>
+      </c>
+      <c r="F59" s="3">
         <v>1200</v>
       </c>
-      <c r="E59" s="3">
+      <c r="G59" s="3">
         <v>1300</v>
       </c>
-      <c r="F59" s="3">
+      <c r="H59" s="3">
         <v>600</v>
       </c>
-      <c r="G59" s="3">
+      <c r="I59" s="3">
         <v>1100</v>
       </c>
-      <c r="H59" s="3">
+      <c r="J59" s="3">
         <v>2700</v>
       </c>
-      <c r="I59" s="3">
+      <c r="K59" s="3">
         <v>2600</v>
       </c>
-      <c r="J59" s="3">
+      <c r="L59" s="3">
         <v>1500</v>
       </c>
-      <c r="K59" s="3">
+      <c r="M59" s="3">
         <v>1100</v>
       </c>
-      <c r="L59" s="3">
+      <c r="N59" s="3">
         <v>3000</v>
       </c>
-      <c r="M59" s="3">
+      <c r="O59" s="3">
         <v>4000</v>
       </c>
-      <c r="N59" s="3">
+      <c r="P59" s="3">
         <v>9100</v>
       </c>
-      <c r="O59" s="3">
+      <c r="Q59" s="3">
         <v>9600</v>
       </c>
-      <c r="P59" s="3">
+      <c r="R59" s="3">
         <v>400</v>
-      </c>
-      <c r="Q59" s="3">
-        <v>1200</v>
-      </c>
-      <c r="R59" s="3">
-        <v>500</v>
       </c>
       <c r="S59" s="3">
         <v>1200</v>
       </c>
       <c r="T59" s="3">
+        <v>500</v>
+      </c>
+      <c r="U59" s="3">
+        <v>1200</v>
+      </c>
+      <c r="V59" s="3">
         <v>100</v>
       </c>
-      <c r="U59" s="3">
+      <c r="W59" s="3">
         <v>600</v>
       </c>
-      <c r="V59" s="3">
+      <c r="X59" s="3">
         <v>400</v>
       </c>
-      <c r="W59" s="3">
+      <c r="Y59" s="3">
         <v>2400</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Z59" s="3">
         <v>1000</v>
       </c>
-      <c r="Y59" s="3">
-        <v>0</v>
-      </c>
-      <c r="Z59" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="60" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA59" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB59" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="60" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>40900</v>
+      </c>
+      <c r="E60" s="3">
+        <v>64300</v>
+      </c>
+      <c r="F60" s="3">
         <v>63200</v>
       </c>
-      <c r="E60" s="3">
+      <c r="G60" s="3">
         <v>58400</v>
       </c>
-      <c r="F60" s="3">
+      <c r="H60" s="3">
         <v>57000</v>
       </c>
-      <c r="G60" s="3">
+      <c r="I60" s="3">
         <v>50000</v>
       </c>
-      <c r="H60" s="3">
+      <c r="J60" s="3">
         <v>47400</v>
       </c>
-      <c r="I60" s="3">
+      <c r="K60" s="3">
         <v>47200</v>
       </c>
-      <c r="J60" s="3">
+      <c r="L60" s="3">
         <v>46900</v>
       </c>
-      <c r="K60" s="3">
+      <c r="M60" s="3">
         <v>42500</v>
       </c>
-      <c r="L60" s="3">
+      <c r="N60" s="3">
         <v>53900</v>
       </c>
-      <c r="M60" s="3">
+      <c r="O60" s="3">
         <v>18800</v>
       </c>
-      <c r="N60" s="3">
+      <c r="P60" s="3">
         <v>21100</v>
       </c>
-      <c r="O60" s="3">
+      <c r="Q60" s="3">
         <v>54100</v>
       </c>
-      <c r="P60" s="3">
+      <c r="R60" s="3">
         <v>8700</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="S60" s="3">
         <v>11100</v>
       </c>
-      <c r="R60" s="3">
+      <c r="T60" s="3">
         <v>6000</v>
       </c>
-      <c r="S60" s="3">
+      <c r="U60" s="3">
         <v>4700</v>
       </c>
-      <c r="T60" s="3">
+      <c r="V60" s="3">
         <v>2100</v>
       </c>
-      <c r="U60" s="3">
+      <c r="W60" s="3">
         <v>600</v>
       </c>
-      <c r="V60" s="3">
+      <c r="X60" s="3">
         <v>500</v>
       </c>
-      <c r="W60" s="3">
+      <c r="Y60" s="3">
         <v>2800</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Z60" s="3">
         <v>8000</v>
       </c>
-      <c r="Y60" s="3">
-        <v>0</v>
-      </c>
-      <c r="Z60" s="3">
+      <c r="AA60" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB60" s="3">
         <v>100</v>
       </c>
     </row>
-    <row r="61" spans="3:26" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>32000</v>
+      </c>
+      <c r="E61" s="3">
+        <v>31600</v>
+      </c>
+      <c r="F61" s="3">
         <v>3600</v>
       </c>
-      <c r="E61" s="3">
+      <c r="G61" s="3">
         <v>4400</v>
       </c>
-      <c r="F61" s="3">
+      <c r="H61" s="3">
         <v>5600</v>
       </c>
-      <c r="G61" s="3">
+      <c r="I61" s="3">
         <v>5500</v>
       </c>
-      <c r="H61" s="3">
+      <c r="J61" s="3">
         <v>5800</v>
       </c>
-      <c r="I61" s="3">
+      <c r="K61" s="3">
         <v>5300</v>
       </c>
-      <c r="J61" s="3">
+      <c r="L61" s="3">
         <v>4100</v>
       </c>
-      <c r="K61" s="3">
+      <c r="M61" s="3">
         <v>3400</v>
       </c>
-      <c r="L61" s="3">
+      <c r="N61" s="3">
         <v>2700</v>
       </c>
-      <c r="M61" s="3">
+      <c r="O61" s="3">
         <v>39300</v>
       </c>
-      <c r="N61" s="3">
+      <c r="P61" s="3">
         <v>45100</v>
       </c>
-      <c r="O61" s="3">
+      <c r="Q61" s="3">
         <v>5100</v>
       </c>
-      <c r="P61" s="3">
+      <c r="R61" s="3">
         <v>30000</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="S61" s="3">
         <v>27600</v>
       </c>
-      <c r="R61" s="3">
+      <c r="T61" s="3">
         <v>26200</v>
       </c>
-      <c r="S61" s="3">
+      <c r="U61" s="3">
         <v>23600</v>
       </c>
-      <c r="T61" s="3">
+      <c r="V61" s="3">
         <v>22400</v>
       </c>
-      <c r="U61" s="3">
-        <v>0</v>
-      </c>
-      <c r="V61" s="3">
+      <c r="W61" s="3">
+        <v>0</v>
+      </c>
+      <c r="X61" s="3">
         <v>6700</v>
       </c>
-      <c r="W61" s="3">
+      <c r="Y61" s="3">
         <v>6700</v>
       </c>
-      <c r="X61" s="3">
-        <v>0</v>
-      </c>
-      <c r="Y61" s="3">
+      <c r="Z61" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA61" s="3">
         <v>7000</v>
       </c>
-      <c r="Z61" s="3">
+      <c r="AB61" s="3">
         <v>7000</v>
       </c>
     </row>
-    <row r="62" spans="3:26" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>3400</v>
+      </c>
+      <c r="E62" s="3">
+        <v>3400</v>
+      </c>
+      <c r="F62" s="3">
         <v>2700</v>
       </c>
-      <c r="E62" s="3">
+      <c r="G62" s="3">
         <v>2700</v>
       </c>
-      <c r="F62" s="3">
+      <c r="H62" s="3">
         <v>3100</v>
-      </c>
-      <c r="G62" s="3">
-        <v>2900</v>
-      </c>
-      <c r="H62" s="3">
-        <v>3200</v>
       </c>
       <c r="I62" s="3">
         <v>2900</v>
       </c>
       <c r="J62" s="3">
+        <v>3200</v>
+      </c>
+      <c r="K62" s="3">
+        <v>2900</v>
+      </c>
+      <c r="L62" s="3">
         <v>2800</v>
       </c>
-      <c r="K62" s="3">
+      <c r="M62" s="3">
         <v>3000</v>
       </c>
-      <c r="L62" s="3">
+      <c r="N62" s="3">
         <v>1200</v>
       </c>
-      <c r="M62" s="3">
+      <c r="O62" s="3">
         <v>1400</v>
       </c>
-      <c r="N62" s="3">
+      <c r="P62" s="3">
         <v>1300</v>
       </c>
-      <c r="O62" s="3">
+      <c r="Q62" s="3">
         <v>1800</v>
       </c>
-      <c r="P62" s="3">
+      <c r="R62" s="3">
         <v>20100</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="S62" s="3">
         <v>19500</v>
       </c>
-      <c r="R62" s="3">
+      <c r="T62" s="3">
         <v>34900</v>
       </c>
-      <c r="S62" s="3">
+      <c r="U62" s="3">
         <v>39400</v>
       </c>
-      <c r="T62" s="3">
+      <c r="V62" s="3">
         <v>29300</v>
       </c>
-      <c r="U62" s="3">
+      <c r="W62" s="3">
         <v>1300</v>
       </c>
-      <c r="V62" s="3">
+      <c r="X62" s="3">
         <v>2000</v>
       </c>
-      <c r="W62" s="3">
+      <c r="Y62" s="3">
         <v>2000</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Z62" s="3">
         <v>2700</v>
       </c>
-      <c r="Y62" s="3">
+      <c r="AA62" s="3">
         <v>3200</v>
       </c>
-      <c r="Z62" s="3">
+      <c r="AB62" s="3">
         <v>3000</v>
       </c>
     </row>
-    <row r="63" spans="3:26" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -4442,8 +4739,14 @@
       <c r="Z63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA63" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -4516,8 +4819,14 @@
       <c r="Z64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA64" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -4590,82 +4899,94 @@
       <c r="Z65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA65" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>78500</v>
+      </c>
+      <c r="E66" s="3">
+        <v>101600</v>
+      </c>
+      <c r="F66" s="3">
         <v>71800</v>
       </c>
-      <c r="E66" s="3">
+      <c r="G66" s="3">
         <v>69300</v>
       </c>
-      <c r="F66" s="3">
+      <c r="H66" s="3">
         <v>67900</v>
       </c>
-      <c r="G66" s="3">
+      <c r="I66" s="3">
         <v>60600</v>
       </c>
-      <c r="H66" s="3">
+      <c r="J66" s="3">
         <v>58600</v>
       </c>
-      <c r="I66" s="3">
+      <c r="K66" s="3">
         <v>57100</v>
       </c>
-      <c r="J66" s="3">
+      <c r="L66" s="3">
         <v>55300</v>
       </c>
-      <c r="K66" s="3">
+      <c r="M66" s="3">
         <v>49500</v>
       </c>
-      <c r="L66" s="3">
+      <c r="N66" s="3">
         <v>58500</v>
       </c>
-      <c r="M66" s="3">
+      <c r="O66" s="3">
         <v>60300</v>
       </c>
-      <c r="N66" s="3">
+      <c r="P66" s="3">
         <v>68200</v>
       </c>
-      <c r="O66" s="3">
+      <c r="Q66" s="3">
         <v>61000</v>
       </c>
-      <c r="P66" s="3">
+      <c r="R66" s="3">
         <v>58800</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="S66" s="3">
         <v>58200</v>
       </c>
-      <c r="R66" s="3">
+      <c r="T66" s="3">
         <v>67100</v>
       </c>
-      <c r="S66" s="3">
+      <c r="U66" s="3">
         <v>67600</v>
       </c>
-      <c r="T66" s="3">
+      <c r="V66" s="3">
         <v>53900</v>
       </c>
-      <c r="U66" s="3">
+      <c r="W66" s="3">
         <v>1900</v>
       </c>
-      <c r="V66" s="3">
+      <c r="X66" s="3">
         <v>9300</v>
       </c>
-      <c r="W66" s="3">
+      <c r="Y66" s="3">
         <v>11500</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Z66" s="3">
         <v>10700</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="AA66" s="3">
         <v>10200</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AB66" s="3">
         <v>10100</v>
       </c>
     </row>
-    <row r="67" spans="2:26" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -4692,8 +5013,10 @@
       <c r="X67" s="3"/>
       <c r="Y67" s="3"/>
       <c r="Z67" s="3"/>
-    </row>
-    <row r="68" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA67" s="3"/>
+      <c r="AB67" s="3"/>
+    </row>
+    <row r="68" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -4766,8 +5089,14 @@
       <c r="Z68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA68" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -4840,8 +5169,14 @@
       <c r="Z69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA69" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -4914,8 +5249,14 @@
       <c r="Z70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA70" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -4988,82 +5329,94 @@
       <c r="Z71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA71" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-272400</v>
+      </c>
+      <c r="E72" s="3">
+        <v>-297800</v>
+      </c>
+      <c r="F72" s="3">
         <v>-211300</v>
       </c>
-      <c r="E72" s="3">
+      <c r="G72" s="3">
         <v>-211400</v>
       </c>
-      <c r="F72" s="3">
+      <c r="H72" s="3">
         <v>-200100</v>
       </c>
-      <c r="G72" s="3">
+      <c r="I72" s="3">
         <v>-191100</v>
       </c>
-      <c r="H72" s="3">
+      <c r="J72" s="3">
         <v>-197100</v>
       </c>
-      <c r="I72" s="3">
+      <c r="K72" s="3">
         <v>-192400</v>
       </c>
-      <c r="J72" s="3">
+      <c r="L72" s="3">
         <v>-190200</v>
       </c>
-      <c r="K72" s="3">
+      <c r="M72" s="3">
         <v>-185900</v>
       </c>
-      <c r="L72" s="3">
+      <c r="N72" s="3">
         <v>-147800</v>
       </c>
-      <c r="M72" s="3">
+      <c r="O72" s="3">
         <v>-144100</v>
       </c>
-      <c r="N72" s="3">
+      <c r="P72" s="3">
         <v>-149700</v>
       </c>
-      <c r="O72" s="3">
+      <c r="Q72" s="3">
         <v>-162900</v>
       </c>
-      <c r="P72" s="3">
+      <c r="R72" s="3">
         <v>-173900</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="S72" s="3">
         <v>-166600</v>
       </c>
-      <c r="R72" s="3">
+      <c r="T72" s="3">
         <v>-174000</v>
       </c>
-      <c r="S72" s="3">
+      <c r="U72" s="3">
         <v>-176800</v>
       </c>
-      <c r="T72" s="3">
+      <c r="V72" s="3">
         <v>-161500</v>
       </c>
-      <c r="U72" s="3">
+      <c r="W72" s="3">
         <v>-151200</v>
       </c>
-      <c r="V72" s="3">
+      <c r="X72" s="3">
         <v>-145000</v>
       </c>
-      <c r="W72" s="3">
+      <c r="Y72" s="3">
         <v>-143000</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Z72" s="3">
         <v>-145900</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="AA72" s="3">
         <v>-145200</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AB72" s="3">
         <v>-143600</v>
       </c>
     </row>
-    <row r="73" spans="2:26" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -5136,8 +5489,14 @@
       <c r="Z73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA73" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -5210,8 +5569,14 @@
       <c r="Z74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA74" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -5284,82 +5649,94 @@
       <c r="Z75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA75" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>59600</v>
+      </c>
+      <c r="E76" s="3">
+        <v>33700</v>
+      </c>
+      <c r="F76" s="3">
         <v>34500</v>
       </c>
-      <c r="E76" s="3">
+      <c r="G76" s="3">
         <v>37500</v>
       </c>
-      <c r="F76" s="3">
+      <c r="H76" s="3">
         <v>37400</v>
       </c>
-      <c r="G76" s="3">
+      <c r="I76" s="3">
         <v>44700</v>
       </c>
-      <c r="H76" s="3">
+      <c r="J76" s="3">
         <v>48500</v>
       </c>
-      <c r="I76" s="3">
+      <c r="K76" s="3">
         <v>51200</v>
       </c>
-      <c r="J76" s="3">
+      <c r="L76" s="3">
         <v>55000</v>
       </c>
-      <c r="K76" s="3">
+      <c r="M76" s="3">
         <v>63100</v>
       </c>
-      <c r="L76" s="3">
+      <c r="N76" s="3">
         <v>96900</v>
       </c>
-      <c r="M76" s="3">
+      <c r="O76" s="3">
         <v>90000</v>
       </c>
-      <c r="N76" s="3">
+      <c r="P76" s="3">
         <v>78700</v>
       </c>
-      <c r="O76" s="3">
+      <c r="Q76" s="3">
         <v>126500</v>
       </c>
-      <c r="P76" s="3">
+      <c r="R76" s="3">
         <v>112100</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="S76" s="3">
         <v>118200</v>
       </c>
-      <c r="R76" s="3">
+      <c r="T76" s="3">
         <v>104200</v>
       </c>
-      <c r="S76" s="3">
+      <c r="U76" s="3">
         <v>100000</v>
       </c>
-      <c r="T76" s="3">
+      <c r="V76" s="3">
         <v>107000</v>
       </c>
-      <c r="U76" s="3">
+      <c r="W76" s="3">
         <v>108200</v>
       </c>
-      <c r="V76" s="3">
+      <c r="X76" s="3">
         <v>104700</v>
       </c>
-      <c r="W76" s="3">
+      <c r="Y76" s="3">
         <v>92200</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Z76" s="3">
         <v>88000</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="AA76" s="3">
         <v>87200</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AB76" s="3">
         <v>88700</v>
       </c>
     </row>
-    <row r="77" spans="2:26" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -5432,161 +5809,179 @@
       <c r="Z77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA77" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:28" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:26" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>46112</v>
+      </c>
+      <c r="E80" s="2">
+        <v>46022</v>
+      </c>
+      <c r="F80" s="2">
         <v>45930</v>
       </c>
-      <c r="E80" s="2">
+      <c r="G80" s="2">
         <v>45838</v>
       </c>
-      <c r="F80" s="2">
+      <c r="H80" s="2">
         <v>45747</v>
       </c>
-      <c r="G80" s="2">
+      <c r="I80" s="2">
         <v>45657</v>
       </c>
-      <c r="H80" s="2">
+      <c r="J80" s="2">
         <v>45565</v>
       </c>
-      <c r="I80" s="2">
+      <c r="K80" s="2">
         <v>45473</v>
       </c>
-      <c r="J80" s="2">
+      <c r="L80" s="2">
         <v>45382</v>
       </c>
-      <c r="K80" s="2">
+      <c r="M80" s="2">
         <v>45291</v>
       </c>
-      <c r="L80" s="2">
+      <c r="N80" s="2">
         <v>45199</v>
       </c>
-      <c r="M80" s="2">
+      <c r="O80" s="2">
         <v>45107</v>
       </c>
-      <c r="N80" s="2">
+      <c r="P80" s="2">
         <v>45016</v>
       </c>
-      <c r="O80" s="2">
+      <c r="Q80" s="2">
         <v>44926</v>
       </c>
-      <c r="P80" s="2">
+      <c r="R80" s="2">
         <v>44834</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="S80" s="2">
         <v>44742</v>
       </c>
-      <c r="R80" s="2">
+      <c r="T80" s="2">
         <v>44651</v>
       </c>
-      <c r="S80" s="2">
+      <c r="U80" s="2">
         <v>44561</v>
       </c>
-      <c r="T80" s="2">
+      <c r="V80" s="2">
         <v>44469</v>
       </c>
-      <c r="U80" s="2">
+      <c r="W80" s="2">
         <v>44377</v>
       </c>
-      <c r="V80" s="2">
+      <c r="X80" s="2">
         <v>44286</v>
       </c>
-      <c r="W80" s="2">
+      <c r="Y80" s="2">
         <v>44196</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Z80" s="2">
         <v>44104</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="AA80" s="2">
         <v>44012</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AB80" s="2">
         <v>43921</v>
       </c>
     </row>
-    <row r="81" spans="3:26" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>20200</v>
+      </c>
+      <c r="E81" s="3">
+        <v>-83200</v>
+      </c>
+      <c r="F81" s="3">
         <v>-3400</v>
       </c>
-      <c r="E81" s="3">
+      <c r="G81" s="3">
         <v>-1500</v>
       </c>
-      <c r="F81" s="3">
+      <c r="H81" s="3">
         <v>-8800</v>
       </c>
-      <c r="G81" s="3">
+      <c r="I81" s="3">
         <v>-6000</v>
       </c>
-      <c r="H81" s="3">
+      <c r="J81" s="3">
         <v>-2200</v>
       </c>
-      <c r="I81" s="3">
+      <c r="K81" s="3">
         <v>-4200</v>
       </c>
-      <c r="J81" s="3">
+      <c r="L81" s="3">
         <v>-9000</v>
       </c>
-      <c r="K81" s="3">
+      <c r="M81" s="3">
         <v>-35500</v>
       </c>
-      <c r="L81" s="3">
+      <c r="N81" s="3">
         <v>-6800</v>
       </c>
-      <c r="M81" s="3">
+      <c r="O81" s="3">
         <v>8900</v>
       </c>
-      <c r="N81" s="3">
+      <c r="P81" s="3">
         <v>-15000</v>
       </c>
-      <c r="O81" s="3">
+      <c r="Q81" s="3">
         <v>10300</v>
       </c>
-      <c r="P81" s="3">
+      <c r="R81" s="3">
         <v>-7600</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="S81" s="3">
         <v>7500</v>
       </c>
-      <c r="R81" s="3">
+      <c r="T81" s="3">
         <v>2300</v>
       </c>
-      <c r="S81" s="3">
+      <c r="U81" s="3">
         <v>-15500</v>
       </c>
-      <c r="T81" s="3">
+      <c r="V81" s="3">
         <v>-10500</v>
       </c>
-      <c r="U81" s="3">
+      <c r="W81" s="3">
         <v>-6400</v>
       </c>
-      <c r="V81" s="3">
+      <c r="X81" s="3">
         <v>-2500</v>
       </c>
-      <c r="W81" s="3">
+      <c r="Y81" s="3">
         <v>2900</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Z81" s="3">
         <v>-1500</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="AA81" s="3">
         <v>-1700</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AB81" s="3">
         <v>-2100</v>
       </c>
     </row>
-    <row r="82" spans="3:26" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -5613,8 +6008,10 @@
       <c r="X82" s="3"/>
       <c r="Y82" s="3"/>
       <c r="Z82" s="3"/>
-    </row>
-    <row r="83" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA82" s="3"/>
+      <c r="AB82" s="3"/>
+    </row>
+    <row r="83" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
@@ -5642,35 +6039,35 @@
       <c r="K83" s="3">
         <v>0</v>
       </c>
-      <c r="L83" s="3" t="s">
-        <v>4</v>
+      <c r="L83" s="3">
+        <v>0</v>
       </c>
       <c r="M83" s="3">
         <v>0</v>
       </c>
-      <c r="N83" s="3">
-        <v>0</v>
-      </c>
-      <c r="O83" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="P83" s="3" t="s">
-        <v>4</v>
+      <c r="N83" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="O83" s="3">
+        <v>0</v>
+      </c>
+      <c r="P83" s="3">
+        <v>0</v>
       </c>
       <c r="Q83" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="R83" s="3">
-        <v>0</v>
-      </c>
-      <c r="S83" s="3">
-        <v>0</v>
-      </c>
-      <c r="T83" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="U83" s="3" t="s">
-        <v>4</v>
+      <c r="R83" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="S83" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="T83" s="3">
+        <v>0</v>
+      </c>
+      <c r="U83" s="3">
+        <v>0</v>
       </c>
       <c r="V83" s="3" t="s">
         <v>4</v>
@@ -5687,8 +6084,14 @@
       <c r="Z83" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="84" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA83" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AB83" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="84" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -5761,8 +6164,14 @@
       <c r="Z84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA84" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -5835,8 +6244,14 @@
       <c r="Z85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA85" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -5909,8 +6324,14 @@
       <c r="Z86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA86" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -5983,8 +6404,14 @@
       <c r="Z87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA87" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -6057,82 +6484,94 @@
       <c r="Z88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA88" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>-2900</v>
+      </c>
+      <c r="E89" s="3">
+        <v>-6600</v>
+      </c>
+      <c r="F89" s="3">
         <v>-1600</v>
       </c>
-      <c r="E89" s="3">
+      <c r="G89" s="3">
         <v>-3300</v>
       </c>
-      <c r="F89" s="3">
+      <c r="H89" s="3">
         <v>-100</v>
       </c>
-      <c r="G89" s="3">
+      <c r="I89" s="3">
         <v>-4300</v>
       </c>
-      <c r="H89" s="3">
+      <c r="J89" s="3">
         <v>-2200</v>
       </c>
-      <c r="I89" s="3">
+      <c r="K89" s="3">
         <v>-2800</v>
       </c>
-      <c r="J89" s="3">
+      <c r="L89" s="3">
         <v>-3000</v>
       </c>
-      <c r="K89" s="3">
+      <c r="M89" s="3">
         <v>-4500</v>
       </c>
-      <c r="L89" s="3">
+      <c r="N89" s="3">
         <v>-8900</v>
       </c>
-      <c r="M89" s="3">
+      <c r="O89" s="3">
         <v>-3000</v>
       </c>
-      <c r="N89" s="3">
+      <c r="P89" s="3">
         <v>-700</v>
       </c>
-      <c r="O89" s="3">
+      <c r="Q89" s="3">
         <v>-6600</v>
       </c>
-      <c r="P89" s="3">
+      <c r="R89" s="3">
         <v>-500</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="S89" s="3">
         <v>-5300</v>
       </c>
-      <c r="R89" s="3">
+      <c r="T89" s="3">
         <v>-3500</v>
       </c>
-      <c r="S89" s="3">
+      <c r="U89" s="3">
         <v>-4900</v>
       </c>
-      <c r="T89" s="3">
+      <c r="V89" s="3">
         <v>-5300</v>
       </c>
-      <c r="U89" s="3">
+      <c r="W89" s="3">
         <v>-3600</v>
       </c>
-      <c r="V89" s="3">
+      <c r="X89" s="3">
         <v>-3100</v>
       </c>
-      <c r="W89" s="3">
+      <c r="Y89" s="3">
         <v>-1500</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Z89" s="3">
         <v>-1200</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="AA89" s="3">
         <v>-1100</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AB89" s="3">
         <v>-1800</v>
       </c>
     </row>
-    <row r="90" spans="3:26" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -6159,82 +6598,90 @@
       <c r="X90" s="3"/>
       <c r="Y90" s="3"/>
       <c r="Z90" s="3"/>
-    </row>
-    <row r="91" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA90" s="3"/>
+      <c r="AB90" s="3"/>
+    </row>
+    <row r="91" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-2500</v>
+      </c>
+      <c r="E91" s="3">
+        <v>-2500</v>
+      </c>
+      <c r="F91" s="3">
         <v>-300</v>
       </c>
-      <c r="E91" s="3">
+      <c r="G91" s="3">
         <v>-300</v>
       </c>
-      <c r="F91" s="3">
+      <c r="H91" s="3">
         <v>-200</v>
       </c>
-      <c r="G91" s="3">
+      <c r="I91" s="3">
         <v>-100</v>
       </c>
-      <c r="H91" s="3">
+      <c r="J91" s="3">
         <v>-100</v>
       </c>
-      <c r="I91" s="3">
+      <c r="K91" s="3">
         <v>200</v>
       </c>
-      <c r="J91" s="3">
+      <c r="L91" s="3">
         <v>-400</v>
       </c>
-      <c r="K91" s="3">
+      <c r="M91" s="3">
         <v>400</v>
       </c>
-      <c r="L91" s="3">
+      <c r="N91" s="3">
         <v>400</v>
       </c>
-      <c r="M91" s="3">
+      <c r="O91" s="3">
         <v>-1900</v>
       </c>
-      <c r="N91" s="3">
+      <c r="P91" s="3">
         <v>-9100</v>
       </c>
-      <c r="O91" s="3">
+      <c r="Q91" s="3">
         <v>-15600</v>
       </c>
-      <c r="P91" s="3">
+      <c r="R91" s="3">
         <v>-18800</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="S91" s="3">
         <v>-8700</v>
       </c>
-      <c r="R91" s="3">
+      <c r="T91" s="3">
         <v>-4500</v>
       </c>
-      <c r="S91" s="3">
+      <c r="U91" s="3">
         <v>-6100</v>
       </c>
-      <c r="T91" s="3">
+      <c r="V91" s="3">
         <v>-600</v>
       </c>
-      <c r="U91" s="3">
+      <c r="W91" s="3">
         <v>500</v>
       </c>
-      <c r="V91" s="3">
+      <c r="X91" s="3">
         <v>-500</v>
       </c>
-      <c r="W91" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="X91" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="Y91" s="3" t="s">
         <v>4</v>
       </c>
       <c r="Z91" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="92" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA91" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AB91" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="92" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -6307,8 +6754,14 @@
       <c r="Z92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA92" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -6381,71 +6834,77 @@
       <c r="Z93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA93" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-2500</v>
+      </c>
+      <c r="E94" s="3">
+        <v>-2500</v>
+      </c>
+      <c r="F94" s="3">
         <v>-300</v>
       </c>
-      <c r="E94" s="3">
+      <c r="G94" s="3">
         <v>-300</v>
       </c>
-      <c r="F94" s="3">
+      <c r="H94" s="3">
         <v>-200</v>
       </c>
-      <c r="G94" s="3">
+      <c r="I94" s="3">
         <v>-100</v>
       </c>
-      <c r="H94" s="3">
+      <c r="J94" s="3">
         <v>300</v>
       </c>
-      <c r="I94" s="3">
+      <c r="K94" s="3">
         <v>700</v>
       </c>
-      <c r="J94" s="3">
-        <v>0</v>
-      </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
+        <v>0</v>
+      </c>
+      <c r="M94" s="3">
         <v>-1200</v>
       </c>
-      <c r="L94" s="3">
+      <c r="N94" s="3">
         <v>600</v>
       </c>
-      <c r="M94" s="3">
+      <c r="O94" s="3">
         <v>-800</v>
       </c>
-      <c r="N94" s="3">
+      <c r="P94" s="3">
         <v>-9100</v>
       </c>
-      <c r="O94" s="3">
+      <c r="Q94" s="3">
         <v>-10900</v>
       </c>
-      <c r="P94" s="3">
+      <c r="R94" s="3">
         <v>-18800</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="S94" s="3">
         <v>-8700</v>
       </c>
-      <c r="R94" s="3">
+      <c r="T94" s="3">
         <v>-5100</v>
       </c>
-      <c r="S94" s="3">
+      <c r="U94" s="3">
         <v>-6100</v>
       </c>
-      <c r="T94" s="3">
+      <c r="V94" s="3">
         <v>-500</v>
       </c>
-      <c r="U94" s="3">
+      <c r="W94" s="3">
         <v>-1500</v>
       </c>
-      <c r="V94" s="3">
-        <v>0</v>
-      </c>
-      <c r="W94" s="3">
-        <v>0</v>
-      </c>
       <c r="X94" s="3">
         <v>0</v>
       </c>
@@ -6455,8 +6914,14 @@
       <c r="Z94" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="95" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA94" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB94" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="95" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -6483,8 +6948,10 @@
       <c r="X95" s="3"/>
       <c r="Y95" s="3"/>
       <c r="Z95" s="3"/>
-    </row>
-    <row r="96" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA95" s="3"/>
+      <c r="AB95" s="3"/>
+    </row>
+    <row r="96" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -6521,11 +6988,11 @@
       <c r="N96" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="O96" s="3">
-        <v>0</v>
-      </c>
-      <c r="P96" s="3">
-        <v>0</v>
+      <c r="O96" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="P96" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="Q96" s="3">
         <v>0</v>
@@ -6557,8 +7024,14 @@
       <c r="Z96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA96" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -6631,8 +7104,14 @@
       <c r="Z97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA97" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -6705,8 +7184,14 @@
       <c r="Z98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA98" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -6779,82 +7264,94 @@
       <c r="Z99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA99" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>6300</v>
+      </c>
+      <c r="E100" s="3">
+        <v>35300</v>
+      </c>
+      <c r="F100" s="3">
         <v>2000</v>
       </c>
-      <c r="E100" s="3">
+      <c r="G100" s="3">
         <v>3400</v>
       </c>
-      <c r="F100" s="3">
-        <v>0</v>
-      </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
+        <v>0</v>
+      </c>
+      <c r="I100" s="3">
         <v>4700</v>
       </c>
-      <c r="H100" s="3">
+      <c r="J100" s="3">
         <v>700</v>
       </c>
-      <c r="I100" s="3">
+      <c r="K100" s="3">
         <v>1400</v>
       </c>
-      <c r="J100" s="3">
+      <c r="L100" s="3">
         <v>1700</v>
       </c>
-      <c r="K100" s="3">
-        <v>0</v>
-      </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
+        <v>0</v>
+      </c>
+      <c r="N100" s="3">
         <v>14900</v>
       </c>
-      <c r="M100" s="3">
-        <v>0</v>
-      </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
+        <v>0</v>
+      </c>
+      <c r="P100" s="3">
         <v>12200</v>
       </c>
-      <c r="O100" s="3">
+      <c r="Q100" s="3">
         <v>6500</v>
       </c>
-      <c r="P100" s="3">
+      <c r="R100" s="3">
         <v>-2500</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="S100" s="3">
         <v>2900</v>
       </c>
-      <c r="R100" s="3">
+      <c r="T100" s="3">
         <v>1600</v>
       </c>
-      <c r="S100" s="3">
+      <c r="U100" s="3">
         <v>8500</v>
       </c>
-      <c r="T100" s="3">
+      <c r="V100" s="3">
         <v>54900</v>
       </c>
-      <c r="U100" s="3">
+      <c r="W100" s="3">
         <v>600</v>
       </c>
-      <c r="V100" s="3">
+      <c r="X100" s="3">
         <v>14900</v>
       </c>
-      <c r="W100" s="3">
+      <c r="Y100" s="3">
         <v>1100</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Z100" s="3">
         <v>2400</v>
       </c>
-      <c r="Y100" s="3">
-        <v>0</v>
-      </c>
-      <c r="Z100" s="3">
+      <c r="AA100" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB100" s="3">
         <v>2100</v>
       </c>
     </row>
-    <row r="101" spans="3:26" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -6868,14 +7365,14 @@
         <v>0</v>
       </c>
       <c r="G101" s="3">
+        <v>0</v>
+      </c>
+      <c r="H101" s="3">
+        <v>0</v>
+      </c>
+      <c r="I101" s="3">
         <v>100</v>
       </c>
-      <c r="H101" s="3">
-        <v>0</v>
-      </c>
-      <c r="I101" s="3">
-        <v>0</v>
-      </c>
       <c r="J101" s="3">
         <v>0</v>
       </c>
@@ -6889,116 +7386,128 @@
         <v>0</v>
       </c>
       <c r="N101" s="3">
+        <v>0</v>
+      </c>
+      <c r="O101" s="3">
+        <v>0</v>
+      </c>
+      <c r="P101" s="3">
         <v>200</v>
       </c>
-      <c r="O101" s="3">
-        <v>0</v>
-      </c>
-      <c r="P101" s="3">
-        <v>0</v>
-      </c>
       <c r="Q101" s="3">
         <v>0</v>
       </c>
       <c r="R101" s="3">
+        <v>0</v>
+      </c>
+      <c r="S101" s="3">
+        <v>0</v>
+      </c>
+      <c r="T101" s="3">
         <v>200</v>
       </c>
-      <c r="S101" s="3">
+      <c r="U101" s="3">
         <v>-100</v>
       </c>
-      <c r="T101" s="3">
+      <c r="V101" s="3">
         <v>600</v>
       </c>
-      <c r="U101" s="3">
-        <v>0</v>
-      </c>
-      <c r="V101" s="3">
-        <v>0</v>
-      </c>
       <c r="W101" s="3">
+        <v>0</v>
+      </c>
+      <c r="X101" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y101" s="3">
         <v>-100</v>
       </c>
-      <c r="X101" s="3">
-        <v>0</v>
-      </c>
-      <c r="Y101" s="3">
-        <v>0</v>
-      </c>
       <c r="Z101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA101" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>800</v>
+      </c>
+      <c r="E102" s="3">
+        <v>26200</v>
+      </c>
+      <c r="F102" s="3">
         <v>100</v>
       </c>
-      <c r="E102" s="3">
+      <c r="G102" s="3">
         <v>-200</v>
       </c>
-      <c r="F102" s="3">
+      <c r="H102" s="3">
         <v>-300</v>
       </c>
-      <c r="G102" s="3">
+      <c r="I102" s="3">
         <v>300</v>
       </c>
-      <c r="H102" s="3">
+      <c r="J102" s="3">
         <v>-1100</v>
       </c>
-      <c r="I102" s="3">
+      <c r="K102" s="3">
         <v>-600</v>
       </c>
-      <c r="J102" s="3">
+      <c r="L102" s="3">
         <v>-1400</v>
       </c>
-      <c r="K102" s="3">
+      <c r="M102" s="3">
         <v>-5700</v>
       </c>
-      <c r="L102" s="3">
+      <c r="N102" s="3">
         <v>6500</v>
       </c>
-      <c r="M102" s="3">
+      <c r="O102" s="3">
         <v>-3800</v>
       </c>
-      <c r="N102" s="3">
+      <c r="P102" s="3">
         <v>2400</v>
       </c>
-      <c r="O102" s="3">
+      <c r="Q102" s="3">
         <v>-11000</v>
       </c>
-      <c r="P102" s="3">
+      <c r="R102" s="3">
         <v>-21800</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="S102" s="3">
         <v>-11200</v>
       </c>
-      <c r="R102" s="3">
+      <c r="T102" s="3">
         <v>-6700</v>
       </c>
-      <c r="S102" s="3">
+      <c r="U102" s="3">
         <v>-2600</v>
       </c>
-      <c r="T102" s="3">
+      <c r="V102" s="3">
         <v>49700</v>
       </c>
-      <c r="U102" s="3">
+      <c r="W102" s="3">
         <v>-4500</v>
       </c>
-      <c r="V102" s="3">
+      <c r="X102" s="3">
         <v>11800</v>
       </c>
-      <c r="W102" s="3">
+      <c r="Y102" s="3">
         <v>-500</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Z102" s="3">
         <v>1100</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="AA102" s="3">
         <v>-1100</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AB102" s="3">
         <v>200</v>
       </c>
     </row>
